--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -13,6 +13,7 @@
     <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +45,29 @@
       <b val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -62,8 +84,13 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -71,11 +98,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="009DB7E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="009DB7E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="009DB7E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="009DB7E8"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -92,6 +133,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1644,4 +1697,85 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002F5597"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ماشین حالت ماژول نگهبان اعتبار (Protection)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>حالت‌ها و گذارهای همین ماژول</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Protection_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>../../../Documentation/System_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>راهنمای رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>بازتولید</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>python3 tools/make_module_state_machines.py</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -593,7 +593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1075,6 +1075,76 @@
       <c r="Q9" s="4" t="inlineStr">
         <is>
           <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PR-010</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>snapshot zeroing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>snapshot نامعتبر به Protection_Run بده</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2s</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>فقط valid چک شود؛ هر 9 فیلد صفر؛ FAULT_ADC زنده بماند بدون latch کاذب</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>بدون fault کاذب</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -974,7 +974,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>این ماژول فقط FAULT_ADC را لمس می‌کند؛ BAT_LOست مالک Fault است</t>
+          <t>این ماژول فقط FAULT_ADC را لمس می‌کند؛ FAULT_CHARGER_BAT_LOST مالک Fault است</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -1134,14 +1134,11 @@
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
           <t>2026-10-12</t>

--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -746,7 +746,9 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>رفتار بوت و شارژ عادی را ببین</t>
+          <t>گام ۱: بیلد معمولی را بگیر که در آن MODULE_PROTECTION=0 است.
+گام ۲: برد را بوت کن و 60 ثانیه شارژ عادی را نگاه کن.
+گام ۳: هیچ خطایی نباید از این ماژول بیاید (Protection_Run اصلاً اجرا نمی‌شود) و رفتار کل سیستم باید مثل وقتی باشد که ماژول اصلاً وجود ندارد؛ مخصوصاً FAULT_ADC نباید القا شود.</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -817,7 +819,10 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>ADC را موقتاً نامعتبر کن (قطع ورودی در warm-up)</t>
+          <t>گام ۱: یک بیلد تستی بگیر که در آن MODULE_PROTECTION=1 باشد.
+گام ۲: ADC را موقتاً نامعتبر کن (مثلاً ورودی را در دورهٔ warm-up قطع کن تا snapshot نامعتبر شود).
+گام ۳: بیت FAULT_ADC باید لحظه‌ای ست شود (در پنل/ماسک ببین).
+گام ۴: ADC را معتبر کن و اولین snapshot معتبر را بده (5 ثانیه کافی است): بیت باید خودش پاک شود؛ بیت بعد از معتبر شدن صفر است.</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -888,7 +893,10 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>بوت سرد؛ پاس‌های اول حفاظت قبل از warm-up اندازه‌گیری</t>
+          <t>گام ۱: بیلد تستی با MODULE_PROTECTION=1 را روی برد بزن.
+گام ۲: بوت سرد بگیر (برق را قطع و وصل کن).
+گام ۳: 10 ثانیه اول را نگاه کن: پاس‌های اول حفاظت قبل از warm-up اندازه‌گیری اجرا می‌شوند و FAULT_ADC فقط لحظه‌ای می‌آید.
+گام ۴: سیستم باید خودش به حالت عادی برسد؛ Changeover نباید در APP_STATE_FAULT گیر کند و شارژر نباید برای همیشه safe-idle بماند.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -959,7 +967,10 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>بیت‌های FAULT_* با ماژول Fault مقایسه شود</t>
+          <t>گام ۱: جدول بیت‌های FAULT_* در app_types.h را جلوی خودت بگذار.
+گام ۲: کد protection.c را خط‌به‌خط با مالکیت بیت‌ها مقایسه کن.
+گام ۳: این ماژول باید فقط FAULT_ADC را ست/پاک کند؛ FAULT_CHARGER_BAT_LOST مال ماژول Fault است و بقیهٔ بیت‌ها هم صاحب خودشان را دارند.
+گام ۴: هیچ تداخلی بین بیت‌ها نباید باشد.</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -1030,7 +1041,10 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>مرور کد برای طراحی حفاظت کامل</t>
+          <t>گام ۱: کد ماژول را کامل مرور کن (protection.c و هدرش).
+گام ۲: شرایط فعال‌سازی حفاظت کامل (اضافه‌جریان، باتری ضعیف و...) و سیاست هر کدام را روی کاغذ بنویس.
+گام ۳: قبل از اینکه MODULE_PROTECTION=1 شود، سند تصمیم را به تأیید کاربر برسان.
+گام ۴: قبولی یعنی همین سند تصمیم موجود و تأیید شده باشد؛ این ردیف تست برد نیست.</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1101,7 +1115,10 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>snapshot نامعتبر به Protection_Run بده</t>
+          <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
+گام ۲: آن را 2 ثانیه به Protection_Run بده.
+گام ۳: تابع باید فقط valid را چک کند و به فیلدهای صفر دست نزند.
+گام ۴: FAULT_ADC باید به‌صورت زنده (بدون latch) بماند و هیچ fault کاذبی ساخته نشود.</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">

--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -15,15 +15,20 @@
     <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="8">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,8 +71,67 @@
       <name val="Vazirmatn"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -89,8 +153,28 @@
         <fgColor rgb="001F3864"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F6FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -112,11 +196,69 @@
         <color rgb="009DB7E8"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -144,6 +286,88 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -507,6 +731,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -517,21 +742,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Protection</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>Protection | اسکلت حفاظت (MODULE_PROTECTION=0) — FAULT_ADC به‌صورت وضعیت لحظه‌ای</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -541,21 +766,21 @@
       <c r="A4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>ماژول در build فعال نیست؛ تنها رفتار تعریف‌شده: Set بیت FAULT_ADC با snapshot نامعتبر و Clear آن با snapshot معتبر (لحظه‌ای، نه latch).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>ایراد قدیمی «latch ابدی FAULT_ADC در بوت» در ممیزی ۲۰۲۶-۰۹-۲۲ اصلاح شد؛ Changeover دیگر در بوت در FAULT گیر نمی‌کند.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>فعال‌سازی آیندهٔ حفاظت کامل (اضافه‌جریان/باتری ضعیف) با MODULE_PROTECTION=1 و به دستور کاربر.</t>
         </is>
@@ -565,7 +790,7 @@
       <c r="A8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>یادداشت: تست‌های PR-002/PR-003 به بیلد تستی با MODULE_PROTECTION=1 نیاز دارند؛ در بیلد فعلی فقط PR-001 قابل اجراست.</t>
         </is>
@@ -583,6 +808,9 @@
     <mergeCell ref="A5"/>
     <mergeCell ref="A1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -590,234 +818,235 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="24" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Protection</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="14" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="14" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="14" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="14" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="J4" s="14" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="K4" s="14" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="L4" s="14" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M4" s="14" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N4" s="14" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="14" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P4" s="14" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q4" s="14" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="5" ht="40.5" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>PR-001</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>ماژول خاموش</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>MODULE_PROTECTION=0</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>گام ۱: بیلد معمولی را بگیر که در آن MODULE_PROTECTION=0 است.
 گام ۲: برد را بوت کن و 60 ثانیه شارژ عادی را نگاه کن.
 گام ۳: هیچ خطایی نباید از این ماژول بیاید (Protection_Run اصلاً اجرا نمی‌شود) و رفتار کل سیستم باید مثل وقتی باشد که ماژول اصلاً وجود ندارد؛ مخصوصاً FAULT_ADC نباید القا شود.</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>60s</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="18" t="inlineStr">
         <is>
           <t>Run اجرا نمی‌شود؛ هیچ خطایی از این ماژول نمی‌آید؛ رفتار سیستم مثل نبود ماژول</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="18" t="inlineStr">
         <is>
           <t>بدون FAULT_ADC القایی</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="K5" s="18" t="inlineStr"/>
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="inlineStr">
+      <c r="M5" s="18" t="inlineStr"/>
+      <c r="N5" s="18" t="inlineStr"/>
+      <c r="O5" s="20" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr">
+      <c r="P5" s="20" t="inlineStr"/>
+      <c r="Q5" s="22" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>PR-002</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>FAULT_ADC لحظه‌ای</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>بیلد تستی با MODULE_PROTECTION=1</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>گام ۱: یک بیلد تستی بگیر که در آن MODULE_PROTECTION=1 باشد.
 گام ۲: ADC را موقتاً نامعتبر کن (مثلاً ورودی را در دورهٔ warm-up قطع کن تا snapshot نامعتبر شود).
@@ -825,73 +1054,73 @@
 گام ۴: ADC را معتبر کن و اولین snapshot معتبر را بده (5 ثانیه کافی است): بیت باید خودش پاک شود؛ بیت بعد از معتبر شدن صفر است.</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="25" t="inlineStr">
         <is>
           <t>snapshot نامعتبر</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="25" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>Set بیت FAULT_ADC به‌صورت لحظه‌ای؛ با اولین snapshot معتبر خودش پاک می‌شود</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>لحظه‌ای نه latch</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t>بیت بعد از معتبر شدن صفر</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="K6" s="23" t="inlineStr"/>
+      <c r="L6" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr"/>
-      <c r="N6" s="4" t="inlineStr"/>
-      <c r="O6" s="4" t="inlineStr">
+      <c r="M6" s="23" t="inlineStr"/>
+      <c r="N6" s="23" t="inlineStr"/>
+      <c r="O6" s="25" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr">
+      <c r="P6" s="25" t="inlineStr"/>
+      <c r="Q6" s="26" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>PR-003</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>بوت قبل از warm-up</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="18" t="inlineStr">
         <is>
           <t>بیلد تستی با MODULE_PROTECTION=1</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>گام ۱: بیلد تستی با MODULE_PROTECTION=1 را روی برد بزن.
 گام ۲: بوت سرد بگیر (برق را قطع و وصل کن).
@@ -899,73 +1128,73 @@
 گام ۴: سیستم باید خودش به حالت عادی برسد؛ Changeover نباید در APP_STATE_FAULT گیر کند و شارژر نباید برای همیشه safe-idle بماند.</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>10s</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="18" t="inlineStr">
         <is>
           <t>FAULT_ADC لحظه‌ای؛ Changeover در APP_STATE_FAULT گیر نمی‌کند و شارژر safe-idle ابدی نمی‌ماند</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="J7" s="18" t="inlineStr">
         <is>
           <t>سیستم به حالت عادی می‌رسد</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="K7" s="18" t="inlineStr"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr"/>
-      <c r="N7" s="4" t="inlineStr"/>
-      <c r="O7" s="4" t="inlineStr">
+      <c r="M7" s="18" t="inlineStr"/>
+      <c r="N7" s="18" t="inlineStr"/>
+      <c r="O7" s="20" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P7" s="4" t="inlineStr"/>
-      <c r="Q7" s="4" t="inlineStr">
+      <c r="P7" s="20" t="inlineStr"/>
+      <c r="Q7" s="22" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="8" ht="54" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>PR-004</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>عدم تداخل مالکیت</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="41" t="inlineStr">
         <is>
           <t>گام ۱: جدول بیت‌های FAULT_* در app_types.h را جلوی خودت بگذار.
 گام ۲: کد protection.c را خط‌به‌خط با مالکیت بیت‌ها مقایسه کن.
@@ -973,73 +1202,73 @@
 گام ۴: هیچ تداخلی بین بیت‌ها نباید باشد.</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="25" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t>این ماژول فقط FAULT_ADC را لمس می‌کند؛ FAULT_CHARGER_BAT_LOST مالک Fault است</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t>بدون تداخل بیت‌ها</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="K8" s="23" t="inlineStr"/>
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr"/>
-      <c r="N8" s="4" t="inlineStr"/>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="M8" s="23" t="inlineStr"/>
+      <c r="N8" s="23" t="inlineStr"/>
+      <c r="O8" s="25" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P8" s="4" t="inlineStr"/>
-      <c r="Q8" s="4" t="inlineStr">
+      <c r="P8" s="25" t="inlineStr"/>
+      <c r="Q8" s="26" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="9" ht="54" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>PR-005</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>فعال‌سازی آینده</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="42" t="inlineStr">
         <is>
           <t>گام ۱: کد ماژول را کامل مرور کن (protection.c و هدرش).
 گام ۲: شرایط فعال‌سازی حفاظت کامل (اضافه‌جریان، باتری ضعیف و...) و سیاست هر کدام را روی کاغذ بنویس.
@@ -1047,73 +1276,73 @@
 گام ۴: قبولی یعنی همین سند تصمیم موجود و تأیید شده باشد؛ این ردیف تست برد نیست.</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="18" t="inlineStr">
         <is>
           <t>شرایط فعال‌سازی و سیاست‌ها قبل از MODULE_PROTECTION=1 مستند و به تأیید کاربر برسد</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="18" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="J9" s="18" t="inlineStr">
         <is>
           <t>سند تصمیم موجود</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="K9" s="18" t="inlineStr"/>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr"/>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="M9" s="18" t="inlineStr"/>
+      <c r="N9" s="18" t="inlineStr"/>
+      <c r="O9" s="20" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P9" s="4" t="inlineStr"/>
-      <c r="Q9" s="4" t="inlineStr">
+      <c r="P9" s="20" t="inlineStr"/>
+      <c r="Q9" s="22" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>PR-010</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>snapshot zeroing</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
 گام ۲: آن را 2 ثانیه به Protection_Run بده.
@@ -1121,68 +1350,319 @@
 گام ۴: FAULT_ADC باید به‌صورت زنده (بدون latch) بماند و هیچ fault کاذبی ساخته نشود.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="25" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="25" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t>فقط valid چک شود؛ هر 9 فیلد صفر؛ FAULT_ADC زنده بماند بدون latch کاذب</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t>بدون fault کاذب</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" s="23" t="n"/>
+      <c r="L10" s="27" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="M10" s="23" t="n"/>
+      <c r="N10" s="23" t="n"/>
+      <c r="O10" s="25" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="P10" s="25" t="n"/>
+      <c r="Q10" s="26" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="Q11" s="28">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="28">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="28">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="28">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="28">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="28">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="28">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="28">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="28">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="28">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="28">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="28">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="28">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="28">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="28">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="28">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="28">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="Q28" s="28">
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="Q29" s="28">
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="Q30" s="28">
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="Q31" s="28">
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="Q32" s="28">
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="Q33" s="28">
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="Q34" s="28">
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="Q35" s="28">
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="Q36" s="28">
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="Q37" s="28">
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="Q38" s="28">
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="Q39" s="28">
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="Q40" s="28">
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="Q41" s="28">
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="Q42" s="28">
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="Q43" s="28">
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="Q44" s="28">
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="Q45" s="28">
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="Q46" s="28">
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="Q47" s="28">
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="Q48" s="28">
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="Q49" s="28">
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="Q50" s="28">
+        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:Q10"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="L5:L9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>='فهرست‌ها'!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="C5:C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
+    <dataValidation sqref="L5:L90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1196,116 +1676,121 @@
     <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Protection</t>
         </is>
       </c>
-    </row>
+      <c r="B1" s="39" t="n"/>
+      <c r="C1" s="39" t="n"/>
+      <c r="D1" s="39" t="n"/>
+      <c r="E1" s="40" t="n"/>
+    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>MODULE_PROTECTION=0</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="30" t="inlineStr">
         <is>
           <t>خاموش؛ اسکلت</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="43" t="inlineStr">
         <is>
           <t>modules_enable.h</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t>فعال‌سازی با دستور کاربر</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>FAULT_ADC</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Set در نامعتبر / Clear در معتبر</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t>لحظه‌ای، بدون latch</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="43" t="inlineStr">
         <is>
           <t>protection.c (اصلاح 2026-09-22)</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="30" t="inlineStr">
         <is>
           <t>قبلاً latch ابدی بود</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>مالکیت بیت‌ها</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>این ماژول فقط FAULT_ADC</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t>BAT_LOST مالک Fault</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="43" t="inlineStr">
         <is>
           <t>fault.h / app_types.h</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1315,6 +1800,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1322,6 +1812,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1344,81 +1835,93 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Protection</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
+      <c r="B2" s="39" t="n"/>
+      <c r="C2" s="39" t="n"/>
+      <c r="D2" s="39" t="n"/>
+      <c r="E2" s="39" t="n"/>
+      <c r="F2" s="39" t="n"/>
+      <c r="G2" s="39" t="n"/>
+      <c r="H2" s="39" t="n"/>
+      <c r="I2" s="39" t="n"/>
+      <c r="J2" s="39" t="n"/>
+      <c r="K2" s="39" t="n"/>
+      <c r="L2" s="39" t="n"/>
+      <c r="M2" s="40" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="29" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="29" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="29" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="29" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="29" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="29" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -1436,6 +1939,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1448,203 +1952,205 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Protection</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Protection — اسکلت حفاظت</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>2026-09-23 (1.0)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>بیلد تستی + پنل ESP</t>
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="29" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="29" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="32" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="32" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="32">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="32">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="32" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="32">
         <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="32" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="32" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="32">
         <f>IF(5=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/5)</f>
         <v/>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="32" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="31" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
@@ -1663,6 +2169,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00808080"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1674,105 +2181,113 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="33" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>انجام شد</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="34" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="34" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="34" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="34" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
@@ -1786,7 +2301,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1798,55 +2313,56 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="35" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول نگهبان اعتبار (Protection)</t>
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="36" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="10" t="inlineStr">
+      <c r="B3" s="37" t="inlineStr">
         <is>
           <t>Protection_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="37" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="36" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="38" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="37" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
@@ -1859,6 +2375,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -9,15 +9,18 @@
   <sheets>
     <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="مراجع سناریو" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ثبت ایراد" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="تأیید نهایی" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="فهرست‌ها" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="ماشین حالت" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'برنامه تست'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'تست‌های برنامه‌نویسی'!$A$4:$Q$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'تست‌های برنامه‌نویسی'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
@@ -28,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -128,6 +131,13 @@
       <name val="Tahoma"/>
       <color rgb="000563C1"/>
       <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="10"/>
       <u val="single"/>
     </font>
   </fonts>
@@ -258,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -368,6 +378,13 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -809,7 +826,7 @@
     <mergeCell ref="A1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId1"/>
+    <hyperlink ref="A9" location="'برنامه تست'!A6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -822,7 +839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q50"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1174,469 +1191,247 @@
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>PR-004</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>عدم تداخل مالکیت</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="inlineStr">
-        <is>
-          <t>متوسط</t>
-        </is>
-      </c>
-      <c r="D8" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="41" t="inlineStr">
-        <is>
-          <t>گام ۱: جدول بیت‌های FAULT_* در app_types.h را جلوی خودت بگذار.
-گام ۲: کد protection.c را خط‌به‌خط با مالکیت بیت‌ها مقایسه کن.
-گام ۳: این ماژول باید فقط FAULT_ADC را ست/پاک کند؛ FAULT_CHARGER_BAT_LOST مال ماژول Fault است و بقیهٔ بیت‌ها هم صاحب خودشان را دارند.
-گام ۴: هیچ تداخلی بین بیت‌ها نباید باشد.</t>
-        </is>
-      </c>
-      <c r="F8" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" s="23" t="inlineStr">
-        <is>
-          <t>این ماژول فقط FAULT_ADC را لمس می‌کند؛ FAULT_CHARGER_BAT_LOST مالک Fault است</t>
-        </is>
-      </c>
-      <c r="I8" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="23" t="inlineStr">
-        <is>
-          <t>بدون تداخل بیت‌ها</t>
-        </is>
-      </c>
-      <c r="K8" s="23" t="inlineStr"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M8" s="23" t="inlineStr"/>
-      <c r="N8" s="23" t="inlineStr"/>
-      <c r="O8" s="25" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P8" s="25" t="inlineStr"/>
-      <c r="Q8" s="26" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="Q8" s="28">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>PR-005</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>فعال‌سازی آینده</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>پایین</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="42" t="inlineStr">
-        <is>
-          <t>گام ۱: کد ماژول را کامل مرور کن (protection.c و هدرش).
-گام ۲: شرایط فعال‌سازی حفاظت کامل (اضافه‌جریان، باتری ضعیف و...) و سیاست هر کدام را روی کاغذ بنویس.
-گام ۳: قبل از اینکه MODULE_PROTECTION=1 شود، سند تصمیم را به تأیید کاربر برسان.
-گام ۴: قبولی یعنی همین سند تصمیم موجود و تأیید شده باشد؛ این ردیف تست برد نیست.</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>شرایط فعال‌سازی و سیاست‌ها قبل از MODULE_PROTECTION=1 مستند و به تأیید کاربر برسد</t>
-        </is>
-      </c>
-      <c r="I9" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="18" t="inlineStr">
-        <is>
-          <t>سند تصمیم موجود</t>
-        </is>
-      </c>
-      <c r="K9" s="18" t="inlineStr"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M9" s="18" t="inlineStr"/>
-      <c r="N9" s="18" t="inlineStr"/>
-      <c r="O9" s="20" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P9" s="20" t="inlineStr"/>
-      <c r="Q9" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="Q9" s="28">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
-        <is>
-          <t>PR-010</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>snapshot zeroing</t>
-        </is>
-      </c>
-      <c r="C10" s="24" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
-        <is>
-          <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
-گام ۲: آن را 2 ثانیه به Protection_Run بده.
-گام ۳: تابع باید فقط valid را چک کند و به فیلدهای صفر دست نزند.
-گام ۴: FAULT_ADC باید به‌صورت زنده (بدون latch) بماند و هیچ fault کاذبی ساخته نشود.</t>
-        </is>
-      </c>
-      <c r="F10" s="25" t="inlineStr">
-        <is>
-          <t>valid=false</t>
-        </is>
-      </c>
-      <c r="G10" s="25" t="inlineStr">
-        <is>
-          <t>2s</t>
-        </is>
-      </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t>فقط valid چک شود؛ هر 9 فیلد صفر؛ FAULT_ADC زنده بماند بدون latch کاذب</t>
-        </is>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t>بدون fault کاذب</t>
-        </is>
-      </c>
-      <c r="K10" s="23" t="n"/>
-      <c r="L10" s="27" t="inlineStr">
-        <is>
-          <t>نیاز به تکرار</t>
-        </is>
-      </c>
-      <c r="M10" s="23" t="n"/>
-      <c r="N10" s="23" t="n"/>
-      <c r="O10" s="25" t="inlineStr">
-        <is>
-          <t>62f3782</t>
-        </is>
-      </c>
-      <c r="P10" s="25" t="n"/>
-      <c r="Q10" s="26" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
+      <c r="Q10" s="28">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="Q11" s="28">
-        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="Q12" s="28">
-        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="Q13" s="28">
-        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="Q14" s="28">
-        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="Q15" s="28">
-        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="Q16" s="28">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="Q17" s="28">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="Q18" s="28">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="Q19" s="28">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="Q20" s="28">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="Q21" s="28">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="Q22" s="28">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="Q23" s="28">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="Q24" s="28">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="28">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="28">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="28">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="28">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="28">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="28">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="28">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="28">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="28">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="28">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="28">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="28">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="28">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="28">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="28">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="28">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="28">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="28">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="28">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="28">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="28">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="28">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="Q47" s="28">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="Q48" s="28">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="Q49" s="28">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="Q50" s="28">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:Q10"/>
+  <autoFilter ref="A4:Q47"/>
   <mergeCells count="3">
     <mergeCell ref="A3:Q3"/>
     <mergeCell ref="A2:Q2"/>
@@ -1650,16 +1445,497 @@
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId2"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="44" t="inlineStr">
+        <is>
+          <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="B2" s="45" t="inlineStr">
+        <is>
+          <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="54" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>PR-004</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>عدم تداخل مالکیت</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>متوسط</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="41" t="inlineStr">
+        <is>
+          <t>گام ۱: جدول بیت‌های FAULT_* در app_types.h را جلوی خودت بگذار.
+گام ۲: کد protection.c را خط‌به‌خط با مالکیت بیت‌ها مقایسه کن.
+گام ۳: این ماژول باید فقط FAULT_ADC را ست/پاک کند؛ FAULT_CHARGER_BAT_LOST مال ماژول Fault است و بقیهٔ بیت‌ها هم صاحب خودشان را دارند.
+گام ۴: هیچ تداخلی بین بیت‌ها نباید باشد.</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>این ماژول فقط FAULT_ADC را لمس می‌کند؛ FAULT_CHARGER_BAT_LOST مالک Fault است</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>بدون تداخل بیت‌ها</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="n"/>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="23" t="n"/>
+      <c r="N5" s="23" t="n"/>
+      <c r="O5" s="25" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>PR-005</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>فعال‌سازی آینده</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>پایین</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="42" t="inlineStr">
+        <is>
+          <t>گام ۱: کد ماژول را کامل مرور کن (protection.c و هدرش).
+گام ۲: شرایط فعال‌سازی حفاظت کامل (اضافه‌جریان، باتری ضعیف و...) و سیاست هر کدام را روی کاغذ بنویس.
+گام ۳: قبل از اینکه MODULE_PROTECTION=1 شود، سند تصمیم را به تأیید کاربر برسان.
+گام ۴: قبولی یعنی همین سند تصمیم موجود و تأیید شده باشد؛ این ردیف تست برد نیست.</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>شرایط فعال‌سازی و سیاست‌ها قبل از MODULE_PROTECTION=1 مستند و به تأیید کاربر برسد</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>سند تصمیم موجود</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M6" s="18" t="n"/>
+      <c r="N6" s="18" t="n"/>
+      <c r="O6" s="20" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P6" s="20" t="n"/>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="54" customHeight="1">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>PR-010</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>snapshot zeroing</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
+گام ۲: آن را 2 ثانیه به Protection_Run بده.
+گام ۳: تابع باید فقط valid را چک کند و به فیلدهای صفر دست نزند.
+گام ۴: FAULT_ADC باید به‌صورت زنده (بدون latch) بماند و هیچ fault کاذبی ساخته نشود.</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>valid=false</t>
+        </is>
+      </c>
+      <c r="G7" s="25" t="inlineStr">
+        <is>
+          <t>2s</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>فقط valid چک شود؛ هر 9 فیلد صفر؛ FAULT_ADC زنده بماند بدون latch کاذب</t>
+        </is>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="23" t="inlineStr">
+        <is>
+          <t>بدون fault کاذب</t>
+        </is>
+      </c>
+      <c r="K7" s="23" t="n"/>
+      <c r="L7" s="27" t="inlineStr">
+        <is>
+          <t>نیاز به تکرار</t>
+        </is>
+      </c>
+      <c r="M7" s="23" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="25" t="inlineStr">
+        <is>
+          <t>62f3782</t>
+        </is>
+      </c>
+      <c r="P7" s="25" t="n"/>
+      <c r="Q7" s="26" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="Q8" s="28">
+        <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="Q9" s="28">
+        <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="Q10" s="28">
+        <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="Q11" s="28">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="Q12" s="28">
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="Q13" s="28">
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="Q14" s="28">
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="Q15" s="28">
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="Q16" s="28">
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="Q17" s="28">
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="Q18" s="28">
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="Q19" s="28">
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="Q20" s="28">
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="Q21" s="28">
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="Q22" s="28">
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="Q23" s="28">
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="Q24" s="28">
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="Q25" s="28">
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="Q26" s="28">
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="Q27" s="28">
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:Q7"/>
+  <dataValidations count="1">
+    <dataValidation sqref="L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00BF8F00"/>
@@ -1809,7 +2085,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C00000"/>
@@ -1936,7 +2212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00548235"/>
@@ -2166,7 +2442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -2298,7 +2574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="007030A0"/>

--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -15,6 +15,7 @@
     <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$47</definedName>
@@ -826,7 +827,7 @@
     <mergeCell ref="A1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A9" location="'برنامه تست'!A6"/>
+    <hyperlink ref="A9" location="'تست‌های آزمایشگاهی'!A5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -839,7 +840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q47"/>
+  <dimension ref="A1:Q46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -987,39 +988,38 @@
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>MODULE_PROTECTION=0</t>
+          <t>دستگاه در حال کار عادی با باتری و بار واقعی است</t>
         </is>
       </c>
       <c r="E5" s="18" t="inlineStr">
         <is>
-          <t>گام ۱: بیلد معمولی را بگیر که در آن MODULE_PROTECTION=0 است.
-گام ۲: برد را بوت کن و 60 ثانیه شارژ عادی را نگاه کن.
-گام ۳: هیچ خطایی نباید از این ماژول بیاید (Protection_Run اصلاً اجرا نمی‌شود) و رفتار کل سیستم باید مثل وقتی باشد که ماژول اصلاً وجود ندارد؛ مخصوصاً FAULT_ADC نباید القا شود.</t>
+          <t>گام ۱: دستگاه را چند ساعت در کار عادی (شارژ و مصرف) زیر نظر بگیر.
+گام ۲: دنبال قطع حفاظتیِ بی‌دلیل بگرد.</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
         <is>
+          <t>کار عادی چندساعته</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>چند ساعت</t>
+        </is>
+      </c>
+      <c r="H5" s="18" t="inlineStr">
+        <is>
+          <t>هیچ قطع حفاظتیِ اضافه‌ای در کار عادی دیده نمی‌شود؛ محصول با همان حفاظت‌های ماژول‌های فعال کار می‌کند</t>
+        </is>
+      </c>
+      <c r="I5" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
-        <is>
-          <t>60s</t>
-        </is>
-      </c>
-      <c r="H5" s="18" t="inlineStr">
-        <is>
-          <t>Run اجرا نمی‌شود؛ هیچ خطایی از این ماژول نمی‌آید؛ رفتار سیستم مثل نبود ماژول</t>
-        </is>
-      </c>
-      <c r="I5" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J5" s="18" t="inlineStr">
         <is>
-          <t>بدون FAULT_ADC القایی</t>
+          <t>کار تمیز چندساعته = قبول؛ قطع بی‌دلیل = رد</t>
         </is>
       </c>
       <c r="K5" s="18" t="inlineStr"/>
@@ -1045,387 +1045,311 @@
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>PR-002</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t>FAULT_ADC لحظه‌ای</t>
-        </is>
-      </c>
-      <c r="C6" s="24" t="inlineStr">
+          <t>PR-003</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>بوت قبل از warm-up</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
-        <is>
-          <t>بیلد تستی با MODULE_PROTECTION=1</t>
-        </is>
-      </c>
-      <c r="E6" s="23" t="inlineStr">
-        <is>
-          <t>گام ۱: یک بیلد تستی بگیر که در آن MODULE_PROTECTION=1 باشد.
-گام ۲: ADC را موقتاً نامعتبر کن (مثلاً ورودی را در دورهٔ warm-up قطع کن تا snapshot نامعتبر شود).
-گام ۳: بیت FAULT_ADC باید لحظه‌ای ست شود (در پنل/ماسک ببین).
-گام ۴: ADC را معتبر کن و اولین snapshot معتبر را بده (5 ثانیه کافی است): بیت باید خودش پاک شود؛ بیت بعد از معتبر شدن صفر است.</t>
-        </is>
-      </c>
-      <c r="F6" s="25" t="inlineStr">
-        <is>
-          <t>snapshot نامعتبر</t>
-        </is>
-      </c>
-      <c r="G6" s="25" t="inlineStr">
-        <is>
-          <t>5s</t>
-        </is>
-      </c>
-      <c r="H6" s="23" t="inlineStr">
-        <is>
-          <t>Set بیت FAULT_ADC به‌صورت لحظه‌ای؛ با اولین snapshot معتبر خودش پاک می‌شود</t>
-        </is>
-      </c>
-      <c r="I6" s="23" t="inlineStr">
-        <is>
-          <t>لحظه‌ای نه latch</t>
-        </is>
-      </c>
-      <c r="J6" s="23" t="inlineStr">
-        <is>
-          <t>بیت بعد از معتبر شدن صفر</t>
-        </is>
-      </c>
-      <c r="K6" s="23" t="inlineStr"/>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>دستگاه کاملاً خاموش و سرد است؛ بار روی خروجی وصل است</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>گام ۱: دستگاه را روشن کن.
+گام ۲: در همان ثانیه‌های اول بار را نگاه کن.</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>روشن‌کردن سرد با بار</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>یک دقیقه</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>خروجی در لحظه‌های اول بی‌دلیل قطع نمی‌شود؛ دستگاه تمیز بالا می‌آید و بار عادی کار می‌کند</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="inlineStr">
+        <is>
+          <t>بالا آمدن تمیز = قبول؛ قطع‌ووصل اول کار = رد</t>
+        </is>
+      </c>
+      <c r="K6" s="18" t="inlineStr"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="23" t="inlineStr"/>
-      <c r="N6" s="23" t="inlineStr"/>
-      <c r="O6" s="25" t="inlineStr">
+      <c r="M6" s="18" t="inlineStr"/>
+      <c r="N6" s="18" t="inlineStr"/>
+      <c r="O6" s="20" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="25" t="inlineStr"/>
-      <c r="Q6" s="26" t="inlineStr">
+      <c r="P6" s="20" t="inlineStr"/>
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>PR-003</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>بوت قبل از warm-up</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>بالا</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>بیلد تستی با MODULE_PROTECTION=1</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="inlineStr">
-        <is>
-          <t>گام ۱: بیلد تستی با MODULE_PROTECTION=1 را روی برد بزن.
-گام ۲: بوت سرد بگیر (برق را قطع و وصل کن).
-گام ۳: 10 ثانیه اول را نگاه کن: پاس‌های اول حفاظت قبل از warm-up اندازه‌گیری اجرا می‌شوند و FAULT_ADC فقط لحظه‌ای می‌آید.
-گام ۴: سیستم باید خودش به حالت عادی برسد؛ Changeover نباید در APP_STATE_FAULT گیر کند و شارژر نباید برای همیشه safe-idle بماند.</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>10s</t>
-        </is>
-      </c>
-      <c r="H7" s="18" t="inlineStr">
-        <is>
-          <t>FAULT_ADC لحظه‌ای؛ Changeover در APP_STATE_FAULT گیر نمی‌کند و شارژر safe-idle ابدی نمی‌ماند</t>
-        </is>
-      </c>
-      <c r="I7" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="inlineStr">
-        <is>
-          <t>سیستم به حالت عادی می‌رسد</t>
-        </is>
-      </c>
-      <c r="K7" s="18" t="inlineStr"/>
-      <c r="L7" s="21" t="inlineStr">
-        <is>
-          <t>در انتظار</t>
-        </is>
-      </c>
-      <c r="M7" s="18" t="inlineStr"/>
-      <c r="N7" s="18" t="inlineStr"/>
-      <c r="O7" s="20" t="inlineStr">
-        <is>
-          <t>TESTER: fill</t>
-        </is>
-      </c>
-      <c r="P7" s="20" t="inlineStr"/>
-      <c r="Q7" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="Q7" s="28">
+        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
       <c r="Q8" s="28">
-        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
       <c r="Q9" s="28">
-        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
+        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
       <c r="Q10" s="28">
-        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
+        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="Q11" s="28">
-        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
+        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="Q12" s="28">
-        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
+        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="Q13" s="28">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
+        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="Q14" s="28">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
+        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="Q15" s="28">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
+        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="Q16" s="28">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
+        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="Q17" s="28">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
+        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="Q18" s="28">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
+        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="Q19" s="28">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
+        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="Q20" s="28">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
+        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="Q21" s="28">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
+        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="Q22" s="28">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
+        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="Q23" s="28">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
+        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="Q24" s="28">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
+        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="Q25" s="28">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
+        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="Q26" s="28">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
+        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="Q27" s="28">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
+        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="Q28" s="28">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
+        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="Q29" s="28">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
+        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="Q30" s="28">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
+        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="Q31" s="28">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
+        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="Q32" s="28">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
+        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="Q33" s="28">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
+        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="Q34" s="28">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
+        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="Q35" s="28">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
+        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="Q36" s="28">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
+        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="Q37" s="28">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
+        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="Q38" s="28">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
+        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="Q39" s="28">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
+        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="Q40" s="28">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
+        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="Q41" s="28">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
+        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="Q42" s="28">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
+        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="Q43" s="28">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
+        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="Q44" s="28">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
+        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="Q45" s="28">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
+        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="Q46" s="28">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="Q47" s="28">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
@@ -2655,4 +2579,230 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>برنامهٔ تست آزمایشگاهی — ماژول Protection</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>شناسه</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>دسته</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>اولویت</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>پیش‌شرط</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>روش اجرای دقیق</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>ورودی‌ها / شرایط</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>مدت مشاهده</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="inlineStr">
+        <is>
+          <t>رفتار مورد انتظار</t>
+        </is>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت حفظ / latch</t>
+        </is>
+      </c>
+      <c r="J4" s="14" t="inlineStr">
+        <is>
+          <t>معیار قبولی</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="inlineStr">
+        <is>
+          <t>نتیجهٔ واقعی / اندازه‌گیری</t>
+        </is>
+      </c>
+      <c r="L4" s="14" t="inlineStr">
+        <is>
+          <t>وضعیت</t>
+        </is>
+      </c>
+      <c r="M4" s="14" t="inlineStr">
+        <is>
+          <t>شرح ایراد / تفاوت</t>
+        </is>
+      </c>
+      <c r="N4" s="14" t="inlineStr">
+        <is>
+          <t>مدرک تست / scope</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>commit</t>
+        </is>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t>نام تست‌کننده</t>
+        </is>
+      </c>
+      <c r="Q4" s="14" t="inlineStr">
+        <is>
+          <t>تاریخ</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40.5" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>PR-002</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>FAULT_ADC لحظه‌ای</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>بالا</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>بیلد تستی با MODULE_PROTECTION=1</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>گام ۱: یک بیلد تستی بگیر که در آن MODULE_PROTECTION=1 باشد.
+گام ۲: ADC را موقتاً نامعتبر کن (مثلاً ورودی را در دورهٔ warm-up قطع کن تا snapshot نامعتبر شود).
+گام ۳: بیت FAULT_ADC باید لحظه‌ای ست شود (در پنل/ماسک ببین).
+گام ۴: ADC را معتبر کن و اولین snapshot معتبر را بده (5 ثانیه کافی است): بیت باید خودش پاک شود؛ بیت بعد از معتبر شدن صفر است.</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>snapshot نامعتبر</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>5s</t>
+        </is>
+      </c>
+      <c r="H5" s="23" t="inlineStr">
+        <is>
+          <t>Set بیت FAULT_ADC به‌صورت لحظه‌ای؛ با اولین snapshot معتبر خودش پاک می‌شود</t>
+        </is>
+      </c>
+      <c r="I5" s="23" t="inlineStr">
+        <is>
+          <t>لحظه‌ای نه latch</t>
+        </is>
+      </c>
+      <c r="J5" s="23" t="inlineStr">
+        <is>
+          <t>بیت بعد از معتبر شدن صفر</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="n"/>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t>در انتظار</t>
+        </is>
+      </c>
+      <c r="M5" s="23" t="n"/>
+      <c r="N5" s="23" t="n"/>
+      <c r="O5" s="25" t="inlineStr">
+        <is>
+          <t>TESTER: fill</t>
+        </is>
+      </c>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="26">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="54" customHeight="1"/>
+    <row r="7" ht="54" customHeight="1"/>
+    <row r="8" ht="54" customHeight="1"/>
+    <row r="9" ht="54" customHeight="1"/>
+    <row r="10" ht="54" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,6 +140,51 @@
       <color rgb="000563C1"/>
       <sz val="10"/>
       <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color rgb="000563C1"/>
+      <sz val="8"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="9">
@@ -269,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -387,6 +432,81 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -760,55 +880,55 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Protection</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>Protection | اسکلت حفاظت (MODULE_PROTECTION=0) — FAULT_ADC به‌صورت وضعیت لحظه‌ای</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="48" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>ماژول در build فعال نیست؛ تنها رفتار تعریف‌شده: Set بیت FAULT_ADC با snapshot نامعتبر و Clear آن با snapshot معتبر (لحظه‌ای، نه latch).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>ایراد قدیمی «latch ابدی FAULT_ADC در بوت» در ممیزی ۲۰۲۶-۰۹-۲۲ اصلاح شد؛ Changeover دیگر در بوت در FAULT گیر نمی‌کند.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>فعال‌سازی آیندهٔ حفاظت کامل (اضافه‌جریان/باتری ضعیف) با MODULE_PROTECTION=1 و به دستور کاربر.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="48" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="50" t="inlineStr">
         <is>
           <t>یادداشت: تست‌های PR-002/PR-003 به بیلد تستی با MODULE_PROTECTION=1 نیاز دارند؛ در بیلد فعلی فقط PR-001 قابل اجراست.</t>
         </is>
@@ -863,493 +983,1181 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Protection</t>
         </is>
       </c>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
+      <c r="D1" s="52" t="n"/>
+      <c r="E1" s="52" t="n"/>
+      <c r="F1" s="52" t="n"/>
+      <c r="G1" s="52" t="n"/>
+      <c r="H1" s="52" t="n"/>
+      <c r="I1" s="52" t="n"/>
+      <c r="J1" s="52" t="n"/>
+      <c r="K1" s="52" t="n"/>
+      <c r="L1" s="52" t="n"/>
+      <c r="M1" s="52" t="n"/>
+      <c r="N1" s="52" t="n"/>
+      <c r="O1" s="52" t="n"/>
+      <c r="P1" s="52" t="n"/>
+      <c r="Q1" s="52" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="B2" s="52" t="n"/>
+      <c r="C2" s="52" t="n"/>
+      <c r="D2" s="52" t="n"/>
+      <c r="E2" s="52" t="n"/>
+      <c r="F2" s="52" t="n"/>
+      <c r="G2" s="52" t="n"/>
+      <c r="H2" s="52" t="n"/>
+      <c r="I2" s="52" t="n"/>
+      <c r="J2" s="52" t="n"/>
+      <c r="K2" s="52" t="n"/>
+      <c r="L2" s="52" t="n"/>
+      <c r="M2" s="52" t="n"/>
+      <c r="N2" s="52" t="n"/>
+      <c r="O2" s="52" t="n"/>
+      <c r="P2" s="52" t="n"/>
+      <c r="Q2" s="52" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="B3" s="52" t="n"/>
+      <c r="C3" s="52" t="n"/>
+      <c r="D3" s="52" t="n"/>
+      <c r="E3" s="52" t="n"/>
+      <c r="F3" s="52" t="n"/>
+      <c r="G3" s="52" t="n"/>
+      <c r="H3" s="52" t="n"/>
+      <c r="I3" s="52" t="n"/>
+      <c r="J3" s="52" t="n"/>
+      <c r="K3" s="52" t="n"/>
+      <c r="L3" s="52" t="n"/>
+      <c r="M3" s="52" t="n"/>
+      <c r="N3" s="52" t="n"/>
+      <c r="O3" s="52" t="n"/>
+      <c r="P3" s="52" t="n"/>
+      <c r="Q3" s="52" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="49" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="49" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="49" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="49" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="49" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="49" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="49" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="49" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="49" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.5" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>PR-001</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="54" t="inlineStr">
         <is>
           <t>ماژول خاموش</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="55" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="54" t="inlineStr">
         <is>
           <t>دستگاه در حال کار عادی با باتری و بار واقعی است</t>
         </is>
       </c>
-      <c r="E5" s="18" t="inlineStr">
+      <c r="E5" s="54" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را چند ساعت در کار عادی (شارژ و مصرف) زیر نظر بگیر.
 گام ۲: دنبال قطع حفاظتیِ بی‌دلیل بگرد.</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="56" t="inlineStr">
         <is>
           <t>کار عادی چندساعته</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="56" t="inlineStr">
         <is>
           <t>چند ساعت</t>
         </is>
       </c>
-      <c r="H5" s="18" t="inlineStr">
+      <c r="H5" s="54" t="inlineStr">
         <is>
           <t>هیچ قطع حفاظتیِ اضافه‌ای در کار عادی دیده نمی‌شود؛ محصول با همان حفاظت‌های ماژول‌های فعال کار می‌کند</t>
         </is>
       </c>
-      <c r="I5" s="18" t="inlineStr">
+      <c r="I5" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="J5" s="54" t="inlineStr">
         <is>
           <t>کار تمیز چندساعته = قبول؛ قطع بی‌دلیل = رد</t>
         </is>
       </c>
-      <c r="K5" s="18" t="inlineStr"/>
-      <c r="L5" s="21" t="inlineStr">
+      <c r="K5" s="54" t="inlineStr"/>
+      <c r="L5" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="18" t="inlineStr"/>
-      <c r="N5" s="18" t="inlineStr"/>
-      <c r="O5" s="20" t="inlineStr">
+      <c r="M5" s="54" t="inlineStr"/>
+      <c r="N5" s="54" t="inlineStr"/>
+      <c r="O5" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="20" t="inlineStr"/>
-      <c r="Q5" s="22" t="inlineStr">
+      <c r="P5" s="56" t="inlineStr"/>
+      <c r="Q5" s="58" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>PR-003</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="54" t="inlineStr">
         <is>
           <t>بوت قبل از warm-up</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="55" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="54" t="inlineStr">
         <is>
           <t>دستگاه کاملاً خاموش و سرد است؛ بار روی خروجی وصل است</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="54" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را روشن کن.
 گام ۲: در همان ثانیه‌های اول بار را نگاه کن.</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="56" t="inlineStr">
         <is>
           <t>روشن‌کردن سرد با بار</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="56" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="54" t="inlineStr">
         <is>
           <t>خروجی در لحظه‌های اول بی‌دلیل قطع نمی‌شود؛ دستگاه تمیز بالا می‌آید و بار عادی کار می‌کند</t>
         </is>
       </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="I6" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="J6" s="54" t="inlineStr">
         <is>
           <t>بالا آمدن تمیز = قبول؛ قطع‌ووصل اول کار = رد</t>
         </is>
       </c>
-      <c r="K6" s="18" t="inlineStr"/>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="K6" s="54" t="inlineStr"/>
+      <c r="L6" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="18" t="inlineStr"/>
-      <c r="N6" s="18" t="inlineStr"/>
-      <c r="O6" s="20" t="inlineStr">
+      <c r="M6" s="54" t="inlineStr"/>
+      <c r="N6" s="54" t="inlineStr"/>
+      <c r="O6" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="20" t="inlineStr"/>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="P6" s="56" t="inlineStr"/>
+      <c r="Q6" s="58" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="Q7" s="28">
+      <c r="A7" s="52" t="n"/>
+      <c r="B7" s="52" t="n"/>
+      <c r="C7" s="52" t="n"/>
+      <c r="D7" s="52" t="n"/>
+      <c r="E7" s="52" t="n"/>
+      <c r="F7" s="52" t="n"/>
+      <c r="G7" s="52" t="n"/>
+      <c r="H7" s="52" t="n"/>
+      <c r="I7" s="52" t="n"/>
+      <c r="J7" s="52" t="n"/>
+      <c r="K7" s="52" t="n"/>
+      <c r="L7" s="52" t="n"/>
+      <c r="M7" s="52" t="n"/>
+      <c r="N7" s="52" t="n"/>
+      <c r="O7" s="52" t="n"/>
+      <c r="P7" s="52" t="n"/>
+      <c r="Q7" s="59">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="54" customHeight="1">
-      <c r="Q8" s="28">
+      <c r="A8" s="52" t="n"/>
+      <c r="B8" s="52" t="n"/>
+      <c r="C8" s="52" t="n"/>
+      <c r="D8" s="52" t="n"/>
+      <c r="E8" s="52" t="n"/>
+      <c r="F8" s="52" t="n"/>
+      <c r="G8" s="52" t="n"/>
+      <c r="H8" s="52" t="n"/>
+      <c r="I8" s="52" t="n"/>
+      <c r="J8" s="52" t="n"/>
+      <c r="K8" s="52" t="n"/>
+      <c r="L8" s="52" t="n"/>
+      <c r="M8" s="52" t="n"/>
+      <c r="N8" s="52" t="n"/>
+      <c r="O8" s="52" t="n"/>
+      <c r="P8" s="52" t="n"/>
+      <c r="Q8" s="59">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="Q9" s="28">
+      <c r="A9" s="52" t="n"/>
+      <c r="B9" s="52" t="n"/>
+      <c r="C9" s="52" t="n"/>
+      <c r="D9" s="52" t="n"/>
+      <c r="E9" s="52" t="n"/>
+      <c r="F9" s="52" t="n"/>
+      <c r="G9" s="52" t="n"/>
+      <c r="H9" s="52" t="n"/>
+      <c r="I9" s="52" t="n"/>
+      <c r="J9" s="52" t="n"/>
+      <c r="K9" s="52" t="n"/>
+      <c r="L9" s="52" t="n"/>
+      <c r="M9" s="52" t="n"/>
+      <c r="N9" s="52" t="n"/>
+      <c r="O9" s="52" t="n"/>
+      <c r="P9" s="52" t="n"/>
+      <c r="Q9" s="59">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="54" customHeight="1">
-      <c r="Q10" s="28">
+      <c r="A10" s="52" t="n"/>
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="52" t="n"/>
+      <c r="D10" s="52" t="n"/>
+      <c r="E10" s="52" t="n"/>
+      <c r="F10" s="52" t="n"/>
+      <c r="G10" s="52" t="n"/>
+      <c r="H10" s="52" t="n"/>
+      <c r="I10" s="52" t="n"/>
+      <c r="J10" s="52" t="n"/>
+      <c r="K10" s="52" t="n"/>
+      <c r="L10" s="52" t="n"/>
+      <c r="M10" s="52" t="n"/>
+      <c r="N10" s="52" t="n"/>
+      <c r="O10" s="52" t="n"/>
+      <c r="P10" s="52" t="n"/>
+      <c r="Q10" s="59">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="28">
+      <c r="A11" s="52" t="n"/>
+      <c r="B11" s="52" t="n"/>
+      <c r="C11" s="52" t="n"/>
+      <c r="D11" s="52" t="n"/>
+      <c r="E11" s="52" t="n"/>
+      <c r="F11" s="52" t="n"/>
+      <c r="G11" s="52" t="n"/>
+      <c r="H11" s="52" t="n"/>
+      <c r="I11" s="52" t="n"/>
+      <c r="J11" s="52" t="n"/>
+      <c r="K11" s="52" t="n"/>
+      <c r="L11" s="52" t="n"/>
+      <c r="M11" s="52" t="n"/>
+      <c r="N11" s="52" t="n"/>
+      <c r="O11" s="52" t="n"/>
+      <c r="P11" s="52" t="n"/>
+      <c r="Q11" s="59">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="28">
+      <c r="A12" s="52" t="n"/>
+      <c r="B12" s="52" t="n"/>
+      <c r="C12" s="52" t="n"/>
+      <c r="D12" s="52" t="n"/>
+      <c r="E12" s="52" t="n"/>
+      <c r="F12" s="52" t="n"/>
+      <c r="G12" s="52" t="n"/>
+      <c r="H12" s="52" t="n"/>
+      <c r="I12" s="52" t="n"/>
+      <c r="J12" s="52" t="n"/>
+      <c r="K12" s="52" t="n"/>
+      <c r="L12" s="52" t="n"/>
+      <c r="M12" s="52" t="n"/>
+      <c r="N12" s="52" t="n"/>
+      <c r="O12" s="52" t="n"/>
+      <c r="P12" s="52" t="n"/>
+      <c r="Q12" s="59">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="28">
+      <c r="A13" s="52" t="n"/>
+      <c r="B13" s="52" t="n"/>
+      <c r="C13" s="52" t="n"/>
+      <c r="D13" s="52" t="n"/>
+      <c r="E13" s="52" t="n"/>
+      <c r="F13" s="52" t="n"/>
+      <c r="G13" s="52" t="n"/>
+      <c r="H13" s="52" t="n"/>
+      <c r="I13" s="52" t="n"/>
+      <c r="J13" s="52" t="n"/>
+      <c r="K13" s="52" t="n"/>
+      <c r="L13" s="52" t="n"/>
+      <c r="M13" s="52" t="n"/>
+      <c r="N13" s="52" t="n"/>
+      <c r="O13" s="52" t="n"/>
+      <c r="P13" s="52" t="n"/>
+      <c r="Q13" s="59">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="28">
+      <c r="A14" s="52" t="n"/>
+      <c r="B14" s="52" t="n"/>
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="52" t="n"/>
+      <c r="E14" s="52" t="n"/>
+      <c r="F14" s="52" t="n"/>
+      <c r="G14" s="52" t="n"/>
+      <c r="H14" s="52" t="n"/>
+      <c r="I14" s="52" t="n"/>
+      <c r="J14" s="52" t="n"/>
+      <c r="K14" s="52" t="n"/>
+      <c r="L14" s="52" t="n"/>
+      <c r="M14" s="52" t="n"/>
+      <c r="N14" s="52" t="n"/>
+      <c r="O14" s="52" t="n"/>
+      <c r="P14" s="52" t="n"/>
+      <c r="Q14" s="59">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="28">
+      <c r="A15" s="52" t="n"/>
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="52" t="n"/>
+      <c r="D15" s="52" t="n"/>
+      <c r="E15" s="52" t="n"/>
+      <c r="F15" s="52" t="n"/>
+      <c r="G15" s="52" t="n"/>
+      <c r="H15" s="52" t="n"/>
+      <c r="I15" s="52" t="n"/>
+      <c r="J15" s="52" t="n"/>
+      <c r="K15" s="52" t="n"/>
+      <c r="L15" s="52" t="n"/>
+      <c r="M15" s="52" t="n"/>
+      <c r="N15" s="52" t="n"/>
+      <c r="O15" s="52" t="n"/>
+      <c r="P15" s="52" t="n"/>
+      <c r="Q15" s="59">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="28">
+      <c r="A16" s="52" t="n"/>
+      <c r="B16" s="52" t="n"/>
+      <c r="C16" s="52" t="n"/>
+      <c r="D16" s="52" t="n"/>
+      <c r="E16" s="52" t="n"/>
+      <c r="F16" s="52" t="n"/>
+      <c r="G16" s="52" t="n"/>
+      <c r="H16" s="52" t="n"/>
+      <c r="I16" s="52" t="n"/>
+      <c r="J16" s="52" t="n"/>
+      <c r="K16" s="52" t="n"/>
+      <c r="L16" s="52" t="n"/>
+      <c r="M16" s="52" t="n"/>
+      <c r="N16" s="52" t="n"/>
+      <c r="O16" s="52" t="n"/>
+      <c r="P16" s="52" t="n"/>
+      <c r="Q16" s="59">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="28">
+      <c r="A17" s="52" t="n"/>
+      <c r="B17" s="52" t="n"/>
+      <c r="C17" s="52" t="n"/>
+      <c r="D17" s="52" t="n"/>
+      <c r="E17" s="52" t="n"/>
+      <c r="F17" s="52" t="n"/>
+      <c r="G17" s="52" t="n"/>
+      <c r="H17" s="52" t="n"/>
+      <c r="I17" s="52" t="n"/>
+      <c r="J17" s="52" t="n"/>
+      <c r="K17" s="52" t="n"/>
+      <c r="L17" s="52" t="n"/>
+      <c r="M17" s="52" t="n"/>
+      <c r="N17" s="52" t="n"/>
+      <c r="O17" s="52" t="n"/>
+      <c r="P17" s="52" t="n"/>
+      <c r="Q17" s="59">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="28">
+      <c r="A18" s="52" t="n"/>
+      <c r="B18" s="52" t="n"/>
+      <c r="C18" s="52" t="n"/>
+      <c r="D18" s="52" t="n"/>
+      <c r="E18" s="52" t="n"/>
+      <c r="F18" s="52" t="n"/>
+      <c r="G18" s="52" t="n"/>
+      <c r="H18" s="52" t="n"/>
+      <c r="I18" s="52" t="n"/>
+      <c r="J18" s="52" t="n"/>
+      <c r="K18" s="52" t="n"/>
+      <c r="L18" s="52" t="n"/>
+      <c r="M18" s="52" t="n"/>
+      <c r="N18" s="52" t="n"/>
+      <c r="O18" s="52" t="n"/>
+      <c r="P18" s="52" t="n"/>
+      <c r="Q18" s="59">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="28">
+      <c r="A19" s="52" t="n"/>
+      <c r="B19" s="52" t="n"/>
+      <c r="C19" s="52" t="n"/>
+      <c r="D19" s="52" t="n"/>
+      <c r="E19" s="52" t="n"/>
+      <c r="F19" s="52" t="n"/>
+      <c r="G19" s="52" t="n"/>
+      <c r="H19" s="52" t="n"/>
+      <c r="I19" s="52" t="n"/>
+      <c r="J19" s="52" t="n"/>
+      <c r="K19" s="52" t="n"/>
+      <c r="L19" s="52" t="n"/>
+      <c r="M19" s="52" t="n"/>
+      <c r="N19" s="52" t="n"/>
+      <c r="O19" s="52" t="n"/>
+      <c r="P19" s="52" t="n"/>
+      <c r="Q19" s="59">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="28">
+      <c r="A20" s="52" t="n"/>
+      <c r="B20" s="52" t="n"/>
+      <c r="C20" s="52" t="n"/>
+      <c r="D20" s="52" t="n"/>
+      <c r="E20" s="52" t="n"/>
+      <c r="F20" s="52" t="n"/>
+      <c r="G20" s="52" t="n"/>
+      <c r="H20" s="52" t="n"/>
+      <c r="I20" s="52" t="n"/>
+      <c r="J20" s="52" t="n"/>
+      <c r="K20" s="52" t="n"/>
+      <c r="L20" s="52" t="n"/>
+      <c r="M20" s="52" t="n"/>
+      <c r="N20" s="52" t="n"/>
+      <c r="O20" s="52" t="n"/>
+      <c r="P20" s="52" t="n"/>
+      <c r="Q20" s="59">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="28">
+      <c r="A21" s="52" t="n"/>
+      <c r="B21" s="52" t="n"/>
+      <c r="C21" s="52" t="n"/>
+      <c r="D21" s="52" t="n"/>
+      <c r="E21" s="52" t="n"/>
+      <c r="F21" s="52" t="n"/>
+      <c r="G21" s="52" t="n"/>
+      <c r="H21" s="52" t="n"/>
+      <c r="I21" s="52" t="n"/>
+      <c r="J21" s="52" t="n"/>
+      <c r="K21" s="52" t="n"/>
+      <c r="L21" s="52" t="n"/>
+      <c r="M21" s="52" t="n"/>
+      <c r="N21" s="52" t="n"/>
+      <c r="O21" s="52" t="n"/>
+      <c r="P21" s="52" t="n"/>
+      <c r="Q21" s="59">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="28">
+      <c r="A22" s="52" t="n"/>
+      <c r="B22" s="52" t="n"/>
+      <c r="C22" s="52" t="n"/>
+      <c r="D22" s="52" t="n"/>
+      <c r="E22" s="52" t="n"/>
+      <c r="F22" s="52" t="n"/>
+      <c r="G22" s="52" t="n"/>
+      <c r="H22" s="52" t="n"/>
+      <c r="I22" s="52" t="n"/>
+      <c r="J22" s="52" t="n"/>
+      <c r="K22" s="52" t="n"/>
+      <c r="L22" s="52" t="n"/>
+      <c r="M22" s="52" t="n"/>
+      <c r="N22" s="52" t="n"/>
+      <c r="O22" s="52" t="n"/>
+      <c r="P22" s="52" t="n"/>
+      <c r="Q22" s="59">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="28">
+      <c r="A23" s="52" t="n"/>
+      <c r="B23" s="52" t="n"/>
+      <c r="C23" s="52" t="n"/>
+      <c r="D23" s="52" t="n"/>
+      <c r="E23" s="52" t="n"/>
+      <c r="F23" s="52" t="n"/>
+      <c r="G23" s="52" t="n"/>
+      <c r="H23" s="52" t="n"/>
+      <c r="I23" s="52" t="n"/>
+      <c r="J23" s="52" t="n"/>
+      <c r="K23" s="52" t="n"/>
+      <c r="L23" s="52" t="n"/>
+      <c r="M23" s="52" t="n"/>
+      <c r="N23" s="52" t="n"/>
+      <c r="O23" s="52" t="n"/>
+      <c r="P23" s="52" t="n"/>
+      <c r="Q23" s="59">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="28">
+      <c r="A24" s="52" t="n"/>
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="52" t="n"/>
+      <c r="D24" s="52" t="n"/>
+      <c r="E24" s="52" t="n"/>
+      <c r="F24" s="52" t="n"/>
+      <c r="G24" s="52" t="n"/>
+      <c r="H24" s="52" t="n"/>
+      <c r="I24" s="52" t="n"/>
+      <c r="J24" s="52" t="n"/>
+      <c r="K24" s="52" t="n"/>
+      <c r="L24" s="52" t="n"/>
+      <c r="M24" s="52" t="n"/>
+      <c r="N24" s="52" t="n"/>
+      <c r="O24" s="52" t="n"/>
+      <c r="P24" s="52" t="n"/>
+      <c r="Q24" s="59">
         <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="28">
+      <c r="A25" s="52" t="n"/>
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="52" t="n"/>
+      <c r="F25" s="52" t="n"/>
+      <c r="G25" s="52" t="n"/>
+      <c r="H25" s="52" t="n"/>
+      <c r="I25" s="52" t="n"/>
+      <c r="J25" s="52" t="n"/>
+      <c r="K25" s="52" t="n"/>
+      <c r="L25" s="52" t="n"/>
+      <c r="M25" s="52" t="n"/>
+      <c r="N25" s="52" t="n"/>
+      <c r="O25" s="52" t="n"/>
+      <c r="P25" s="52" t="n"/>
+      <c r="Q25" s="59">
         <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="28">
+      <c r="A26" s="52" t="n"/>
+      <c r="B26" s="52" t="n"/>
+      <c r="C26" s="52" t="n"/>
+      <c r="D26" s="52" t="n"/>
+      <c r="E26" s="52" t="n"/>
+      <c r="F26" s="52" t="n"/>
+      <c r="G26" s="52" t="n"/>
+      <c r="H26" s="52" t="n"/>
+      <c r="I26" s="52" t="n"/>
+      <c r="J26" s="52" t="n"/>
+      <c r="K26" s="52" t="n"/>
+      <c r="L26" s="52" t="n"/>
+      <c r="M26" s="52" t="n"/>
+      <c r="N26" s="52" t="n"/>
+      <c r="O26" s="52" t="n"/>
+      <c r="P26" s="52" t="n"/>
+      <c r="Q26" s="59">
         <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="28">
+      <c r="A27" s="52" t="n"/>
+      <c r="B27" s="52" t="n"/>
+      <c r="C27" s="52" t="n"/>
+      <c r="D27" s="52" t="n"/>
+      <c r="E27" s="52" t="n"/>
+      <c r="F27" s="52" t="n"/>
+      <c r="G27" s="52" t="n"/>
+      <c r="H27" s="52" t="n"/>
+      <c r="I27" s="52" t="n"/>
+      <c r="J27" s="52" t="n"/>
+      <c r="K27" s="52" t="n"/>
+      <c r="L27" s="52" t="n"/>
+      <c r="M27" s="52" t="n"/>
+      <c r="N27" s="52" t="n"/>
+      <c r="O27" s="52" t="n"/>
+      <c r="P27" s="52" t="n"/>
+      <c r="Q27" s="59">
         <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="Q28" s="28">
+      <c r="A28" s="52" t="n"/>
+      <c r="B28" s="52" t="n"/>
+      <c r="C28" s="52" t="n"/>
+      <c r="D28" s="52" t="n"/>
+      <c r="E28" s="52" t="n"/>
+      <c r="F28" s="52" t="n"/>
+      <c r="G28" s="52" t="n"/>
+      <c r="H28" s="52" t="n"/>
+      <c r="I28" s="52" t="n"/>
+      <c r="J28" s="52" t="n"/>
+      <c r="K28" s="52" t="n"/>
+      <c r="L28" s="52" t="n"/>
+      <c r="M28" s="52" t="n"/>
+      <c r="N28" s="52" t="n"/>
+      <c r="O28" s="52" t="n"/>
+      <c r="P28" s="52" t="n"/>
+      <c r="Q28" s="59">
         <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="Q29" s="28">
+      <c r="A29" s="52" t="n"/>
+      <c r="B29" s="52" t="n"/>
+      <c r="C29" s="52" t="n"/>
+      <c r="D29" s="52" t="n"/>
+      <c r="E29" s="52" t="n"/>
+      <c r="F29" s="52" t="n"/>
+      <c r="G29" s="52" t="n"/>
+      <c r="H29" s="52" t="n"/>
+      <c r="I29" s="52" t="n"/>
+      <c r="J29" s="52" t="n"/>
+      <c r="K29" s="52" t="n"/>
+      <c r="L29" s="52" t="n"/>
+      <c r="M29" s="52" t="n"/>
+      <c r="N29" s="52" t="n"/>
+      <c r="O29" s="52" t="n"/>
+      <c r="P29" s="52" t="n"/>
+      <c r="Q29" s="59">
         <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="Q30" s="28">
+      <c r="A30" s="52" t="n"/>
+      <c r="B30" s="52" t="n"/>
+      <c r="C30" s="52" t="n"/>
+      <c r="D30" s="52" t="n"/>
+      <c r="E30" s="52" t="n"/>
+      <c r="F30" s="52" t="n"/>
+      <c r="G30" s="52" t="n"/>
+      <c r="H30" s="52" t="n"/>
+      <c r="I30" s="52" t="n"/>
+      <c r="J30" s="52" t="n"/>
+      <c r="K30" s="52" t="n"/>
+      <c r="L30" s="52" t="n"/>
+      <c r="M30" s="52" t="n"/>
+      <c r="N30" s="52" t="n"/>
+      <c r="O30" s="52" t="n"/>
+      <c r="P30" s="52" t="n"/>
+      <c r="Q30" s="59">
         <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="Q31" s="28">
+      <c r="A31" s="52" t="n"/>
+      <c r="B31" s="52" t="n"/>
+      <c r="C31" s="52" t="n"/>
+      <c r="D31" s="52" t="n"/>
+      <c r="E31" s="52" t="n"/>
+      <c r="F31" s="52" t="n"/>
+      <c r="G31" s="52" t="n"/>
+      <c r="H31" s="52" t="n"/>
+      <c r="I31" s="52" t="n"/>
+      <c r="J31" s="52" t="n"/>
+      <c r="K31" s="52" t="n"/>
+      <c r="L31" s="52" t="n"/>
+      <c r="M31" s="52" t="n"/>
+      <c r="N31" s="52" t="n"/>
+      <c r="O31" s="52" t="n"/>
+      <c r="P31" s="52" t="n"/>
+      <c r="Q31" s="59">
         <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="Q32" s="28">
+      <c r="A32" s="52" t="n"/>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+      <c r="E32" s="52" t="n"/>
+      <c r="F32" s="52" t="n"/>
+      <c r="G32" s="52" t="n"/>
+      <c r="H32" s="52" t="n"/>
+      <c r="I32" s="52" t="n"/>
+      <c r="J32" s="52" t="n"/>
+      <c r="K32" s="52" t="n"/>
+      <c r="L32" s="52" t="n"/>
+      <c r="M32" s="52" t="n"/>
+      <c r="N32" s="52" t="n"/>
+      <c r="O32" s="52" t="n"/>
+      <c r="P32" s="52" t="n"/>
+      <c r="Q32" s="59">
         <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="Q33" s="28">
+      <c r="A33" s="52" t="n"/>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+      <c r="E33" s="52" t="n"/>
+      <c r="F33" s="52" t="n"/>
+      <c r="G33" s="52" t="n"/>
+      <c r="H33" s="52" t="n"/>
+      <c r="I33" s="52" t="n"/>
+      <c r="J33" s="52" t="n"/>
+      <c r="K33" s="52" t="n"/>
+      <c r="L33" s="52" t="n"/>
+      <c r="M33" s="52" t="n"/>
+      <c r="N33" s="52" t="n"/>
+      <c r="O33" s="52" t="n"/>
+      <c r="P33" s="52" t="n"/>
+      <c r="Q33" s="59">
         <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="Q34" s="28">
+      <c r="A34" s="52" t="n"/>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+      <c r="E34" s="52" t="n"/>
+      <c r="F34" s="52" t="n"/>
+      <c r="G34" s="52" t="n"/>
+      <c r="H34" s="52" t="n"/>
+      <c r="I34" s="52" t="n"/>
+      <c r="J34" s="52" t="n"/>
+      <c r="K34" s="52" t="n"/>
+      <c r="L34" s="52" t="n"/>
+      <c r="M34" s="52" t="n"/>
+      <c r="N34" s="52" t="n"/>
+      <c r="O34" s="52" t="n"/>
+      <c r="P34" s="52" t="n"/>
+      <c r="Q34" s="59">
         <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="Q35" s="28">
+      <c r="A35" s="52" t="n"/>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+      <c r="E35" s="52" t="n"/>
+      <c r="F35" s="52" t="n"/>
+      <c r="G35" s="52" t="n"/>
+      <c r="H35" s="52" t="n"/>
+      <c r="I35" s="52" t="n"/>
+      <c r="J35" s="52" t="n"/>
+      <c r="K35" s="52" t="n"/>
+      <c r="L35" s="52" t="n"/>
+      <c r="M35" s="52" t="n"/>
+      <c r="N35" s="52" t="n"/>
+      <c r="O35" s="52" t="n"/>
+      <c r="P35" s="52" t="n"/>
+      <c r="Q35" s="59">
         <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="Q36" s="28">
+      <c r="A36" s="52" t="n"/>
+      <c r="B36" s="52" t="n"/>
+      <c r="C36" s="52" t="n"/>
+      <c r="D36" s="52" t="n"/>
+      <c r="E36" s="52" t="n"/>
+      <c r="F36" s="52" t="n"/>
+      <c r="G36" s="52" t="n"/>
+      <c r="H36" s="52" t="n"/>
+      <c r="I36" s="52" t="n"/>
+      <c r="J36" s="52" t="n"/>
+      <c r="K36" s="52" t="n"/>
+      <c r="L36" s="52" t="n"/>
+      <c r="M36" s="52" t="n"/>
+      <c r="N36" s="52" t="n"/>
+      <c r="O36" s="52" t="n"/>
+      <c r="P36" s="52" t="n"/>
+      <c r="Q36" s="59">
         <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="Q37" s="28">
+      <c r="A37" s="52" t="n"/>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+      <c r="E37" s="52" t="n"/>
+      <c r="F37" s="52" t="n"/>
+      <c r="G37" s="52" t="n"/>
+      <c r="H37" s="52" t="n"/>
+      <c r="I37" s="52" t="n"/>
+      <c r="J37" s="52" t="n"/>
+      <c r="K37" s="52" t="n"/>
+      <c r="L37" s="52" t="n"/>
+      <c r="M37" s="52" t="n"/>
+      <c r="N37" s="52" t="n"/>
+      <c r="O37" s="52" t="n"/>
+      <c r="P37" s="52" t="n"/>
+      <c r="Q37" s="59">
         <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="Q38" s="28">
+      <c r="A38" s="52" t="n"/>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+      <c r="E38" s="52" t="n"/>
+      <c r="F38" s="52" t="n"/>
+      <c r="G38" s="52" t="n"/>
+      <c r="H38" s="52" t="n"/>
+      <c r="I38" s="52" t="n"/>
+      <c r="J38" s="52" t="n"/>
+      <c r="K38" s="52" t="n"/>
+      <c r="L38" s="52" t="n"/>
+      <c r="M38" s="52" t="n"/>
+      <c r="N38" s="52" t="n"/>
+      <c r="O38" s="52" t="n"/>
+      <c r="P38" s="52" t="n"/>
+      <c r="Q38" s="59">
         <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="Q39" s="28">
+      <c r="A39" s="52" t="n"/>
+      <c r="B39" s="52" t="n"/>
+      <c r="C39" s="52" t="n"/>
+      <c r="D39" s="52" t="n"/>
+      <c r="E39" s="52" t="n"/>
+      <c r="F39" s="52" t="n"/>
+      <c r="G39" s="52" t="n"/>
+      <c r="H39" s="52" t="n"/>
+      <c r="I39" s="52" t="n"/>
+      <c r="J39" s="52" t="n"/>
+      <c r="K39" s="52" t="n"/>
+      <c r="L39" s="52" t="n"/>
+      <c r="M39" s="52" t="n"/>
+      <c r="N39" s="52" t="n"/>
+      <c r="O39" s="52" t="n"/>
+      <c r="P39" s="52" t="n"/>
+      <c r="Q39" s="59">
         <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="Q40" s="28">
+      <c r="A40" s="52" t="n"/>
+      <c r="B40" s="52" t="n"/>
+      <c r="C40" s="52" t="n"/>
+      <c r="D40" s="52" t="n"/>
+      <c r="E40" s="52" t="n"/>
+      <c r="F40" s="52" t="n"/>
+      <c r="G40" s="52" t="n"/>
+      <c r="H40" s="52" t="n"/>
+      <c r="I40" s="52" t="n"/>
+      <c r="J40" s="52" t="n"/>
+      <c r="K40" s="52" t="n"/>
+      <c r="L40" s="52" t="n"/>
+      <c r="M40" s="52" t="n"/>
+      <c r="N40" s="52" t="n"/>
+      <c r="O40" s="52" t="n"/>
+      <c r="P40" s="52" t="n"/>
+      <c r="Q40" s="59">
         <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="Q41" s="28">
+      <c r="A41" s="52" t="n"/>
+      <c r="B41" s="52" t="n"/>
+      <c r="C41" s="52" t="n"/>
+      <c r="D41" s="52" t="n"/>
+      <c r="E41" s="52" t="n"/>
+      <c r="F41" s="52" t="n"/>
+      <c r="G41" s="52" t="n"/>
+      <c r="H41" s="52" t="n"/>
+      <c r="I41" s="52" t="n"/>
+      <c r="J41" s="52" t="n"/>
+      <c r="K41" s="52" t="n"/>
+      <c r="L41" s="52" t="n"/>
+      <c r="M41" s="52" t="n"/>
+      <c r="N41" s="52" t="n"/>
+      <c r="O41" s="52" t="n"/>
+      <c r="P41" s="52" t="n"/>
+      <c r="Q41" s="59">
         <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="Q42" s="28">
+      <c r="A42" s="52" t="n"/>
+      <c r="B42" s="52" t="n"/>
+      <c r="C42" s="52" t="n"/>
+      <c r="D42" s="52" t="n"/>
+      <c r="E42" s="52" t="n"/>
+      <c r="F42" s="52" t="n"/>
+      <c r="G42" s="52" t="n"/>
+      <c r="H42" s="52" t="n"/>
+      <c r="I42" s="52" t="n"/>
+      <c r="J42" s="52" t="n"/>
+      <c r="K42" s="52" t="n"/>
+      <c r="L42" s="52" t="n"/>
+      <c r="M42" s="52" t="n"/>
+      <c r="N42" s="52" t="n"/>
+      <c r="O42" s="52" t="n"/>
+      <c r="P42" s="52" t="n"/>
+      <c r="Q42" s="59">
         <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="Q43" s="28">
+      <c r="A43" s="52" t="n"/>
+      <c r="B43" s="52" t="n"/>
+      <c r="C43" s="52" t="n"/>
+      <c r="D43" s="52" t="n"/>
+      <c r="E43" s="52" t="n"/>
+      <c r="F43" s="52" t="n"/>
+      <c r="G43" s="52" t="n"/>
+      <c r="H43" s="52" t="n"/>
+      <c r="I43" s="52" t="n"/>
+      <c r="J43" s="52" t="n"/>
+      <c r="K43" s="52" t="n"/>
+      <c r="L43" s="52" t="n"/>
+      <c r="M43" s="52" t="n"/>
+      <c r="N43" s="52" t="n"/>
+      <c r="O43" s="52" t="n"/>
+      <c r="P43" s="52" t="n"/>
+      <c r="Q43" s="59">
         <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="Q44" s="28">
+      <c r="A44" s="52" t="n"/>
+      <c r="B44" s="52" t="n"/>
+      <c r="C44" s="52" t="n"/>
+      <c r="D44" s="52" t="n"/>
+      <c r="E44" s="52" t="n"/>
+      <c r="F44" s="52" t="n"/>
+      <c r="G44" s="52" t="n"/>
+      <c r="H44" s="52" t="n"/>
+      <c r="I44" s="52" t="n"/>
+      <c r="J44" s="52" t="n"/>
+      <c r="K44" s="52" t="n"/>
+      <c r="L44" s="52" t="n"/>
+      <c r="M44" s="52" t="n"/>
+      <c r="N44" s="52" t="n"/>
+      <c r="O44" s="52" t="n"/>
+      <c r="P44" s="52" t="n"/>
+      <c r="Q44" s="59">
         <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="Q45" s="28">
+      <c r="A45" s="52" t="n"/>
+      <c r="B45" s="52" t="n"/>
+      <c r="C45" s="52" t="n"/>
+      <c r="D45" s="52" t="n"/>
+      <c r="E45" s="52" t="n"/>
+      <c r="F45" s="52" t="n"/>
+      <c r="G45" s="52" t="n"/>
+      <c r="H45" s="52" t="n"/>
+      <c r="I45" s="52" t="n"/>
+      <c r="J45" s="52" t="n"/>
+      <c r="K45" s="52" t="n"/>
+      <c r="L45" s="52" t="n"/>
+      <c r="M45" s="52" t="n"/>
+      <c r="N45" s="52" t="n"/>
+      <c r="O45" s="52" t="n"/>
+      <c r="P45" s="52" t="n"/>
+      <c r="Q45" s="59">
         <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="Q46" s="28">
+      <c r="A46" s="52" t="n"/>
+      <c r="B46" s="52" t="n"/>
+      <c r="C46" s="52" t="n"/>
+      <c r="D46" s="52" t="n"/>
+      <c r="E46" s="52" t="n"/>
+      <c r="F46" s="52" t="n"/>
+      <c r="G46" s="52" t="n"/>
+      <c r="H46" s="52" t="n"/>
+      <c r="I46" s="52" t="n"/>
+      <c r="J46" s="52" t="n"/>
+      <c r="K46" s="52" t="n"/>
+      <c r="L46" s="52" t="n"/>
+      <c r="M46" s="52" t="n"/>
+      <c r="N46" s="52" t="n"/>
+      <c r="O46" s="52" t="n"/>
+      <c r="P46" s="52" t="n"/>
+      <c r="Q46" s="59">
         <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
         <v/>
       </c>
@@ -1404,129 +2212,179 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="44" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
       </c>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
+      <c r="D1" s="52" t="n"/>
+      <c r="E1" s="52" t="n"/>
+      <c r="F1" s="52" t="n"/>
+      <c r="G1" s="52" t="n"/>
+      <c r="H1" s="52" t="n"/>
+      <c r="I1" s="52" t="n"/>
+      <c r="J1" s="52" t="n"/>
+      <c r="K1" s="52" t="n"/>
+      <c r="L1" s="52" t="n"/>
+      <c r="M1" s="52" t="n"/>
+      <c r="N1" s="52" t="n"/>
+      <c r="O1" s="52" t="n"/>
+      <c r="P1" s="52" t="n"/>
+      <c r="Q1" s="52" t="n"/>
     </row>
     <row r="2" ht="42" customHeight="1">
-      <c r="B2" s="45" t="inlineStr">
+      <c r="A2" s="52" t="n"/>
+      <c r="B2" s="61" t="inlineStr">
         <is>
           <t>این شیت جدا از ولیدیشن عملی برد است: چک‌های کدنویسی، تست‌های هاست، بازبینی کد و تزریق با دیباگر. این‌ها با گیت‌های check_ai_rules و check_firmware_syntax و تست‌های هاست پوشش داده می‌شوند؛ برای بررسی عملکرد روی برد واقعی لازم نیستند.</t>
         </is>
       </c>
-    </row>
-    <row r="3"/>
+      <c r="C2" s="52" t="n"/>
+      <c r="D2" s="52" t="n"/>
+      <c r="E2" s="52" t="n"/>
+      <c r="F2" s="52" t="n"/>
+      <c r="G2" s="52" t="n"/>
+      <c r="H2" s="52" t="n"/>
+      <c r="I2" s="52" t="n"/>
+      <c r="J2" s="52" t="n"/>
+      <c r="K2" s="52" t="n"/>
+      <c r="L2" s="52" t="n"/>
+      <c r="M2" s="52" t="n"/>
+      <c r="N2" s="52" t="n"/>
+      <c r="O2" s="52" t="n"/>
+      <c r="P2" s="52" t="n"/>
+      <c r="Q2" s="52" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="52" t="n"/>
+      <c r="B3" s="52" t="n"/>
+      <c r="C3" s="52" t="n"/>
+      <c r="D3" s="52" t="n"/>
+      <c r="E3" s="52" t="n"/>
+      <c r="F3" s="52" t="n"/>
+      <c r="G3" s="52" t="n"/>
+      <c r="H3" s="52" t="n"/>
+      <c r="I3" s="52" t="n"/>
+      <c r="J3" s="52" t="n"/>
+      <c r="K3" s="52" t="n"/>
+      <c r="L3" s="52" t="n"/>
+      <c r="M3" s="52" t="n"/>
+      <c r="N3" s="52" t="n"/>
+      <c r="O3" s="52" t="n"/>
+      <c r="P3" s="52" t="n"/>
+      <c r="Q3" s="52" t="n"/>
+    </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="49" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="49" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="49" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="49" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="49" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="49" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="49" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="49" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="49" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="54" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>PR-004</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>عدم تداخل مالکیت</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="C5" s="63" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E5" s="41" t="inlineStr">
+      <c r="E5" s="64" t="inlineStr">
         <is>
           <t>گام ۱: جدول بیت‌های FAULT_* در app_types.h را جلوی خودت بگذار.
 گام ۲: کد protection.c را خط‌به‌خط با مالکیت بیت‌ها مقایسه کن.
@@ -1534,73 +2392,73 @@
 گام ۴: هیچ تداخلی بین بیت‌ها نباید باشد.</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="63" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="62" t="inlineStr">
         <is>
           <t>این ماژول فقط FAULT_ADC را لمس می‌کند؛ FAULT_CHARGER_BAT_LOST مالک Fault است</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="I5" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="J5" s="62" t="inlineStr">
         <is>
           <t>بدون تداخل بیت‌ها</t>
         </is>
       </c>
-      <c r="K5" s="23" t="n"/>
-      <c r="L5" s="21" t="inlineStr">
+      <c r="K5" s="62" t="n"/>
+      <c r="L5" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="23" t="n"/>
-      <c r="N5" s="23" t="n"/>
-      <c r="O5" s="25" t="inlineStr">
+      <c r="M5" s="62" t="n"/>
+      <c r="N5" s="62" t="n"/>
+      <c r="O5" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="25" t="n"/>
-      <c r="Q5" s="26" t="inlineStr">
+      <c r="P5" s="63" t="n"/>
+      <c r="Q5" s="65" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="53" t="inlineStr">
         <is>
           <t>PR-005</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="54" t="inlineStr">
         <is>
           <t>فعال‌سازی آینده</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="56" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="42" t="inlineStr">
+      <c r="E6" s="66" t="inlineStr">
         <is>
           <t>گام ۱: کد ماژول را کامل مرور کن (protection.c و هدرش).
 گام ۲: شرایط فعال‌سازی حفاظت کامل (اضافه‌جریان، باتری ضعیف و...) و سیاست هر کدام را روی کاغذ بنویس.
@@ -1608,73 +2466,73 @@
 گام ۴: قبولی یعنی همین سند تصمیم موجود و تأیید شده باشد؛ این ردیف تست برد نیست.</t>
         </is>
       </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F6" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr">
+      <c r="G6" s="56" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="H6" s="54" t="inlineStr">
         <is>
           <t>شرایط فعال‌سازی و سیاست‌ها قبل از MODULE_PROTECTION=1 مستند و به تأیید کاربر برسد</t>
         </is>
       </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="I6" s="54" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="18" t="inlineStr">
+      <c r="J6" s="54" t="inlineStr">
         <is>
           <t>سند تصمیم موجود</t>
         </is>
       </c>
-      <c r="K6" s="18" t="n"/>
-      <c r="L6" s="21" t="inlineStr">
+      <c r="K6" s="54" t="n"/>
+      <c r="L6" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="18" t="n"/>
-      <c r="N6" s="18" t="n"/>
-      <c r="O6" s="20" t="inlineStr">
+      <c r="M6" s="54" t="n"/>
+      <c r="N6" s="54" t="n"/>
+      <c r="O6" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="20" t="n"/>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="P6" s="56" t="n"/>
+      <c r="Q6" s="58" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="53" t="inlineStr">
         <is>
           <t>PR-010</t>
         </is>
       </c>
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="62" t="inlineStr">
         <is>
           <t>snapshot zeroing</t>
         </is>
       </c>
-      <c r="C7" s="24" t="inlineStr">
+      <c r="C7" s="67" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="62" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="62" t="inlineStr">
         <is>
           <t>گام ۱: یک snapshot نامعتبر بساز: valid=false و هر 9 فیلد صفر.
 گام ۲: آن را 2 ثانیه به Protection_Run بده.
@@ -1682,167 +2540,487 @@
 گام ۴: FAULT_ADC باید به‌صورت زنده (بدون latch) بماند و هیچ fault کاذبی ساخته نشود.</t>
         </is>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" s="63" t="inlineStr">
         <is>
           <t>valid=false</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="63" t="inlineStr">
         <is>
           <t>2s</t>
         </is>
       </c>
-      <c r="H7" s="23" t="inlineStr">
+      <c r="H7" s="62" t="inlineStr">
         <is>
           <t>فقط valid چک شود؛ هر 9 فیلد صفر؛ FAULT_ADC زنده بماند بدون latch کاذب</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J7" s="23" t="inlineStr">
+      <c r="J7" s="62" t="inlineStr">
         <is>
           <t>بدون fault کاذب</t>
         </is>
       </c>
-      <c r="K7" s="23" t="n"/>
-      <c r="L7" s="27" t="inlineStr">
+      <c r="K7" s="62" t="n"/>
+      <c r="L7" s="68" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
-      <c r="M7" s="23" t="n"/>
-      <c r="N7" s="23" t="n"/>
-      <c r="O7" s="25" t="inlineStr">
+      <c r="M7" s="62" t="n"/>
+      <c r="N7" s="62" t="n"/>
+      <c r="O7" s="63" t="inlineStr">
         <is>
           <t>62f3782</t>
         </is>
       </c>
-      <c r="P7" s="25" t="n"/>
-      <c r="Q7" s="26" t="inlineStr">
+      <c r="P7" s="63" t="n"/>
+      <c r="Q7" s="65" t="inlineStr">
         <is>
           <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="Q8" s="28">
+      <c r="A8" s="52" t="n"/>
+      <c r="B8" s="52" t="n"/>
+      <c r="C8" s="52" t="n"/>
+      <c r="D8" s="52" t="n"/>
+      <c r="E8" s="52" t="n"/>
+      <c r="F8" s="52" t="n"/>
+      <c r="G8" s="52" t="n"/>
+      <c r="H8" s="52" t="n"/>
+      <c r="I8" s="52" t="n"/>
+      <c r="J8" s="52" t="n"/>
+      <c r="K8" s="52" t="n"/>
+      <c r="L8" s="52" t="n"/>
+      <c r="M8" s="52" t="n"/>
+      <c r="N8" s="52" t="n"/>
+      <c r="O8" s="52" t="n"/>
+      <c r="P8" s="52" t="n"/>
+      <c r="Q8" s="59">
         <f>IF(OR(L8="",L8="در انتظار"),"",IF(Q8="",TODAY(),Q8))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="Q9" s="28">
+      <c r="A9" s="52" t="n"/>
+      <c r="B9" s="52" t="n"/>
+      <c r="C9" s="52" t="n"/>
+      <c r="D9" s="52" t="n"/>
+      <c r="E9" s="52" t="n"/>
+      <c r="F9" s="52" t="n"/>
+      <c r="G9" s="52" t="n"/>
+      <c r="H9" s="52" t="n"/>
+      <c r="I9" s="52" t="n"/>
+      <c r="J9" s="52" t="n"/>
+      <c r="K9" s="52" t="n"/>
+      <c r="L9" s="52" t="n"/>
+      <c r="M9" s="52" t="n"/>
+      <c r="N9" s="52" t="n"/>
+      <c r="O9" s="52" t="n"/>
+      <c r="P9" s="52" t="n"/>
+      <c r="Q9" s="59">
         <f>IF(OR(L9="",L9="در انتظار"),"",IF(Q9="",TODAY(),Q9))</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" s="28">
+      <c r="A10" s="52" t="n"/>
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="52" t="n"/>
+      <c r="D10" s="52" t="n"/>
+      <c r="E10" s="52" t="n"/>
+      <c r="F10" s="52" t="n"/>
+      <c r="G10" s="52" t="n"/>
+      <c r="H10" s="52" t="n"/>
+      <c r="I10" s="52" t="n"/>
+      <c r="J10" s="52" t="n"/>
+      <c r="K10" s="52" t="n"/>
+      <c r="L10" s="52" t="n"/>
+      <c r="M10" s="52" t="n"/>
+      <c r="N10" s="52" t="n"/>
+      <c r="O10" s="52" t="n"/>
+      <c r="P10" s="52" t="n"/>
+      <c r="Q10" s="59">
         <f>IF(OR(L10="",L10="در انتظار"),"",IF(Q10="",TODAY(),Q10))</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="28">
+      <c r="A11" s="52" t="n"/>
+      <c r="B11" s="52" t="n"/>
+      <c r="C11" s="52" t="n"/>
+      <c r="D11" s="52" t="n"/>
+      <c r="E11" s="52" t="n"/>
+      <c r="F11" s="52" t="n"/>
+      <c r="G11" s="52" t="n"/>
+      <c r="H11" s="52" t="n"/>
+      <c r="I11" s="52" t="n"/>
+      <c r="J11" s="52" t="n"/>
+      <c r="K11" s="52" t="n"/>
+      <c r="L11" s="52" t="n"/>
+      <c r="M11" s="52" t="n"/>
+      <c r="N11" s="52" t="n"/>
+      <c r="O11" s="52" t="n"/>
+      <c r="P11" s="52" t="n"/>
+      <c r="Q11" s="59">
         <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="28">
+      <c r="A12" s="52" t="n"/>
+      <c r="B12" s="52" t="n"/>
+      <c r="C12" s="52" t="n"/>
+      <c r="D12" s="52" t="n"/>
+      <c r="E12" s="52" t="n"/>
+      <c r="F12" s="52" t="n"/>
+      <c r="G12" s="52" t="n"/>
+      <c r="H12" s="52" t="n"/>
+      <c r="I12" s="52" t="n"/>
+      <c r="J12" s="52" t="n"/>
+      <c r="K12" s="52" t="n"/>
+      <c r="L12" s="52" t="n"/>
+      <c r="M12" s="52" t="n"/>
+      <c r="N12" s="52" t="n"/>
+      <c r="O12" s="52" t="n"/>
+      <c r="P12" s="52" t="n"/>
+      <c r="Q12" s="59">
         <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="28">
+      <c r="A13" s="52" t="n"/>
+      <c r="B13" s="52" t="n"/>
+      <c r="C13" s="52" t="n"/>
+      <c r="D13" s="52" t="n"/>
+      <c r="E13" s="52" t="n"/>
+      <c r="F13" s="52" t="n"/>
+      <c r="G13" s="52" t="n"/>
+      <c r="H13" s="52" t="n"/>
+      <c r="I13" s="52" t="n"/>
+      <c r="J13" s="52" t="n"/>
+      <c r="K13" s="52" t="n"/>
+      <c r="L13" s="52" t="n"/>
+      <c r="M13" s="52" t="n"/>
+      <c r="N13" s="52" t="n"/>
+      <c r="O13" s="52" t="n"/>
+      <c r="P13" s="52" t="n"/>
+      <c r="Q13" s="59">
         <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="28">
+      <c r="A14" s="52" t="n"/>
+      <c r="B14" s="52" t="n"/>
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="52" t="n"/>
+      <c r="E14" s="52" t="n"/>
+      <c r="F14" s="52" t="n"/>
+      <c r="G14" s="52" t="n"/>
+      <c r="H14" s="52" t="n"/>
+      <c r="I14" s="52" t="n"/>
+      <c r="J14" s="52" t="n"/>
+      <c r="K14" s="52" t="n"/>
+      <c r="L14" s="52" t="n"/>
+      <c r="M14" s="52" t="n"/>
+      <c r="N14" s="52" t="n"/>
+      <c r="O14" s="52" t="n"/>
+      <c r="P14" s="52" t="n"/>
+      <c r="Q14" s="59">
         <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="Q15" s="28">
+      <c r="A15" s="52" t="n"/>
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="52" t="n"/>
+      <c r="D15" s="52" t="n"/>
+      <c r="E15" s="52" t="n"/>
+      <c r="F15" s="52" t="n"/>
+      <c r="G15" s="52" t="n"/>
+      <c r="H15" s="52" t="n"/>
+      <c r="I15" s="52" t="n"/>
+      <c r="J15" s="52" t="n"/>
+      <c r="K15" s="52" t="n"/>
+      <c r="L15" s="52" t="n"/>
+      <c r="M15" s="52" t="n"/>
+      <c r="N15" s="52" t="n"/>
+      <c r="O15" s="52" t="n"/>
+      <c r="P15" s="52" t="n"/>
+      <c r="Q15" s="59">
         <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="Q16" s="28">
+      <c r="A16" s="52" t="n"/>
+      <c r="B16" s="52" t="n"/>
+      <c r="C16" s="52" t="n"/>
+      <c r="D16" s="52" t="n"/>
+      <c r="E16" s="52" t="n"/>
+      <c r="F16" s="52" t="n"/>
+      <c r="G16" s="52" t="n"/>
+      <c r="H16" s="52" t="n"/>
+      <c r="I16" s="52" t="n"/>
+      <c r="J16" s="52" t="n"/>
+      <c r="K16" s="52" t="n"/>
+      <c r="L16" s="52" t="n"/>
+      <c r="M16" s="52" t="n"/>
+      <c r="N16" s="52" t="n"/>
+      <c r="O16" s="52" t="n"/>
+      <c r="P16" s="52" t="n"/>
+      <c r="Q16" s="59">
         <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="Q17" s="28">
+      <c r="A17" s="52" t="n"/>
+      <c r="B17" s="52" t="n"/>
+      <c r="C17" s="52" t="n"/>
+      <c r="D17" s="52" t="n"/>
+      <c r="E17" s="52" t="n"/>
+      <c r="F17" s="52" t="n"/>
+      <c r="G17" s="52" t="n"/>
+      <c r="H17" s="52" t="n"/>
+      <c r="I17" s="52" t="n"/>
+      <c r="J17" s="52" t="n"/>
+      <c r="K17" s="52" t="n"/>
+      <c r="L17" s="52" t="n"/>
+      <c r="M17" s="52" t="n"/>
+      <c r="N17" s="52" t="n"/>
+      <c r="O17" s="52" t="n"/>
+      <c r="P17" s="52" t="n"/>
+      <c r="Q17" s="59">
         <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="Q18" s="28">
+      <c r="A18" s="52" t="n"/>
+      <c r="B18" s="52" t="n"/>
+      <c r="C18" s="52" t="n"/>
+      <c r="D18" s="52" t="n"/>
+      <c r="E18" s="52" t="n"/>
+      <c r="F18" s="52" t="n"/>
+      <c r="G18" s="52" t="n"/>
+      <c r="H18" s="52" t="n"/>
+      <c r="I18" s="52" t="n"/>
+      <c r="J18" s="52" t="n"/>
+      <c r="K18" s="52" t="n"/>
+      <c r="L18" s="52" t="n"/>
+      <c r="M18" s="52" t="n"/>
+      <c r="N18" s="52" t="n"/>
+      <c r="O18" s="52" t="n"/>
+      <c r="P18" s="52" t="n"/>
+      <c r="Q18" s="59">
         <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="Q19" s="28">
+      <c r="A19" s="52" t="n"/>
+      <c r="B19" s="52" t="n"/>
+      <c r="C19" s="52" t="n"/>
+      <c r="D19" s="52" t="n"/>
+      <c r="E19" s="52" t="n"/>
+      <c r="F19" s="52" t="n"/>
+      <c r="G19" s="52" t="n"/>
+      <c r="H19" s="52" t="n"/>
+      <c r="I19" s="52" t="n"/>
+      <c r="J19" s="52" t="n"/>
+      <c r="K19" s="52" t="n"/>
+      <c r="L19" s="52" t="n"/>
+      <c r="M19" s="52" t="n"/>
+      <c r="N19" s="52" t="n"/>
+      <c r="O19" s="52" t="n"/>
+      <c r="P19" s="52" t="n"/>
+      <c r="Q19" s="59">
         <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="Q20" s="28">
+      <c r="A20" s="52" t="n"/>
+      <c r="B20" s="52" t="n"/>
+      <c r="C20" s="52" t="n"/>
+      <c r="D20" s="52" t="n"/>
+      <c r="E20" s="52" t="n"/>
+      <c r="F20" s="52" t="n"/>
+      <c r="G20" s="52" t="n"/>
+      <c r="H20" s="52" t="n"/>
+      <c r="I20" s="52" t="n"/>
+      <c r="J20" s="52" t="n"/>
+      <c r="K20" s="52" t="n"/>
+      <c r="L20" s="52" t="n"/>
+      <c r="M20" s="52" t="n"/>
+      <c r="N20" s="52" t="n"/>
+      <c r="O20" s="52" t="n"/>
+      <c r="P20" s="52" t="n"/>
+      <c r="Q20" s="59">
         <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="Q21" s="28">
+      <c r="A21" s="52" t="n"/>
+      <c r="B21" s="52" t="n"/>
+      <c r="C21" s="52" t="n"/>
+      <c r="D21" s="52" t="n"/>
+      <c r="E21" s="52" t="n"/>
+      <c r="F21" s="52" t="n"/>
+      <c r="G21" s="52" t="n"/>
+      <c r="H21" s="52" t="n"/>
+      <c r="I21" s="52" t="n"/>
+      <c r="J21" s="52" t="n"/>
+      <c r="K21" s="52" t="n"/>
+      <c r="L21" s="52" t="n"/>
+      <c r="M21" s="52" t="n"/>
+      <c r="N21" s="52" t="n"/>
+      <c r="O21" s="52" t="n"/>
+      <c r="P21" s="52" t="n"/>
+      <c r="Q21" s="59">
         <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="Q22" s="28">
+      <c r="A22" s="52" t="n"/>
+      <c r="B22" s="52" t="n"/>
+      <c r="C22" s="52" t="n"/>
+      <c r="D22" s="52" t="n"/>
+      <c r="E22" s="52" t="n"/>
+      <c r="F22" s="52" t="n"/>
+      <c r="G22" s="52" t="n"/>
+      <c r="H22" s="52" t="n"/>
+      <c r="I22" s="52" t="n"/>
+      <c r="J22" s="52" t="n"/>
+      <c r="K22" s="52" t="n"/>
+      <c r="L22" s="52" t="n"/>
+      <c r="M22" s="52" t="n"/>
+      <c r="N22" s="52" t="n"/>
+      <c r="O22" s="52" t="n"/>
+      <c r="P22" s="52" t="n"/>
+      <c r="Q22" s="59">
         <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="Q23" s="28">
+      <c r="A23" s="52" t="n"/>
+      <c r="B23" s="52" t="n"/>
+      <c r="C23" s="52" t="n"/>
+      <c r="D23" s="52" t="n"/>
+      <c r="E23" s="52" t="n"/>
+      <c r="F23" s="52" t="n"/>
+      <c r="G23" s="52" t="n"/>
+      <c r="H23" s="52" t="n"/>
+      <c r="I23" s="52" t="n"/>
+      <c r="J23" s="52" t="n"/>
+      <c r="K23" s="52" t="n"/>
+      <c r="L23" s="52" t="n"/>
+      <c r="M23" s="52" t="n"/>
+      <c r="N23" s="52" t="n"/>
+      <c r="O23" s="52" t="n"/>
+      <c r="P23" s="52" t="n"/>
+      <c r="Q23" s="59">
         <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="Q24" s="28">
+      <c r="A24" s="52" t="n"/>
+      <c r="B24" s="52" t="n"/>
+      <c r="C24" s="52" t="n"/>
+      <c r="D24" s="52" t="n"/>
+      <c r="E24" s="52" t="n"/>
+      <c r="F24" s="52" t="n"/>
+      <c r="G24" s="52" t="n"/>
+      <c r="H24" s="52" t="n"/>
+      <c r="I24" s="52" t="n"/>
+      <c r="J24" s="52" t="n"/>
+      <c r="K24" s="52" t="n"/>
+      <c r="L24" s="52" t="n"/>
+      <c r="M24" s="52" t="n"/>
+      <c r="N24" s="52" t="n"/>
+      <c r="O24" s="52" t="n"/>
+      <c r="P24" s="52" t="n"/>
+      <c r="Q24" s="59">
         <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="Q25" s="28">
+      <c r="A25" s="52" t="n"/>
+      <c r="B25" s="52" t="n"/>
+      <c r="C25" s="52" t="n"/>
+      <c r="D25" s="52" t="n"/>
+      <c r="E25" s="52" t="n"/>
+      <c r="F25" s="52" t="n"/>
+      <c r="G25" s="52" t="n"/>
+      <c r="H25" s="52" t="n"/>
+      <c r="I25" s="52" t="n"/>
+      <c r="J25" s="52" t="n"/>
+      <c r="K25" s="52" t="n"/>
+      <c r="L25" s="52" t="n"/>
+      <c r="M25" s="52" t="n"/>
+      <c r="N25" s="52" t="n"/>
+      <c r="O25" s="52" t="n"/>
+      <c r="P25" s="52" t="n"/>
+      <c r="Q25" s="59">
         <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="Q26" s="28">
+      <c r="A26" s="52" t="n"/>
+      <c r="B26" s="52" t="n"/>
+      <c r="C26" s="52" t="n"/>
+      <c r="D26" s="52" t="n"/>
+      <c r="E26" s="52" t="n"/>
+      <c r="F26" s="52" t="n"/>
+      <c r="G26" s="52" t="n"/>
+      <c r="H26" s="52" t="n"/>
+      <c r="I26" s="52" t="n"/>
+      <c r="J26" s="52" t="n"/>
+      <c r="K26" s="52" t="n"/>
+      <c r="L26" s="52" t="n"/>
+      <c r="M26" s="52" t="n"/>
+      <c r="N26" s="52" t="n"/>
+      <c r="O26" s="52" t="n"/>
+      <c r="P26" s="52" t="n"/>
+      <c r="Q26" s="59">
         <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="Q27" s="28">
+      <c r="A27" s="52" t="n"/>
+      <c r="B27" s="52" t="n"/>
+      <c r="C27" s="52" t="n"/>
+      <c r="D27" s="52" t="n"/>
+      <c r="E27" s="52" t="n"/>
+      <c r="F27" s="52" t="n"/>
+      <c r="G27" s="52" t="n"/>
+      <c r="H27" s="52" t="n"/>
+      <c r="I27" s="52" t="n"/>
+      <c r="J27" s="52" t="n"/>
+      <c r="K27" s="52" t="n"/>
+      <c r="L27" s="52" t="n"/>
+      <c r="M27" s="52" t="n"/>
+      <c r="N27" s="52" t="n"/>
+      <c r="O27" s="52" t="n"/>
+      <c r="P27" s="52" t="n"/>
+      <c r="Q27" s="59">
         <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
         <v/>
       </c>
@@ -1877,120 +3055,126 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Protection</t>
         </is>
       </c>
-      <c r="B1" s="39" t="n"/>
-      <c r="C1" s="39" t="n"/>
-      <c r="D1" s="39" t="n"/>
-      <c r="E1" s="40" t="n"/>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="69" t="n"/>
+      <c r="C1" s="69" t="n"/>
+      <c r="D1" s="69" t="n"/>
+      <c r="E1" s="70" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="52" t="n"/>
+      <c r="B2" s="52" t="n"/>
+      <c r="C2" s="52" t="n"/>
+      <c r="D2" s="52" t="n"/>
+      <c r="E2" s="52" t="n"/>
+    </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>موضوع</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>شرط / مقدار</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="71" t="inlineStr">
         <is>
           <t>ثابت / محل کد</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="71" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="72" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
         <is>
           <t>MODULE_PROTECTION=0</t>
         </is>
       </c>
-      <c r="C4" s="30" t="inlineStr">
+      <c r="C4" s="72" t="inlineStr">
         <is>
           <t>خاموش؛ اسکلت</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="73" t="inlineStr">
         <is>
           <t>modules_enable.h</t>
         </is>
       </c>
-      <c r="E4" s="30" t="inlineStr">
+      <c r="E4" s="72" t="inlineStr">
         <is>
           <t>فعال‌سازی با دستور کاربر</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="30" t="inlineStr">
+      <c r="A5" s="72" t="inlineStr">
         <is>
           <t>FAULT_ADC</t>
         </is>
       </c>
-      <c r="B5" s="30" t="inlineStr">
+      <c r="B5" s="72" t="inlineStr">
         <is>
           <t>Set در نامعتبر / Clear در معتبر</t>
         </is>
       </c>
-      <c r="C5" s="30" t="inlineStr">
+      <c r="C5" s="72" t="inlineStr">
         <is>
           <t>لحظه‌ای، بدون latch</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="73" t="inlineStr">
         <is>
           <t>protection.c (اصلاح 2026-09-22)</t>
         </is>
       </c>
-      <c r="E5" s="30" t="inlineStr">
+      <c r="E5" s="72" t="inlineStr">
         <is>
           <t>قبلاً latch ابدی بود</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="72" t="inlineStr">
         <is>
           <t>مالکیت بیت‌ها</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="72" t="inlineStr">
         <is>
           <t>این ماژول فقط FAULT_ADC</t>
         </is>
       </c>
-      <c r="C6" s="30" t="inlineStr">
+      <c r="C6" s="72" t="inlineStr">
         <is>
           <t>BAT_LOST مالک Fault</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
+      <c r="D6" s="73" t="inlineStr">
         <is>
           <t>fault.h / app_types.h</t>
         </is>
       </c>
-      <c r="E6" s="30" t="inlineStr">
+      <c r="E6" s="72" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -2035,93 +3219,105 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Protection</t>
         </is>
       </c>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
+      <c r="D1" s="52" t="n"/>
+      <c r="E1" s="52" t="n"/>
+      <c r="F1" s="52" t="n"/>
+      <c r="G1" s="52" t="n"/>
+      <c r="H1" s="52" t="n"/>
+      <c r="I1" s="52" t="n"/>
+      <c r="J1" s="52" t="n"/>
+      <c r="K1" s="52" t="n"/>
+      <c r="L1" s="52" t="n"/>
+      <c r="M1" s="52" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="49" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="39" t="n"/>
-      <c r="C2" s="39" t="n"/>
-      <c r="D2" s="39" t="n"/>
-      <c r="E2" s="39" t="n"/>
-      <c r="F2" s="39" t="n"/>
-      <c r="G2" s="39" t="n"/>
-      <c r="H2" s="39" t="n"/>
-      <c r="I2" s="39" t="n"/>
-      <c r="J2" s="39" t="n"/>
-      <c r="K2" s="39" t="n"/>
-      <c r="L2" s="39" t="n"/>
-      <c r="M2" s="40" t="n"/>
+      <c r="B2" s="69" t="n"/>
+      <c r="C2" s="69" t="n"/>
+      <c r="D2" s="69" t="n"/>
+      <c r="E2" s="69" t="n"/>
+      <c r="F2" s="69" t="n"/>
+      <c r="G2" s="69" t="n"/>
+      <c r="H2" s="69" t="n"/>
+      <c r="I2" s="69" t="n"/>
+      <c r="J2" s="69" t="n"/>
+      <c r="K2" s="69" t="n"/>
+      <c r="L2" s="69" t="n"/>
+      <c r="M2" s="70" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="71" t="inlineStr">
         <is>
           <t>شماره ایراد</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>شناسه تست</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="71" t="inlineStr">
         <is>
           <t>تاریخ کشف</t>
         </is>
       </c>
-      <c r="D3" s="29" t="inlineStr">
+      <c r="D3" s="71" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="71" t="inlineStr">
         <is>
           <t>شرح کوتاه ایراد</t>
         </is>
       </c>
-      <c r="F3" s="29" t="inlineStr">
+      <c r="F3" s="71" t="inlineStr">
         <is>
           <t>مراحل بازتولید</t>
         </is>
       </c>
-      <c r="G3" s="29" t="inlineStr">
+      <c r="G3" s="71" t="inlineStr">
         <is>
           <t>انتظار</t>
         </is>
       </c>
-      <c r="H3" s="29" t="inlineStr">
+      <c r="H3" s="71" t="inlineStr">
         <is>
           <t>واقعیت</t>
         </is>
       </c>
-      <c r="I3" s="29" t="inlineStr">
+      <c r="I3" s="71" t="inlineStr">
         <is>
           <t>مدرک/مسیر عکس یا scope</t>
         </is>
       </c>
-      <c r="J3" s="29" t="inlineStr">
+      <c r="J3" s="71" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="K3" s="29" t="inlineStr">
+      <c r="K3" s="71" t="inlineStr">
         <is>
           <t>محل احتمالی</t>
         </is>
       </c>
-      <c r="L3" s="29" t="inlineStr">
+      <c r="L3" s="71" t="inlineStr">
         <is>
           <t>وضعیت ایراد</t>
         </is>
       </c>
-      <c r="M3" s="29" t="inlineStr">
+      <c r="M3" s="71" t="inlineStr">
         <is>
           <t>تأیید رفع / توضیحات</t>
         </is>
@@ -2152,209 +3348,233 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="47" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Protection</t>
         </is>
       </c>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
+      <c r="B2" s="52" t="n"/>
+      <c r="C2" s="52" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>مشخصات تست</t>
         </is>
       </c>
+      <c r="B3" s="52" t="n"/>
+      <c r="C3" s="52" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>پروژه</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="48" t="inlineStr">
         <is>
           <t>ChangeOver</t>
         </is>
       </c>
+      <c r="C4" s="52" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>ماژول</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="48" t="inlineStr">
         <is>
           <t>Protection — اسکلت حفاظت</t>
         </is>
       </c>
+      <c r="C5" s="52" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="48" t="inlineStr">
         <is>
           <t>تاریخ ساخت فرم</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="48" t="inlineStr">
         <is>
           <t>2026-09-23 (1.0)</t>
         </is>
       </c>
+      <c r="C6" s="52" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>نسخه فرم</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="48" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
+      <c r="C7" s="52" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="48" t="inlineStr">
         <is>
           <t>commit firmware</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="48" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
+      <c r="C8" s="52" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="48" t="inlineStr">
         <is>
           <t>ابزار</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="48" t="inlineStr">
         <is>
           <t>بیلد تستی + پنل ESP</t>
         </is>
       </c>
-    </row>
-    <row r="10"/>
+      <c r="C9" s="52" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="52" t="n"/>
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="52" t="n"/>
+    </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="74" t="inlineStr">
         <is>
           <t>خلاصهٔ خودکار وضعیت تست‌ها</t>
         </is>
       </c>
+      <c r="B11" s="52" t="n"/>
+      <c r="C11" s="52" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="71" t="inlineStr">
         <is>
           <t>شاخص</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="71" t="inlineStr">
         <is>
           <t>مقدار</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
+      <c r="C12" s="71" t="inlineStr">
         <is>
           <t>توضیح</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="32" t="inlineStr">
+      <c r="A13" s="75" t="inlineStr">
         <is>
           <t>کل تست‌ها</t>
         </is>
       </c>
-      <c r="B13" s="32" t="n">
+      <c r="B13" s="75" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="32" t="inlineStr">
+      <c r="C13" s="75" t="inlineStr">
         <is>
           <t>همهٔ ردیف‌های برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="75" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
-      <c r="B14" s="32">
+      <c r="B14" s="75">
         <f>COUNTIF('برنامه تست'!L:L,"قبول")</f>
         <v/>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" s="75" t="inlineStr">
         <is>
           <t>COUNTIF برنامه تست</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="32" t="inlineStr">
+      <c r="A15" s="75" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
-      <c r="B15" s="32">
+      <c r="B15" s="75">
         <f>COUNTIF('برنامه تست'!L:L,"رد")</f>
         <v/>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="75" t="inlineStr">
         <is>
           <t>COUNTIF رد</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="75" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="B16" s="32">
+      <c r="B16" s="75">
         <f>COUNTIF('برنامه تست'!L:L,"در انتظار")</f>
         <v/>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C16" s="75" t="inlineStr">
         <is>
           <t>پیش از تست برد</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="32" t="inlineStr">
+      <c r="A17" s="75" t="inlineStr">
         <is>
           <t>نرخ قبولی</t>
         </is>
       </c>
-      <c r="B17" s="32">
+      <c r="B17" s="75">
         <f>IF(5=0,0,COUNTIF('برنامه تست'!L:L,"قبول")/5)</f>
         <v/>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" s="75" t="inlineStr">
         <is>
           <t>قبول/کل</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
+    <row r="18">
+      <c r="A18" s="52" t="n"/>
+      <c r="B18" s="52" t="n"/>
+      <c r="C18" s="52" t="n"/>
+    </row>
     <row r="19">
-      <c r="A19" s="31" t="inlineStr">
+      <c r="A19" s="74" t="inlineStr">
         <is>
           <t>امضا و تأیید: تست‌کننده ______  بازبین ______  تاریخ ______</t>
         </is>
       </c>
+      <c r="B19" s="52" t="n"/>
+      <c r="C19" s="52" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2381,117 +3601,136 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="33" t="inlineStr">
+      <c r="A1" s="76" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
+      <c r="B1" s="52" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="34" t="inlineStr">
+      <c r="A2" s="77" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
+      <c r="B2" s="52" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="34" t="inlineStr">
+      <c r="A3" s="77" t="inlineStr">
         <is>
           <t>انجام شد</t>
         </is>
       </c>
+      <c r="B3" s="52" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="77" t="inlineStr">
         <is>
           <t>قبول</t>
         </is>
       </c>
+      <c r="B4" s="52" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>رد</t>
         </is>
       </c>
+      <c r="B5" s="52" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="77" t="inlineStr">
         <is>
           <t>مسدود</t>
         </is>
       </c>
+      <c r="B6" s="52" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="52" t="inlineStr">
         <is>
           <t>نیاز به تکرار</t>
         </is>
       </c>
+      <c r="B7" s="52" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="76" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
+      <c r="B8" s="52" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="34" t="inlineStr">
+      <c r="A9" s="52" t="n"/>
+      <c r="B9" s="77" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="34" t="inlineStr">
+      <c r="A10" s="52" t="n"/>
+      <c r="B10" s="77" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="34" t="inlineStr">
+      <c r="A11" s="52" t="n"/>
+      <c r="B11" s="77" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
+    <row r="12">
+      <c r="A12" s="52" t="n"/>
+      <c r="B12" s="52" t="n"/>
+    </row>
     <row r="13">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="76" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
       </c>
+      <c r="B13" s="52" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="77" t="inlineStr">
         <is>
           <t>بحرانی</t>
         </is>
       </c>
+      <c r="B14" s="52" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="34" t="inlineStr">
+      <c r="A15" s="77" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
+      <c r="B15" s="52" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="inlineStr">
+      <c r="A16" s="77" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
+      <c r="B16" s="52" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="A17" s="77" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
+      <c r="B17" s="52" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2513,60 +3752,70 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="35" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>ماشین حالت ماژول نگهبان اعتبار (Protection)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="52" t="n"/>
+      <c r="B2" s="52" t="n"/>
+      <c r="C2" s="52" t="n"/>
+    </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>حالت‌ها و گذارهای همین ماژول</t>
         </is>
       </c>
-      <c r="B3" s="37" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Protection_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C3" s="52" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
         </is>
       </c>
-      <c r="B4" s="37" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>../../../Documentation/System_State_Machine.xlsx</t>
         </is>
       </c>
+      <c r="C4" s="52" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="36" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>راهنمای رنگ‌ها</t>
         </is>
       </c>
-      <c r="B5" s="38" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
         </is>
       </c>
+      <c r="C5" s="52" t="n"/>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>بازتولید</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>python3 tools/make_module_state_machines.py</t>
         </is>
       </c>
+      <c r="C6" s="52" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2611,135 +3860,183 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="51" t="inlineStr">
         <is>
           <t>برنامهٔ تست آزمایشگاهی — ماژول Protection</t>
         </is>
       </c>
+      <c r="B1" s="52" t="n"/>
+      <c r="C1" s="52" t="n"/>
+      <c r="D1" s="52" t="n"/>
+      <c r="E1" s="52" t="n"/>
+      <c r="F1" s="52" t="n"/>
+      <c r="G1" s="52" t="n"/>
+      <c r="H1" s="52" t="n"/>
+      <c r="I1" s="52" t="n"/>
+      <c r="J1" s="52" t="n"/>
+      <c r="K1" s="52" t="n"/>
+      <c r="L1" s="52" t="n"/>
+      <c r="M1" s="52" t="n"/>
+      <c r="N1" s="52" t="n"/>
+      <c r="O1" s="52" t="n"/>
+      <c r="P1" s="52" t="n"/>
+      <c r="Q1" s="52" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="48" t="inlineStr">
         <is>
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="B2" s="52" t="n"/>
+      <c r="C2" s="52" t="n"/>
+      <c r="D2" s="52" t="n"/>
+      <c r="E2" s="52" t="n"/>
+      <c r="F2" s="52" t="n"/>
+      <c r="G2" s="52" t="n"/>
+      <c r="H2" s="52" t="n"/>
+      <c r="I2" s="52" t="n"/>
+      <c r="J2" s="52" t="n"/>
+      <c r="K2" s="52" t="n"/>
+      <c r="L2" s="52" t="n"/>
+      <c r="M2" s="52" t="n"/>
+      <c r="N2" s="52" t="n"/>
+      <c r="O2" s="52" t="n"/>
+      <c r="P2" s="52" t="n"/>
+      <c r="Q2" s="52" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="B3" s="52" t="n"/>
+      <c r="C3" s="52" t="n"/>
+      <c r="D3" s="52" t="n"/>
+      <c r="E3" s="52" t="n"/>
+      <c r="F3" s="52" t="n"/>
+      <c r="G3" s="52" t="n"/>
+      <c r="H3" s="52" t="n"/>
+      <c r="I3" s="52" t="n"/>
+      <c r="J3" s="52" t="n"/>
+      <c r="K3" s="52" t="n"/>
+      <c r="L3" s="52" t="n"/>
+      <c r="M3" s="52" t="n"/>
+      <c r="N3" s="52" t="n"/>
+      <c r="O3" s="52" t="n"/>
+      <c r="P3" s="52" t="n"/>
+      <c r="Q3" s="52" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="49" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="49" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="49" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="49" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="49" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="14" t="inlineStr">
+      <c r="G4" s="49" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="H4" s="49" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="49" t="inlineStr">
         <is>
           <t>وضعیت حفظ / latch</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="49" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="49" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="14" t="inlineStr">
+      <c r="L4" s="49" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="14" t="inlineStr">
+      <c r="M4" s="49" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="14" t="inlineStr">
+      <c r="N4" s="49" t="inlineStr">
         <is>
           <t>مدرک تست / scope</t>
         </is>
       </c>
-      <c r="O4" s="14" t="inlineStr">
+      <c r="O4" s="49" t="inlineStr">
         <is>
           <t>commit</t>
         </is>
       </c>
-      <c r="P4" s="14" t="inlineStr">
+      <c r="P4" s="49" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="14" t="inlineStr">
+      <c r="Q4" s="49" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.5" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="53" t="inlineStr">
         <is>
           <t>PR-002</t>
         </is>
       </c>
-      <c r="B5" s="23" t="inlineStr">
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>FAULT_ADC لحظه‌ای</t>
         </is>
       </c>
-      <c r="C5" s="24" t="inlineStr">
+      <c r="C5" s="67" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="62" t="inlineStr">
         <is>
           <t>بیلد تستی با MODULE_PROTECTION=1</t>
         </is>
       </c>
-      <c r="E5" s="23" t="inlineStr">
+      <c r="E5" s="62" t="inlineStr">
         <is>
           <t>گام ۱: یک بیلد تستی بگیر که در آن MODULE_PROTECTION=1 باشد.
 گام ۲: ADC را موقتاً نامعتبر کن (مثلاً ورودی را در دورهٔ warm-up قطع کن تا snapshot نامعتبر شود).
@@ -2747,46 +4044,46 @@
 گام ۴: ADC را معتبر کن و اولین snapshot معتبر را بده (5 ثانیه کافی است): بیت باید خودش پاک شود؛ بیت بعد از معتبر شدن صفر است.</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" s="63" t="inlineStr">
         <is>
           <t>snapshot نامعتبر</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="G5" s="63" t="inlineStr">
         <is>
           <t>5s</t>
         </is>
       </c>
-      <c r="H5" s="23" t="inlineStr">
+      <c r="H5" s="62" t="inlineStr">
         <is>
           <t>Set بیت FAULT_ADC به‌صورت لحظه‌ای؛ با اولین snapshot معتبر خودش پاک می‌شود</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="I5" s="62" t="inlineStr">
         <is>
           <t>لحظه‌ای نه latch</t>
         </is>
       </c>
-      <c r="J5" s="23" t="inlineStr">
+      <c r="J5" s="62" t="inlineStr">
         <is>
           <t>بیت بعد از معتبر شدن صفر</t>
         </is>
       </c>
-      <c r="K5" s="23" t="n"/>
-      <c r="L5" s="21" t="inlineStr">
+      <c r="K5" s="62" t="n"/>
+      <c r="L5" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="23" t="n"/>
-      <c r="N5" s="23" t="n"/>
-      <c r="O5" s="25" t="inlineStr">
+      <c r="M5" s="62" t="n"/>
+      <c r="N5" s="62" t="n"/>
+      <c r="O5" s="63" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="25" t="n"/>
-      <c r="Q5" s="26">
+      <c r="P5" s="63" t="n"/>
+      <c r="Q5" s="65">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>

--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -186,6 +186,10 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -230,7 +234,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -310,11 +314,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -507,6 +512,9 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -873,7 +881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -931,6 +939,14 @@
       <c r="A9" s="50" t="inlineStr">
         <is>
           <t>یادداشت: تست‌های PR-002/PR-003 به بیلد تستی با MODULE_PROTECTION=1 نیاز دارند؛ در بیلد فعلی فقط PR-001 قابل اجراست.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="78" t="inlineStr">
+        <is>
+          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
+ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
         </is>
       </c>
     </row>
@@ -988,22 +1004,6 @@
           <t>برنامهٔ تست عملی — ماژول Protection</t>
         </is>
       </c>
-      <c r="B1" s="52" t="n"/>
-      <c r="C1" s="52" t="n"/>
-      <c r="D1" s="52" t="n"/>
-      <c r="E1" s="52" t="n"/>
-      <c r="F1" s="52" t="n"/>
-      <c r="G1" s="52" t="n"/>
-      <c r="H1" s="52" t="n"/>
-      <c r="I1" s="52" t="n"/>
-      <c r="J1" s="52" t="n"/>
-      <c r="K1" s="52" t="n"/>
-      <c r="L1" s="52" t="n"/>
-      <c r="M1" s="52" t="n"/>
-      <c r="N1" s="52" t="n"/>
-      <c r="O1" s="52" t="n"/>
-      <c r="P1" s="52" t="n"/>
-      <c r="Q1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="48" t="inlineStr">
@@ -1011,22 +1011,6 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
-      <c r="B2" s="52" t="n"/>
-      <c r="C2" s="52" t="n"/>
-      <c r="D2" s="52" t="n"/>
-      <c r="E2" s="52" t="n"/>
-      <c r="F2" s="52" t="n"/>
-      <c r="G2" s="52" t="n"/>
-      <c r="H2" s="52" t="n"/>
-      <c r="I2" s="52" t="n"/>
-      <c r="J2" s="52" t="n"/>
-      <c r="K2" s="52" t="n"/>
-      <c r="L2" s="52" t="n"/>
-      <c r="M2" s="52" t="n"/>
-      <c r="N2" s="52" t="n"/>
-      <c r="O2" s="52" t="n"/>
-      <c r="P2" s="52" t="n"/>
-      <c r="Q2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="48" t="inlineStr">
@@ -1034,22 +1018,6 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
-      <c r="B3" s="52" t="n"/>
-      <c r="C3" s="52" t="n"/>
-      <c r="D3" s="52" t="n"/>
-      <c r="E3" s="52" t="n"/>
-      <c r="F3" s="52" t="n"/>
-      <c r="G3" s="52" t="n"/>
-      <c r="H3" s="52" t="n"/>
-      <c r="I3" s="52" t="n"/>
-      <c r="J3" s="52" t="n"/>
-      <c r="K3" s="52" t="n"/>
-      <c r="L3" s="52" t="n"/>
-      <c r="M3" s="52" t="n"/>
-      <c r="N3" s="52" t="n"/>
-      <c r="O3" s="52" t="n"/>
-      <c r="P3" s="52" t="n"/>
-      <c r="Q3" s="52" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="49" t="inlineStr">
@@ -1099,7 +1067,7 @@
       </c>
       <c r="J4" s="49" t="inlineStr">
         <is>
-          <t>معیار قبولی</t>
+          <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
       <c r="K4" s="49" t="inlineStr">
@@ -1187,27 +1155,26 @@
       </c>
       <c r="J5" s="54" t="inlineStr">
         <is>
-          <t>کار تمیز چندساعته = قبول؛ قطع بی‌دلیل = رد</t>
-        </is>
-      </c>
-      <c r="K5" s="54" t="inlineStr"/>
+          <t>باید ببینید: در کار عادی هیچ قطع حفاظتیِ اضافه‌ای نیست و دستگاه چند ساعت تمیز کار می‌کند. اگر قطع بی‌دلیل دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K5" s="54" t="n"/>
       <c r="L5" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M5" s="54" t="inlineStr"/>
-      <c r="N5" s="54" t="inlineStr"/>
+      <c r="M5" s="54" t="n"/>
+      <c r="N5" s="54" t="n"/>
       <c r="O5" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P5" s="56" t="inlineStr"/>
-      <c r="Q5" s="58" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
+      <c r="P5" s="56" t="n"/>
+      <c r="Q5" s="58">
+        <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
+        <v/>
       </c>
     </row>
     <row r="6" ht="54" customHeight="1">
@@ -1223,7 +1190,7 @@
       </c>
       <c r="C6" s="55" t="inlineStr">
         <is>
-          <t>بالا</t>
+          <t>متوسط</t>
         </is>
       </c>
       <c r="D6" s="54" t="inlineStr">
@@ -1259,908 +1226,787 @@
       </c>
       <c r="J6" s="54" t="inlineStr">
         <is>
-          <t>بالا آمدن تمیز = قبول؛ قطع‌ووصل اول کار = رد</t>
-        </is>
-      </c>
-      <c r="K6" s="54" t="inlineStr"/>
+          <t>باید ببینید: دستگاه در لحظه‌های اول بی‌دلیل قطع نمی‌شود و تمیز بالا می‌آید و بار عادی کار می‌کند. اگر قطع‌ووصل اول کار دیدید، قبول نیست.</t>
+        </is>
+      </c>
+      <c r="K6" s="54" t="n"/>
       <c r="L6" s="57" t="inlineStr">
         <is>
           <t>در انتظار</t>
         </is>
       </c>
-      <c r="M6" s="54" t="inlineStr"/>
-      <c r="N6" s="54" t="inlineStr"/>
+      <c r="M6" s="54" t="n"/>
+      <c r="N6" s="54" t="n"/>
       <c r="O6" s="56" t="inlineStr">
         <is>
           <t>TESTER: fill</t>
         </is>
       </c>
-      <c r="P6" s="56" t="inlineStr"/>
-      <c r="Q6" s="58" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="52" t="n"/>
-      <c r="B7" s="52" t="n"/>
-      <c r="C7" s="52" t="n"/>
-      <c r="D7" s="52" t="n"/>
-      <c r="E7" s="52" t="n"/>
-      <c r="F7" s="52" t="n"/>
-      <c r="G7" s="52" t="n"/>
-      <c r="H7" s="52" t="n"/>
-      <c r="I7" s="52" t="n"/>
-      <c r="J7" s="52" t="n"/>
-      <c r="K7" s="52" t="n"/>
-      <c r="L7" s="52" t="n"/>
-      <c r="M7" s="52" t="n"/>
-      <c r="N7" s="52" t="n"/>
-      <c r="O7" s="52" t="n"/>
-      <c r="P7" s="52" t="n"/>
-      <c r="Q7" s="59">
-        <f>IF(OR(L11="",L11="در انتظار"),"",IF(Q11="",TODAY(),Q11))</f>
+      <c r="P6" s="56" t="n"/>
+      <c r="Q6" s="58">
+        <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="54" customHeight="1">
-      <c r="A8" s="52" t="n"/>
-      <c r="B8" s="52" t="n"/>
-      <c r="C8" s="52" t="n"/>
-      <c r="D8" s="52" t="n"/>
-      <c r="E8" s="52" t="n"/>
-      <c r="F8" s="52" t="n"/>
-      <c r="G8" s="52" t="n"/>
-      <c r="H8" s="52" t="n"/>
-      <c r="I8" s="52" t="n"/>
-      <c r="J8" s="52" t="n"/>
-      <c r="K8" s="52" t="n"/>
-      <c r="L8" s="52" t="n"/>
-      <c r="M8" s="52" t="n"/>
-      <c r="N8" s="52" t="n"/>
-      <c r="O8" s="52" t="n"/>
-      <c r="P8" s="52" t="n"/>
-      <c r="Q8" s="59">
-        <f>IF(OR(L12="",L12="در انتظار"),"",IF(Q12="",TODAY(),Q12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="52" t="n"/>
-      <c r="B9" s="52" t="n"/>
-      <c r="C9" s="52" t="n"/>
-      <c r="D9" s="52" t="n"/>
-      <c r="E9" s="52" t="n"/>
-      <c r="F9" s="52" t="n"/>
-      <c r="G9" s="52" t="n"/>
-      <c r="H9" s="52" t="n"/>
-      <c r="I9" s="52" t="n"/>
-      <c r="J9" s="52" t="n"/>
-      <c r="K9" s="52" t="n"/>
-      <c r="L9" s="52" t="n"/>
-      <c r="M9" s="52" t="n"/>
-      <c r="N9" s="52" t="n"/>
-      <c r="O9" s="52" t="n"/>
-      <c r="P9" s="52" t="n"/>
-      <c r="Q9" s="59">
-        <f>IF(OR(L13="",L13="در انتظار"),"",IF(Q13="",TODAY(),Q13))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="54" customHeight="1">
-      <c r="A10" s="52" t="n"/>
-      <c r="B10" s="52" t="n"/>
-      <c r="C10" s="52" t="n"/>
-      <c r="D10" s="52" t="n"/>
-      <c r="E10" s="52" t="n"/>
-      <c r="F10" s="52" t="n"/>
-      <c r="G10" s="52" t="n"/>
-      <c r="H10" s="52" t="n"/>
-      <c r="I10" s="52" t="n"/>
-      <c r="J10" s="52" t="n"/>
-      <c r="K10" s="52" t="n"/>
-      <c r="L10" s="52" t="n"/>
-      <c r="M10" s="52" t="n"/>
-      <c r="N10" s="52" t="n"/>
-      <c r="O10" s="52" t="n"/>
-      <c r="P10" s="52" t="n"/>
-      <c r="Q10" s="59">
-        <f>IF(OR(L14="",L14="در انتظار"),"",IF(Q14="",TODAY(),Q14))</f>
-        <v/>
-      </c>
+    <row r="7">
+      <c r="A7" s="79" t="n"/>
+      <c r="B7" s="79" t="n"/>
+      <c r="C7" s="79" t="n"/>
+      <c r="D7" s="79" t="n"/>
+      <c r="E7" s="79" t="n"/>
+      <c r="F7" s="79" t="n"/>
+      <c r="G7" s="79" t="n"/>
+      <c r="H7" s="79" t="n"/>
+      <c r="I7" s="79" t="n"/>
+      <c r="J7" s="79" t="n"/>
+      <c r="K7" s="79" t="n"/>
+      <c r="L7" s="79" t="n"/>
+      <c r="M7" s="79" t="n"/>
+      <c r="N7" s="79" t="n"/>
+      <c r="O7" s="79" t="n"/>
+      <c r="P7" s="79" t="n"/>
+      <c r="Q7" s="80" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="79" t="n"/>
+      <c r="B8" s="79" t="n"/>
+      <c r="C8" s="79" t="n"/>
+      <c r="D8" s="79" t="n"/>
+      <c r="E8" s="79" t="n"/>
+      <c r="F8" s="79" t="n"/>
+      <c r="G8" s="79" t="n"/>
+      <c r="H8" s="79" t="n"/>
+      <c r="I8" s="79" t="n"/>
+      <c r="J8" s="79" t="n"/>
+      <c r="K8" s="79" t="n"/>
+      <c r="L8" s="79" t="n"/>
+      <c r="M8" s="79" t="n"/>
+      <c r="N8" s="79" t="n"/>
+      <c r="O8" s="79" t="n"/>
+      <c r="P8" s="79" t="n"/>
+      <c r="Q8" s="80" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="79" t="n"/>
+      <c r="B9" s="79" t="n"/>
+      <c r="C9" s="79" t="n"/>
+      <c r="D9" s="79" t="n"/>
+      <c r="E9" s="79" t="n"/>
+      <c r="F9" s="79" t="n"/>
+      <c r="G9" s="79" t="n"/>
+      <c r="H9" s="79" t="n"/>
+      <c r="I9" s="79" t="n"/>
+      <c r="J9" s="79" t="n"/>
+      <c r="K9" s="79" t="n"/>
+      <c r="L9" s="79" t="n"/>
+      <c r="M9" s="79" t="n"/>
+      <c r="N9" s="79" t="n"/>
+      <c r="O9" s="79" t="n"/>
+      <c r="P9" s="79" t="n"/>
+      <c r="Q9" s="80" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="79" t="n"/>
+      <c r="B10" s="79" t="n"/>
+      <c r="C10" s="79" t="n"/>
+      <c r="D10" s="79" t="n"/>
+      <c r="E10" s="79" t="n"/>
+      <c r="F10" s="79" t="n"/>
+      <c r="G10" s="79" t="n"/>
+      <c r="H10" s="79" t="n"/>
+      <c r="I10" s="79" t="n"/>
+      <c r="J10" s="79" t="n"/>
+      <c r="K10" s="79" t="n"/>
+      <c r="L10" s="79" t="n"/>
+      <c r="M10" s="79" t="n"/>
+      <c r="N10" s="79" t="n"/>
+      <c r="O10" s="79" t="n"/>
+      <c r="P10" s="79" t="n"/>
+      <c r="Q10" s="80" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="52" t="n"/>
-      <c r="B11" s="52" t="n"/>
-      <c r="C11" s="52" t="n"/>
-      <c r="D11" s="52" t="n"/>
-      <c r="E11" s="52" t="n"/>
-      <c r="F11" s="52" t="n"/>
-      <c r="G11" s="52" t="n"/>
-      <c r="H11" s="52" t="n"/>
-      <c r="I11" s="52" t="n"/>
-      <c r="J11" s="52" t="n"/>
-      <c r="K11" s="52" t="n"/>
-      <c r="L11" s="52" t="n"/>
-      <c r="M11" s="52" t="n"/>
-      <c r="N11" s="52" t="n"/>
-      <c r="O11" s="52" t="n"/>
-      <c r="P11" s="52" t="n"/>
-      <c r="Q11" s="59">
-        <f>IF(OR(L15="",L15="در انتظار"),"",IF(Q15="",TODAY(),Q15))</f>
-        <v/>
-      </c>
+      <c r="A11" s="79" t="n"/>
+      <c r="B11" s="79" t="n"/>
+      <c r="C11" s="79" t="n"/>
+      <c r="D11" s="79" t="n"/>
+      <c r="E11" s="79" t="n"/>
+      <c r="F11" s="79" t="n"/>
+      <c r="G11" s="79" t="n"/>
+      <c r="H11" s="79" t="n"/>
+      <c r="I11" s="79" t="n"/>
+      <c r="J11" s="79" t="n"/>
+      <c r="K11" s="79" t="n"/>
+      <c r="L11" s="79" t="n"/>
+      <c r="M11" s="79" t="n"/>
+      <c r="N11" s="79" t="n"/>
+      <c r="O11" s="79" t="n"/>
+      <c r="P11" s="79" t="n"/>
+      <c r="Q11" s="80" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="52" t="n"/>
-      <c r="B12" s="52" t="n"/>
-      <c r="C12" s="52" t="n"/>
-      <c r="D12" s="52" t="n"/>
-      <c r="E12" s="52" t="n"/>
-      <c r="F12" s="52" t="n"/>
-      <c r="G12" s="52" t="n"/>
-      <c r="H12" s="52" t="n"/>
-      <c r="I12" s="52" t="n"/>
-      <c r="J12" s="52" t="n"/>
-      <c r="K12" s="52" t="n"/>
-      <c r="L12" s="52" t="n"/>
-      <c r="M12" s="52" t="n"/>
-      <c r="N12" s="52" t="n"/>
-      <c r="O12" s="52" t="n"/>
-      <c r="P12" s="52" t="n"/>
-      <c r="Q12" s="59">
-        <f>IF(OR(L16="",L16="در انتظار"),"",IF(Q16="",TODAY(),Q16))</f>
-        <v/>
-      </c>
+      <c r="A12" s="79" t="n"/>
+      <c r="B12" s="79" t="n"/>
+      <c r="C12" s="79" t="n"/>
+      <c r="D12" s="79" t="n"/>
+      <c r="E12" s="79" t="n"/>
+      <c r="F12" s="79" t="n"/>
+      <c r="G12" s="79" t="n"/>
+      <c r="H12" s="79" t="n"/>
+      <c r="I12" s="79" t="n"/>
+      <c r="J12" s="79" t="n"/>
+      <c r="K12" s="79" t="n"/>
+      <c r="L12" s="79" t="n"/>
+      <c r="M12" s="79" t="n"/>
+      <c r="N12" s="79" t="n"/>
+      <c r="O12" s="79" t="n"/>
+      <c r="P12" s="79" t="n"/>
+      <c r="Q12" s="80" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="52" t="n"/>
-      <c r="B13" s="52" t="n"/>
-      <c r="C13" s="52" t="n"/>
-      <c r="D13" s="52" t="n"/>
-      <c r="E13" s="52" t="n"/>
-      <c r="F13" s="52" t="n"/>
-      <c r="G13" s="52" t="n"/>
-      <c r="H13" s="52" t="n"/>
-      <c r="I13" s="52" t="n"/>
-      <c r="J13" s="52" t="n"/>
-      <c r="K13" s="52" t="n"/>
-      <c r="L13" s="52" t="n"/>
-      <c r="M13" s="52" t="n"/>
-      <c r="N13" s="52" t="n"/>
-      <c r="O13" s="52" t="n"/>
-      <c r="P13" s="52" t="n"/>
-      <c r="Q13" s="59">
-        <f>IF(OR(L17="",L17="در انتظار"),"",IF(Q17="",TODAY(),Q17))</f>
-        <v/>
-      </c>
+      <c r="A13" s="79" t="n"/>
+      <c r="B13" s="79" t="n"/>
+      <c r="C13" s="79" t="n"/>
+      <c r="D13" s="79" t="n"/>
+      <c r="E13" s="79" t="n"/>
+      <c r="F13" s="79" t="n"/>
+      <c r="G13" s="79" t="n"/>
+      <c r="H13" s="79" t="n"/>
+      <c r="I13" s="79" t="n"/>
+      <c r="J13" s="79" t="n"/>
+      <c r="K13" s="79" t="n"/>
+      <c r="L13" s="79" t="n"/>
+      <c r="M13" s="79" t="n"/>
+      <c r="N13" s="79" t="n"/>
+      <c r="O13" s="79" t="n"/>
+      <c r="P13" s="79" t="n"/>
+      <c r="Q13" s="80" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="52" t="n"/>
-      <c r="B14" s="52" t="n"/>
-      <c r="C14" s="52" t="n"/>
-      <c r="D14" s="52" t="n"/>
-      <c r="E14" s="52" t="n"/>
-      <c r="F14" s="52" t="n"/>
-      <c r="G14" s="52" t="n"/>
-      <c r="H14" s="52" t="n"/>
-      <c r="I14" s="52" t="n"/>
-      <c r="J14" s="52" t="n"/>
-      <c r="K14" s="52" t="n"/>
-      <c r="L14" s="52" t="n"/>
-      <c r="M14" s="52" t="n"/>
-      <c r="N14" s="52" t="n"/>
-      <c r="O14" s="52" t="n"/>
-      <c r="P14" s="52" t="n"/>
-      <c r="Q14" s="59">
-        <f>IF(OR(L18="",L18="در انتظار"),"",IF(Q18="",TODAY(),Q18))</f>
-        <v/>
-      </c>
+      <c r="A14" s="79" t="n"/>
+      <c r="B14" s="79" t="n"/>
+      <c r="C14" s="79" t="n"/>
+      <c r="D14" s="79" t="n"/>
+      <c r="E14" s="79" t="n"/>
+      <c r="F14" s="79" t="n"/>
+      <c r="G14" s="79" t="n"/>
+      <c r="H14" s="79" t="n"/>
+      <c r="I14" s="79" t="n"/>
+      <c r="J14" s="79" t="n"/>
+      <c r="K14" s="79" t="n"/>
+      <c r="L14" s="79" t="n"/>
+      <c r="M14" s="79" t="n"/>
+      <c r="N14" s="79" t="n"/>
+      <c r="O14" s="79" t="n"/>
+      <c r="P14" s="79" t="n"/>
+      <c r="Q14" s="80" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="52" t="n"/>
-      <c r="B15" s="52" t="n"/>
-      <c r="C15" s="52" t="n"/>
-      <c r="D15" s="52" t="n"/>
-      <c r="E15" s="52" t="n"/>
-      <c r="F15" s="52" t="n"/>
-      <c r="G15" s="52" t="n"/>
-      <c r="H15" s="52" t="n"/>
-      <c r="I15" s="52" t="n"/>
-      <c r="J15" s="52" t="n"/>
-      <c r="K15" s="52" t="n"/>
-      <c r="L15" s="52" t="n"/>
-      <c r="M15" s="52" t="n"/>
-      <c r="N15" s="52" t="n"/>
-      <c r="O15" s="52" t="n"/>
-      <c r="P15" s="52" t="n"/>
-      <c r="Q15" s="59">
-        <f>IF(OR(L19="",L19="در انتظار"),"",IF(Q19="",TODAY(),Q19))</f>
-        <v/>
-      </c>
+      <c r="A15" s="79" t="n"/>
+      <c r="B15" s="79" t="n"/>
+      <c r="C15" s="79" t="n"/>
+      <c r="D15" s="79" t="n"/>
+      <c r="E15" s="79" t="n"/>
+      <c r="F15" s="79" t="n"/>
+      <c r="G15" s="79" t="n"/>
+      <c r="H15" s="79" t="n"/>
+      <c r="I15" s="79" t="n"/>
+      <c r="J15" s="79" t="n"/>
+      <c r="K15" s="79" t="n"/>
+      <c r="L15" s="79" t="n"/>
+      <c r="M15" s="79" t="n"/>
+      <c r="N15" s="79" t="n"/>
+      <c r="O15" s="79" t="n"/>
+      <c r="P15" s="79" t="n"/>
+      <c r="Q15" s="80" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="52" t="n"/>
-      <c r="B16" s="52" t="n"/>
-      <c r="C16" s="52" t="n"/>
-      <c r="D16" s="52" t="n"/>
-      <c r="E16" s="52" t="n"/>
-      <c r="F16" s="52" t="n"/>
-      <c r="G16" s="52" t="n"/>
-      <c r="H16" s="52" t="n"/>
-      <c r="I16" s="52" t="n"/>
-      <c r="J16" s="52" t="n"/>
-      <c r="K16" s="52" t="n"/>
-      <c r="L16" s="52" t="n"/>
-      <c r="M16" s="52" t="n"/>
-      <c r="N16" s="52" t="n"/>
-      <c r="O16" s="52" t="n"/>
-      <c r="P16" s="52" t="n"/>
-      <c r="Q16" s="59">
-        <f>IF(OR(L20="",L20="در انتظار"),"",IF(Q20="",TODAY(),Q20))</f>
-        <v/>
-      </c>
+      <c r="A16" s="79" t="n"/>
+      <c r="B16" s="79" t="n"/>
+      <c r="C16" s="79" t="n"/>
+      <c r="D16" s="79" t="n"/>
+      <c r="E16" s="79" t="n"/>
+      <c r="F16" s="79" t="n"/>
+      <c r="G16" s="79" t="n"/>
+      <c r="H16" s="79" t="n"/>
+      <c r="I16" s="79" t="n"/>
+      <c r="J16" s="79" t="n"/>
+      <c r="K16" s="79" t="n"/>
+      <c r="L16" s="79" t="n"/>
+      <c r="M16" s="79" t="n"/>
+      <c r="N16" s="79" t="n"/>
+      <c r="O16" s="79" t="n"/>
+      <c r="P16" s="79" t="n"/>
+      <c r="Q16" s="80" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="52" t="n"/>
-      <c r="B17" s="52" t="n"/>
-      <c r="C17" s="52" t="n"/>
-      <c r="D17" s="52" t="n"/>
-      <c r="E17" s="52" t="n"/>
-      <c r="F17" s="52" t="n"/>
-      <c r="G17" s="52" t="n"/>
-      <c r="H17" s="52" t="n"/>
-      <c r="I17" s="52" t="n"/>
-      <c r="J17" s="52" t="n"/>
-      <c r="K17" s="52" t="n"/>
-      <c r="L17" s="52" t="n"/>
-      <c r="M17" s="52" t="n"/>
-      <c r="N17" s="52" t="n"/>
-      <c r="O17" s="52" t="n"/>
-      <c r="P17" s="52" t="n"/>
-      <c r="Q17" s="59">
-        <f>IF(OR(L21="",L21="در انتظار"),"",IF(Q21="",TODAY(),Q21))</f>
-        <v/>
-      </c>
+      <c r="A17" s="79" t="n"/>
+      <c r="B17" s="79" t="n"/>
+      <c r="C17" s="79" t="n"/>
+      <c r="D17" s="79" t="n"/>
+      <c r="E17" s="79" t="n"/>
+      <c r="F17" s="79" t="n"/>
+      <c r="G17" s="79" t="n"/>
+      <c r="H17" s="79" t="n"/>
+      <c r="I17" s="79" t="n"/>
+      <c r="J17" s="79" t="n"/>
+      <c r="K17" s="79" t="n"/>
+      <c r="L17" s="79" t="n"/>
+      <c r="M17" s="79" t="n"/>
+      <c r="N17" s="79" t="n"/>
+      <c r="O17" s="79" t="n"/>
+      <c r="P17" s="79" t="n"/>
+      <c r="Q17" s="80" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="52" t="n"/>
-      <c r="B18" s="52" t="n"/>
-      <c r="C18" s="52" t="n"/>
-      <c r="D18" s="52" t="n"/>
-      <c r="E18" s="52" t="n"/>
-      <c r="F18" s="52" t="n"/>
-      <c r="G18" s="52" t="n"/>
-      <c r="H18" s="52" t="n"/>
-      <c r="I18" s="52" t="n"/>
-      <c r="J18" s="52" t="n"/>
-      <c r="K18" s="52" t="n"/>
-      <c r="L18" s="52" t="n"/>
-      <c r="M18" s="52" t="n"/>
-      <c r="N18" s="52" t="n"/>
-      <c r="O18" s="52" t="n"/>
-      <c r="P18" s="52" t="n"/>
-      <c r="Q18" s="59">
-        <f>IF(OR(L22="",L22="در انتظار"),"",IF(Q22="",TODAY(),Q22))</f>
-        <v/>
-      </c>
+      <c r="A18" s="79" t="n"/>
+      <c r="B18" s="79" t="n"/>
+      <c r="C18" s="79" t="n"/>
+      <c r="D18" s="79" t="n"/>
+      <c r="E18" s="79" t="n"/>
+      <c r="F18" s="79" t="n"/>
+      <c r="G18" s="79" t="n"/>
+      <c r="H18" s="79" t="n"/>
+      <c r="I18" s="79" t="n"/>
+      <c r="J18" s="79" t="n"/>
+      <c r="K18" s="79" t="n"/>
+      <c r="L18" s="79" t="n"/>
+      <c r="M18" s="79" t="n"/>
+      <c r="N18" s="79" t="n"/>
+      <c r="O18" s="79" t="n"/>
+      <c r="P18" s="79" t="n"/>
+      <c r="Q18" s="80" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="52" t="n"/>
-      <c r="B19" s="52" t="n"/>
-      <c r="C19" s="52" t="n"/>
-      <c r="D19" s="52" t="n"/>
-      <c r="E19" s="52" t="n"/>
-      <c r="F19" s="52" t="n"/>
-      <c r="G19" s="52" t="n"/>
-      <c r="H19" s="52" t="n"/>
-      <c r="I19" s="52" t="n"/>
-      <c r="J19" s="52" t="n"/>
-      <c r="K19" s="52" t="n"/>
-      <c r="L19" s="52" t="n"/>
-      <c r="M19" s="52" t="n"/>
-      <c r="N19" s="52" t="n"/>
-      <c r="O19" s="52" t="n"/>
-      <c r="P19" s="52" t="n"/>
-      <c r="Q19" s="59">
-        <f>IF(OR(L23="",L23="در انتظار"),"",IF(Q23="",TODAY(),Q23))</f>
-        <v/>
-      </c>
+      <c r="A19" s="79" t="n"/>
+      <c r="B19" s="79" t="n"/>
+      <c r="C19" s="79" t="n"/>
+      <c r="D19" s="79" t="n"/>
+      <c r="E19" s="79" t="n"/>
+      <c r="F19" s="79" t="n"/>
+      <c r="G19" s="79" t="n"/>
+      <c r="H19" s="79" t="n"/>
+      <c r="I19" s="79" t="n"/>
+      <c r="J19" s="79" t="n"/>
+      <c r="K19" s="79" t="n"/>
+      <c r="L19" s="79" t="n"/>
+      <c r="M19" s="79" t="n"/>
+      <c r="N19" s="79" t="n"/>
+      <c r="O19" s="79" t="n"/>
+      <c r="P19" s="79" t="n"/>
+      <c r="Q19" s="80" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="52" t="n"/>
-      <c r="B20" s="52" t="n"/>
-      <c r="C20" s="52" t="n"/>
-      <c r="D20" s="52" t="n"/>
-      <c r="E20" s="52" t="n"/>
-      <c r="F20" s="52" t="n"/>
-      <c r="G20" s="52" t="n"/>
-      <c r="H20" s="52" t="n"/>
-      <c r="I20" s="52" t="n"/>
-      <c r="J20" s="52" t="n"/>
-      <c r="K20" s="52" t="n"/>
-      <c r="L20" s="52" t="n"/>
-      <c r="M20" s="52" t="n"/>
-      <c r="N20" s="52" t="n"/>
-      <c r="O20" s="52" t="n"/>
-      <c r="P20" s="52" t="n"/>
-      <c r="Q20" s="59">
-        <f>IF(OR(L24="",L24="در انتظار"),"",IF(Q24="",TODAY(),Q24))</f>
-        <v/>
-      </c>
+      <c r="A20" s="79" t="n"/>
+      <c r="B20" s="79" t="n"/>
+      <c r="C20" s="79" t="n"/>
+      <c r="D20" s="79" t="n"/>
+      <c r="E20" s="79" t="n"/>
+      <c r="F20" s="79" t="n"/>
+      <c r="G20" s="79" t="n"/>
+      <c r="H20" s="79" t="n"/>
+      <c r="I20" s="79" t="n"/>
+      <c r="J20" s="79" t="n"/>
+      <c r="K20" s="79" t="n"/>
+      <c r="L20" s="79" t="n"/>
+      <c r="M20" s="79" t="n"/>
+      <c r="N20" s="79" t="n"/>
+      <c r="O20" s="79" t="n"/>
+      <c r="P20" s="79" t="n"/>
+      <c r="Q20" s="80" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="52" t="n"/>
-      <c r="B21" s="52" t="n"/>
-      <c r="C21" s="52" t="n"/>
-      <c r="D21" s="52" t="n"/>
-      <c r="E21" s="52" t="n"/>
-      <c r="F21" s="52" t="n"/>
-      <c r="G21" s="52" t="n"/>
-      <c r="H21" s="52" t="n"/>
-      <c r="I21" s="52" t="n"/>
-      <c r="J21" s="52" t="n"/>
-      <c r="K21" s="52" t="n"/>
-      <c r="L21" s="52" t="n"/>
-      <c r="M21" s="52" t="n"/>
-      <c r="N21" s="52" t="n"/>
-      <c r="O21" s="52" t="n"/>
-      <c r="P21" s="52" t="n"/>
-      <c r="Q21" s="59">
-        <f>IF(OR(L25="",L25="در انتظار"),"",IF(Q25="",TODAY(),Q25))</f>
-        <v/>
-      </c>
+      <c r="A21" s="79" t="n"/>
+      <c r="B21" s="79" t="n"/>
+      <c r="C21" s="79" t="n"/>
+      <c r="D21" s="79" t="n"/>
+      <c r="E21" s="79" t="n"/>
+      <c r="F21" s="79" t="n"/>
+      <c r="G21" s="79" t="n"/>
+      <c r="H21" s="79" t="n"/>
+      <c r="I21" s="79" t="n"/>
+      <c r="J21" s="79" t="n"/>
+      <c r="K21" s="79" t="n"/>
+      <c r="L21" s="79" t="n"/>
+      <c r="M21" s="79" t="n"/>
+      <c r="N21" s="79" t="n"/>
+      <c r="O21" s="79" t="n"/>
+      <c r="P21" s="79" t="n"/>
+      <c r="Q21" s="80" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="52" t="n"/>
-      <c r="B22" s="52" t="n"/>
-      <c r="C22" s="52" t="n"/>
-      <c r="D22" s="52" t="n"/>
-      <c r="E22" s="52" t="n"/>
-      <c r="F22" s="52" t="n"/>
-      <c r="G22" s="52" t="n"/>
-      <c r="H22" s="52" t="n"/>
-      <c r="I22" s="52" t="n"/>
-      <c r="J22" s="52" t="n"/>
-      <c r="K22" s="52" t="n"/>
-      <c r="L22" s="52" t="n"/>
-      <c r="M22" s="52" t="n"/>
-      <c r="N22" s="52" t="n"/>
-      <c r="O22" s="52" t="n"/>
-      <c r="P22" s="52" t="n"/>
-      <c r="Q22" s="59">
-        <f>IF(OR(L26="",L26="در انتظار"),"",IF(Q26="",TODAY(),Q26))</f>
-        <v/>
-      </c>
+      <c r="A22" s="79" t="n"/>
+      <c r="B22" s="79" t="n"/>
+      <c r="C22" s="79" t="n"/>
+      <c r="D22" s="79" t="n"/>
+      <c r="E22" s="79" t="n"/>
+      <c r="F22" s="79" t="n"/>
+      <c r="G22" s="79" t="n"/>
+      <c r="H22" s="79" t="n"/>
+      <c r="I22" s="79" t="n"/>
+      <c r="J22" s="79" t="n"/>
+      <c r="K22" s="79" t="n"/>
+      <c r="L22" s="79" t="n"/>
+      <c r="M22" s="79" t="n"/>
+      <c r="N22" s="79" t="n"/>
+      <c r="O22" s="79" t="n"/>
+      <c r="P22" s="79" t="n"/>
+      <c r="Q22" s="80" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="52" t="n"/>
-      <c r="B23" s="52" t="n"/>
-      <c r="C23" s="52" t="n"/>
-      <c r="D23" s="52" t="n"/>
-      <c r="E23" s="52" t="n"/>
-      <c r="F23" s="52" t="n"/>
-      <c r="G23" s="52" t="n"/>
-      <c r="H23" s="52" t="n"/>
-      <c r="I23" s="52" t="n"/>
-      <c r="J23" s="52" t="n"/>
-      <c r="K23" s="52" t="n"/>
-      <c r="L23" s="52" t="n"/>
-      <c r="M23" s="52" t="n"/>
-      <c r="N23" s="52" t="n"/>
-      <c r="O23" s="52" t="n"/>
-      <c r="P23" s="52" t="n"/>
-      <c r="Q23" s="59">
-        <f>IF(OR(L27="",L27="در انتظار"),"",IF(Q27="",TODAY(),Q27))</f>
-        <v/>
-      </c>
+      <c r="A23" s="79" t="n"/>
+      <c r="B23" s="79" t="n"/>
+      <c r="C23" s="79" t="n"/>
+      <c r="D23" s="79" t="n"/>
+      <c r="E23" s="79" t="n"/>
+      <c r="F23" s="79" t="n"/>
+      <c r="G23" s="79" t="n"/>
+      <c r="H23" s="79" t="n"/>
+      <c r="I23" s="79" t="n"/>
+      <c r="J23" s="79" t="n"/>
+      <c r="K23" s="79" t="n"/>
+      <c r="L23" s="79" t="n"/>
+      <c r="M23" s="79" t="n"/>
+      <c r="N23" s="79" t="n"/>
+      <c r="O23" s="79" t="n"/>
+      <c r="P23" s="79" t="n"/>
+      <c r="Q23" s="80" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="52" t="n"/>
-      <c r="B24" s="52" t="n"/>
-      <c r="C24" s="52" t="n"/>
-      <c r="D24" s="52" t="n"/>
-      <c r="E24" s="52" t="n"/>
-      <c r="F24" s="52" t="n"/>
-      <c r="G24" s="52" t="n"/>
-      <c r="H24" s="52" t="n"/>
-      <c r="I24" s="52" t="n"/>
-      <c r="J24" s="52" t="n"/>
-      <c r="K24" s="52" t="n"/>
-      <c r="L24" s="52" t="n"/>
-      <c r="M24" s="52" t="n"/>
-      <c r="N24" s="52" t="n"/>
-      <c r="O24" s="52" t="n"/>
-      <c r="P24" s="52" t="n"/>
-      <c r="Q24" s="59">
-        <f>IF(OR(L28="",L28="در انتظار"),"",IF(Q28="",TODAY(),Q28))</f>
-        <v/>
-      </c>
+      <c r="A24" s="79" t="n"/>
+      <c r="B24" s="79" t="n"/>
+      <c r="C24" s="79" t="n"/>
+      <c r="D24" s="79" t="n"/>
+      <c r="E24" s="79" t="n"/>
+      <c r="F24" s="79" t="n"/>
+      <c r="G24" s="79" t="n"/>
+      <c r="H24" s="79" t="n"/>
+      <c r="I24" s="79" t="n"/>
+      <c r="J24" s="79" t="n"/>
+      <c r="K24" s="79" t="n"/>
+      <c r="L24" s="79" t="n"/>
+      <c r="M24" s="79" t="n"/>
+      <c r="N24" s="79" t="n"/>
+      <c r="O24" s="79" t="n"/>
+      <c r="P24" s="79" t="n"/>
+      <c r="Q24" s="80" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="52" t="n"/>
-      <c r="B25" s="52" t="n"/>
-      <c r="C25" s="52" t="n"/>
-      <c r="D25" s="52" t="n"/>
-      <c r="E25" s="52" t="n"/>
-      <c r="F25" s="52" t="n"/>
-      <c r="G25" s="52" t="n"/>
-      <c r="H25" s="52" t="n"/>
-      <c r="I25" s="52" t="n"/>
-      <c r="J25" s="52" t="n"/>
-      <c r="K25" s="52" t="n"/>
-      <c r="L25" s="52" t="n"/>
-      <c r="M25" s="52" t="n"/>
-      <c r="N25" s="52" t="n"/>
-      <c r="O25" s="52" t="n"/>
-      <c r="P25" s="52" t="n"/>
-      <c r="Q25" s="59">
-        <f>IF(OR(L29="",L29="در انتظار"),"",IF(Q29="",TODAY(),Q29))</f>
-        <v/>
-      </c>
+      <c r="A25" s="79" t="n"/>
+      <c r="B25" s="79" t="n"/>
+      <c r="C25" s="79" t="n"/>
+      <c r="D25" s="79" t="n"/>
+      <c r="E25" s="79" t="n"/>
+      <c r="F25" s="79" t="n"/>
+      <c r="G25" s="79" t="n"/>
+      <c r="H25" s="79" t="n"/>
+      <c r="I25" s="79" t="n"/>
+      <c r="J25" s="79" t="n"/>
+      <c r="K25" s="79" t="n"/>
+      <c r="L25" s="79" t="n"/>
+      <c r="M25" s="79" t="n"/>
+      <c r="N25" s="79" t="n"/>
+      <c r="O25" s="79" t="n"/>
+      <c r="P25" s="79" t="n"/>
+      <c r="Q25" s="80" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="52" t="n"/>
-      <c r="B26" s="52" t="n"/>
-      <c r="C26" s="52" t="n"/>
-      <c r="D26" s="52" t="n"/>
-      <c r="E26" s="52" t="n"/>
-      <c r="F26" s="52" t="n"/>
-      <c r="G26" s="52" t="n"/>
-      <c r="H26" s="52" t="n"/>
-      <c r="I26" s="52" t="n"/>
-      <c r="J26" s="52" t="n"/>
-      <c r="K26" s="52" t="n"/>
-      <c r="L26" s="52" t="n"/>
-      <c r="M26" s="52" t="n"/>
-      <c r="N26" s="52" t="n"/>
-      <c r="O26" s="52" t="n"/>
-      <c r="P26" s="52" t="n"/>
-      <c r="Q26" s="59">
-        <f>IF(OR(L30="",L30="در انتظار"),"",IF(Q30="",TODAY(),Q30))</f>
-        <v/>
-      </c>
+      <c r="A26" s="79" t="n"/>
+      <c r="B26" s="79" t="n"/>
+      <c r="C26" s="79" t="n"/>
+      <c r="D26" s="79" t="n"/>
+      <c r="E26" s="79" t="n"/>
+      <c r="F26" s="79" t="n"/>
+      <c r="G26" s="79" t="n"/>
+      <c r="H26" s="79" t="n"/>
+      <c r="I26" s="79" t="n"/>
+      <c r="J26" s="79" t="n"/>
+      <c r="K26" s="79" t="n"/>
+      <c r="L26" s="79" t="n"/>
+      <c r="M26" s="79" t="n"/>
+      <c r="N26" s="79" t="n"/>
+      <c r="O26" s="79" t="n"/>
+      <c r="P26" s="79" t="n"/>
+      <c r="Q26" s="80" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="52" t="n"/>
-      <c r="B27" s="52" t="n"/>
-      <c r="C27" s="52" t="n"/>
-      <c r="D27" s="52" t="n"/>
-      <c r="E27" s="52" t="n"/>
-      <c r="F27" s="52" t="n"/>
-      <c r="G27" s="52" t="n"/>
-      <c r="H27" s="52" t="n"/>
-      <c r="I27" s="52" t="n"/>
-      <c r="J27" s="52" t="n"/>
-      <c r="K27" s="52" t="n"/>
-      <c r="L27" s="52" t="n"/>
-      <c r="M27" s="52" t="n"/>
-      <c r="N27" s="52" t="n"/>
-      <c r="O27" s="52" t="n"/>
-      <c r="P27" s="52" t="n"/>
-      <c r="Q27" s="59">
-        <f>IF(OR(L31="",L31="در انتظار"),"",IF(Q31="",TODAY(),Q31))</f>
-        <v/>
-      </c>
+      <c r="A27" s="79" t="n"/>
+      <c r="B27" s="79" t="n"/>
+      <c r="C27" s="79" t="n"/>
+      <c r="D27" s="79" t="n"/>
+      <c r="E27" s="79" t="n"/>
+      <c r="F27" s="79" t="n"/>
+      <c r="G27" s="79" t="n"/>
+      <c r="H27" s="79" t="n"/>
+      <c r="I27" s="79" t="n"/>
+      <c r="J27" s="79" t="n"/>
+      <c r="K27" s="79" t="n"/>
+      <c r="L27" s="79" t="n"/>
+      <c r="M27" s="79" t="n"/>
+      <c r="N27" s="79" t="n"/>
+      <c r="O27" s="79" t="n"/>
+      <c r="P27" s="79" t="n"/>
+      <c r="Q27" s="80" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="52" t="n"/>
-      <c r="B28" s="52" t="n"/>
-      <c r="C28" s="52" t="n"/>
-      <c r="D28" s="52" t="n"/>
-      <c r="E28" s="52" t="n"/>
-      <c r="F28" s="52" t="n"/>
-      <c r="G28" s="52" t="n"/>
-      <c r="H28" s="52" t="n"/>
-      <c r="I28" s="52" t="n"/>
-      <c r="J28" s="52" t="n"/>
-      <c r="K28" s="52" t="n"/>
-      <c r="L28" s="52" t="n"/>
-      <c r="M28" s="52" t="n"/>
-      <c r="N28" s="52" t="n"/>
-      <c r="O28" s="52" t="n"/>
-      <c r="P28" s="52" t="n"/>
-      <c r="Q28" s="59">
-        <f>IF(OR(L32="",L32="در انتظار"),"",IF(Q32="",TODAY(),Q32))</f>
-        <v/>
-      </c>
+      <c r="A28" s="79" t="n"/>
+      <c r="B28" s="79" t="n"/>
+      <c r="C28" s="79" t="n"/>
+      <c r="D28" s="79" t="n"/>
+      <c r="E28" s="79" t="n"/>
+      <c r="F28" s="79" t="n"/>
+      <c r="G28" s="79" t="n"/>
+      <c r="H28" s="79" t="n"/>
+      <c r="I28" s="79" t="n"/>
+      <c r="J28" s="79" t="n"/>
+      <c r="K28" s="79" t="n"/>
+      <c r="L28" s="79" t="n"/>
+      <c r="M28" s="79" t="n"/>
+      <c r="N28" s="79" t="n"/>
+      <c r="O28" s="79" t="n"/>
+      <c r="P28" s="79" t="n"/>
+      <c r="Q28" s="80" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="52" t="n"/>
-      <c r="B29" s="52" t="n"/>
-      <c r="C29" s="52" t="n"/>
-      <c r="D29" s="52" t="n"/>
-      <c r="E29" s="52" t="n"/>
-      <c r="F29" s="52" t="n"/>
-      <c r="G29" s="52" t="n"/>
-      <c r="H29" s="52" t="n"/>
-      <c r="I29" s="52" t="n"/>
-      <c r="J29" s="52" t="n"/>
-      <c r="K29" s="52" t="n"/>
-      <c r="L29" s="52" t="n"/>
-      <c r="M29" s="52" t="n"/>
-      <c r="N29" s="52" t="n"/>
-      <c r="O29" s="52" t="n"/>
-      <c r="P29" s="52" t="n"/>
-      <c r="Q29" s="59">
-        <f>IF(OR(L33="",L33="در انتظار"),"",IF(Q33="",TODAY(),Q33))</f>
-        <v/>
-      </c>
+      <c r="A29" s="79" t="n"/>
+      <c r="B29" s="79" t="n"/>
+      <c r="C29" s="79" t="n"/>
+      <c r="D29" s="79" t="n"/>
+      <c r="E29" s="79" t="n"/>
+      <c r="F29" s="79" t="n"/>
+      <c r="G29" s="79" t="n"/>
+      <c r="H29" s="79" t="n"/>
+      <c r="I29" s="79" t="n"/>
+      <c r="J29" s="79" t="n"/>
+      <c r="K29" s="79" t="n"/>
+      <c r="L29" s="79" t="n"/>
+      <c r="M29" s="79" t="n"/>
+      <c r="N29" s="79" t="n"/>
+      <c r="O29" s="79" t="n"/>
+      <c r="P29" s="79" t="n"/>
+      <c r="Q29" s="80" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="52" t="n"/>
-      <c r="B30" s="52" t="n"/>
-      <c r="C30" s="52" t="n"/>
-      <c r="D30" s="52" t="n"/>
-      <c r="E30" s="52" t="n"/>
-      <c r="F30" s="52" t="n"/>
-      <c r="G30" s="52" t="n"/>
-      <c r="H30" s="52" t="n"/>
-      <c r="I30" s="52" t="n"/>
-      <c r="J30" s="52" t="n"/>
-      <c r="K30" s="52" t="n"/>
-      <c r="L30" s="52" t="n"/>
-      <c r="M30" s="52" t="n"/>
-      <c r="N30" s="52" t="n"/>
-      <c r="O30" s="52" t="n"/>
-      <c r="P30" s="52" t="n"/>
-      <c r="Q30" s="59">
-        <f>IF(OR(L34="",L34="در انتظار"),"",IF(Q34="",TODAY(),Q34))</f>
-        <v/>
-      </c>
+      <c r="A30" s="79" t="n"/>
+      <c r="B30" s="79" t="n"/>
+      <c r="C30" s="79" t="n"/>
+      <c r="D30" s="79" t="n"/>
+      <c r="E30" s="79" t="n"/>
+      <c r="F30" s="79" t="n"/>
+      <c r="G30" s="79" t="n"/>
+      <c r="H30" s="79" t="n"/>
+      <c r="I30" s="79" t="n"/>
+      <c r="J30" s="79" t="n"/>
+      <c r="K30" s="79" t="n"/>
+      <c r="L30" s="79" t="n"/>
+      <c r="M30" s="79" t="n"/>
+      <c r="N30" s="79" t="n"/>
+      <c r="O30" s="79" t="n"/>
+      <c r="P30" s="79" t="n"/>
+      <c r="Q30" s="80" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="52" t="n"/>
-      <c r="B31" s="52" t="n"/>
-      <c r="C31" s="52" t="n"/>
-      <c r="D31" s="52" t="n"/>
-      <c r="E31" s="52" t="n"/>
-      <c r="F31" s="52" t="n"/>
-      <c r="G31" s="52" t="n"/>
-      <c r="H31" s="52" t="n"/>
-      <c r="I31" s="52" t="n"/>
-      <c r="J31" s="52" t="n"/>
-      <c r="K31" s="52" t="n"/>
-      <c r="L31" s="52" t="n"/>
-      <c r="M31" s="52" t="n"/>
-      <c r="N31" s="52" t="n"/>
-      <c r="O31" s="52" t="n"/>
-      <c r="P31" s="52" t="n"/>
-      <c r="Q31" s="59">
-        <f>IF(OR(L35="",L35="در انتظار"),"",IF(Q35="",TODAY(),Q35))</f>
-        <v/>
-      </c>
+      <c r="A31" s="79" t="n"/>
+      <c r="B31" s="79" t="n"/>
+      <c r="C31" s="79" t="n"/>
+      <c r="D31" s="79" t="n"/>
+      <c r="E31" s="79" t="n"/>
+      <c r="F31" s="79" t="n"/>
+      <c r="G31" s="79" t="n"/>
+      <c r="H31" s="79" t="n"/>
+      <c r="I31" s="79" t="n"/>
+      <c r="J31" s="79" t="n"/>
+      <c r="K31" s="79" t="n"/>
+      <c r="L31" s="79" t="n"/>
+      <c r="M31" s="79" t="n"/>
+      <c r="N31" s="79" t="n"/>
+      <c r="O31" s="79" t="n"/>
+      <c r="P31" s="79" t="n"/>
+      <c r="Q31" s="80" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="52" t="n"/>
-      <c r="B32" s="52" t="n"/>
-      <c r="C32" s="52" t="n"/>
-      <c r="D32" s="52" t="n"/>
-      <c r="E32" s="52" t="n"/>
-      <c r="F32" s="52" t="n"/>
-      <c r="G32" s="52" t="n"/>
-      <c r="H32" s="52" t="n"/>
-      <c r="I32" s="52" t="n"/>
-      <c r="J32" s="52" t="n"/>
-      <c r="K32" s="52" t="n"/>
-      <c r="L32" s="52" t="n"/>
-      <c r="M32" s="52" t="n"/>
-      <c r="N32" s="52" t="n"/>
-      <c r="O32" s="52" t="n"/>
-      <c r="P32" s="52" t="n"/>
-      <c r="Q32" s="59">
-        <f>IF(OR(L36="",L36="در انتظار"),"",IF(Q36="",TODAY(),Q36))</f>
-        <v/>
-      </c>
+      <c r="A32" s="79" t="n"/>
+      <c r="B32" s="79" t="n"/>
+      <c r="C32" s="79" t="n"/>
+      <c r="D32" s="79" t="n"/>
+      <c r="E32" s="79" t="n"/>
+      <c r="F32" s="79" t="n"/>
+      <c r="G32" s="79" t="n"/>
+      <c r="H32" s="79" t="n"/>
+      <c r="I32" s="79" t="n"/>
+      <c r="J32" s="79" t="n"/>
+      <c r="K32" s="79" t="n"/>
+      <c r="L32" s="79" t="n"/>
+      <c r="M32" s="79" t="n"/>
+      <c r="N32" s="79" t="n"/>
+      <c r="O32" s="79" t="n"/>
+      <c r="P32" s="79" t="n"/>
+      <c r="Q32" s="80" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="52" t="n"/>
-      <c r="B33" s="52" t="n"/>
-      <c r="C33" s="52" t="n"/>
-      <c r="D33" s="52" t="n"/>
-      <c r="E33" s="52" t="n"/>
-      <c r="F33" s="52" t="n"/>
-      <c r="G33" s="52" t="n"/>
-      <c r="H33" s="52" t="n"/>
-      <c r="I33" s="52" t="n"/>
-      <c r="J33" s="52" t="n"/>
-      <c r="K33" s="52" t="n"/>
-      <c r="L33" s="52" t="n"/>
-      <c r="M33" s="52" t="n"/>
-      <c r="N33" s="52" t="n"/>
-      <c r="O33" s="52" t="n"/>
-      <c r="P33" s="52" t="n"/>
-      <c r="Q33" s="59">
-        <f>IF(OR(L37="",L37="در انتظار"),"",IF(Q37="",TODAY(),Q37))</f>
-        <v/>
-      </c>
+      <c r="A33" s="79" t="n"/>
+      <c r="B33" s="79" t="n"/>
+      <c r="C33" s="79" t="n"/>
+      <c r="D33" s="79" t="n"/>
+      <c r="E33" s="79" t="n"/>
+      <c r="F33" s="79" t="n"/>
+      <c r="G33" s="79" t="n"/>
+      <c r="H33" s="79" t="n"/>
+      <c r="I33" s="79" t="n"/>
+      <c r="J33" s="79" t="n"/>
+      <c r="K33" s="79" t="n"/>
+      <c r="L33" s="79" t="n"/>
+      <c r="M33" s="79" t="n"/>
+      <c r="N33" s="79" t="n"/>
+      <c r="O33" s="79" t="n"/>
+      <c r="P33" s="79" t="n"/>
+      <c r="Q33" s="80" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="52" t="n"/>
-      <c r="B34" s="52" t="n"/>
-      <c r="C34" s="52" t="n"/>
-      <c r="D34" s="52" t="n"/>
-      <c r="E34" s="52" t="n"/>
-      <c r="F34" s="52" t="n"/>
-      <c r="G34" s="52" t="n"/>
-      <c r="H34" s="52" t="n"/>
-      <c r="I34" s="52" t="n"/>
-      <c r="J34" s="52" t="n"/>
-      <c r="K34" s="52" t="n"/>
-      <c r="L34" s="52" t="n"/>
-      <c r="M34" s="52" t="n"/>
-      <c r="N34" s="52" t="n"/>
-      <c r="O34" s="52" t="n"/>
-      <c r="P34" s="52" t="n"/>
-      <c r="Q34" s="59">
-        <f>IF(OR(L38="",L38="در انتظار"),"",IF(Q38="",TODAY(),Q38))</f>
-        <v/>
-      </c>
+      <c r="A34" s="79" t="n"/>
+      <c r="B34" s="79" t="n"/>
+      <c r="C34" s="79" t="n"/>
+      <c r="D34" s="79" t="n"/>
+      <c r="E34" s="79" t="n"/>
+      <c r="F34" s="79" t="n"/>
+      <c r="G34" s="79" t="n"/>
+      <c r="H34" s="79" t="n"/>
+      <c r="I34" s="79" t="n"/>
+      <c r="J34" s="79" t="n"/>
+      <c r="K34" s="79" t="n"/>
+      <c r="L34" s="79" t="n"/>
+      <c r="M34" s="79" t="n"/>
+      <c r="N34" s="79" t="n"/>
+      <c r="O34" s="79" t="n"/>
+      <c r="P34" s="79" t="n"/>
+      <c r="Q34" s="80" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="52" t="n"/>
-      <c r="B35" s="52" t="n"/>
-      <c r="C35" s="52" t="n"/>
-      <c r="D35" s="52" t="n"/>
-      <c r="E35" s="52" t="n"/>
-      <c r="F35" s="52" t="n"/>
-      <c r="G35" s="52" t="n"/>
-      <c r="H35" s="52" t="n"/>
-      <c r="I35" s="52" t="n"/>
-      <c r="J35" s="52" t="n"/>
-      <c r="K35" s="52" t="n"/>
-      <c r="L35" s="52" t="n"/>
-      <c r="M35" s="52" t="n"/>
-      <c r="N35" s="52" t="n"/>
-      <c r="O35" s="52" t="n"/>
-      <c r="P35" s="52" t="n"/>
-      <c r="Q35" s="59">
-        <f>IF(OR(L39="",L39="در انتظار"),"",IF(Q39="",TODAY(),Q39))</f>
-        <v/>
-      </c>
+      <c r="A35" s="79" t="n"/>
+      <c r="B35" s="79" t="n"/>
+      <c r="C35" s="79" t="n"/>
+      <c r="D35" s="79" t="n"/>
+      <c r="E35" s="79" t="n"/>
+      <c r="F35" s="79" t="n"/>
+      <c r="G35" s="79" t="n"/>
+      <c r="H35" s="79" t="n"/>
+      <c r="I35" s="79" t="n"/>
+      <c r="J35" s="79" t="n"/>
+      <c r="K35" s="79" t="n"/>
+      <c r="L35" s="79" t="n"/>
+      <c r="M35" s="79" t="n"/>
+      <c r="N35" s="79" t="n"/>
+      <c r="O35" s="79" t="n"/>
+      <c r="P35" s="79" t="n"/>
+      <c r="Q35" s="80" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="52" t="n"/>
-      <c r="B36" s="52" t="n"/>
-      <c r="C36" s="52" t="n"/>
-      <c r="D36" s="52" t="n"/>
-      <c r="E36" s="52" t="n"/>
-      <c r="F36" s="52" t="n"/>
-      <c r="G36" s="52" t="n"/>
-      <c r="H36" s="52" t="n"/>
-      <c r="I36" s="52" t="n"/>
-      <c r="J36" s="52" t="n"/>
-      <c r="K36" s="52" t="n"/>
-      <c r="L36" s="52" t="n"/>
-      <c r="M36" s="52" t="n"/>
-      <c r="N36" s="52" t="n"/>
-      <c r="O36" s="52" t="n"/>
-      <c r="P36" s="52" t="n"/>
-      <c r="Q36" s="59">
-        <f>IF(OR(L40="",L40="در انتظار"),"",IF(Q40="",TODAY(),Q40))</f>
-        <v/>
-      </c>
+      <c r="A36" s="79" t="n"/>
+      <c r="B36" s="79" t="n"/>
+      <c r="C36" s="79" t="n"/>
+      <c r="D36" s="79" t="n"/>
+      <c r="E36" s="79" t="n"/>
+      <c r="F36" s="79" t="n"/>
+      <c r="G36" s="79" t="n"/>
+      <c r="H36" s="79" t="n"/>
+      <c r="I36" s="79" t="n"/>
+      <c r="J36" s="79" t="n"/>
+      <c r="K36" s="79" t="n"/>
+      <c r="L36" s="79" t="n"/>
+      <c r="M36" s="79" t="n"/>
+      <c r="N36" s="79" t="n"/>
+      <c r="O36" s="79" t="n"/>
+      <c r="P36" s="79" t="n"/>
+      <c r="Q36" s="80" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="52" t="n"/>
-      <c r="B37" s="52" t="n"/>
-      <c r="C37" s="52" t="n"/>
-      <c r="D37" s="52" t="n"/>
-      <c r="E37" s="52" t="n"/>
-      <c r="F37" s="52" t="n"/>
-      <c r="G37" s="52" t="n"/>
-      <c r="H37" s="52" t="n"/>
-      <c r="I37" s="52" t="n"/>
-      <c r="J37" s="52" t="n"/>
-      <c r="K37" s="52" t="n"/>
-      <c r="L37" s="52" t="n"/>
-      <c r="M37" s="52" t="n"/>
-      <c r="N37" s="52" t="n"/>
-      <c r="O37" s="52" t="n"/>
-      <c r="P37" s="52" t="n"/>
-      <c r="Q37" s="59">
-        <f>IF(OR(L41="",L41="در انتظار"),"",IF(Q41="",TODAY(),Q41))</f>
-        <v/>
-      </c>
+      <c r="A37" s="79" t="n"/>
+      <c r="B37" s="79" t="n"/>
+      <c r="C37" s="79" t="n"/>
+      <c r="D37" s="79" t="n"/>
+      <c r="E37" s="79" t="n"/>
+      <c r="F37" s="79" t="n"/>
+      <c r="G37" s="79" t="n"/>
+      <c r="H37" s="79" t="n"/>
+      <c r="I37" s="79" t="n"/>
+      <c r="J37" s="79" t="n"/>
+      <c r="K37" s="79" t="n"/>
+      <c r="L37" s="79" t="n"/>
+      <c r="M37" s="79" t="n"/>
+      <c r="N37" s="79" t="n"/>
+      <c r="O37" s="79" t="n"/>
+      <c r="P37" s="79" t="n"/>
+      <c r="Q37" s="80" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="52" t="n"/>
-      <c r="B38" s="52" t="n"/>
-      <c r="C38" s="52" t="n"/>
-      <c r="D38" s="52" t="n"/>
-      <c r="E38" s="52" t="n"/>
-      <c r="F38" s="52" t="n"/>
-      <c r="G38" s="52" t="n"/>
-      <c r="H38" s="52" t="n"/>
-      <c r="I38" s="52" t="n"/>
-      <c r="J38" s="52" t="n"/>
-      <c r="K38" s="52" t="n"/>
-      <c r="L38" s="52" t="n"/>
-      <c r="M38" s="52" t="n"/>
-      <c r="N38" s="52" t="n"/>
-      <c r="O38" s="52" t="n"/>
-      <c r="P38" s="52" t="n"/>
-      <c r="Q38" s="59">
-        <f>IF(OR(L42="",L42="در انتظار"),"",IF(Q42="",TODAY(),Q42))</f>
-        <v/>
-      </c>
+      <c r="A38" s="79" t="n"/>
+      <c r="B38" s="79" t="n"/>
+      <c r="C38" s="79" t="n"/>
+      <c r="D38" s="79" t="n"/>
+      <c r="E38" s="79" t="n"/>
+      <c r="F38" s="79" t="n"/>
+      <c r="G38" s="79" t="n"/>
+      <c r="H38" s="79" t="n"/>
+      <c r="I38" s="79" t="n"/>
+      <c r="J38" s="79" t="n"/>
+      <c r="K38" s="79" t="n"/>
+      <c r="L38" s="79" t="n"/>
+      <c r="M38" s="79" t="n"/>
+      <c r="N38" s="79" t="n"/>
+      <c r="O38" s="79" t="n"/>
+      <c r="P38" s="79" t="n"/>
+      <c r="Q38" s="80" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="52" t="n"/>
-      <c r="B39" s="52" t="n"/>
-      <c r="C39" s="52" t="n"/>
-      <c r="D39" s="52" t="n"/>
-      <c r="E39" s="52" t="n"/>
-      <c r="F39" s="52" t="n"/>
-      <c r="G39" s="52" t="n"/>
-      <c r="H39" s="52" t="n"/>
-      <c r="I39" s="52" t="n"/>
-      <c r="J39" s="52" t="n"/>
-      <c r="K39" s="52" t="n"/>
-      <c r="L39" s="52" t="n"/>
-      <c r="M39" s="52" t="n"/>
-      <c r="N39" s="52" t="n"/>
-      <c r="O39" s="52" t="n"/>
-      <c r="P39" s="52" t="n"/>
-      <c r="Q39" s="59">
-        <f>IF(OR(L43="",L43="در انتظار"),"",IF(Q43="",TODAY(),Q43))</f>
-        <v/>
-      </c>
+      <c r="A39" s="79" t="n"/>
+      <c r="B39" s="79" t="n"/>
+      <c r="C39" s="79" t="n"/>
+      <c r="D39" s="79" t="n"/>
+      <c r="E39" s="79" t="n"/>
+      <c r="F39" s="79" t="n"/>
+      <c r="G39" s="79" t="n"/>
+      <c r="H39" s="79" t="n"/>
+      <c r="I39" s="79" t="n"/>
+      <c r="J39" s="79" t="n"/>
+      <c r="K39" s="79" t="n"/>
+      <c r="L39" s="79" t="n"/>
+      <c r="M39" s="79" t="n"/>
+      <c r="N39" s="79" t="n"/>
+      <c r="O39" s="79" t="n"/>
+      <c r="P39" s="79" t="n"/>
+      <c r="Q39" s="80" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="52" t="n"/>
-      <c r="B40" s="52" t="n"/>
-      <c r="C40" s="52" t="n"/>
-      <c r="D40" s="52" t="n"/>
-      <c r="E40" s="52" t="n"/>
-      <c r="F40" s="52" t="n"/>
-      <c r="G40" s="52" t="n"/>
-      <c r="H40" s="52" t="n"/>
-      <c r="I40" s="52" t="n"/>
-      <c r="J40" s="52" t="n"/>
-      <c r="K40" s="52" t="n"/>
-      <c r="L40" s="52" t="n"/>
-      <c r="M40" s="52" t="n"/>
-      <c r="N40" s="52" t="n"/>
-      <c r="O40" s="52" t="n"/>
-      <c r="P40" s="52" t="n"/>
-      <c r="Q40" s="59">
-        <f>IF(OR(L44="",L44="در انتظار"),"",IF(Q44="",TODAY(),Q44))</f>
-        <v/>
-      </c>
+      <c r="A40" s="79" t="n"/>
+      <c r="B40" s="79" t="n"/>
+      <c r="C40" s="79" t="n"/>
+      <c r="D40" s="79" t="n"/>
+      <c r="E40" s="79" t="n"/>
+      <c r="F40" s="79" t="n"/>
+      <c r="G40" s="79" t="n"/>
+      <c r="H40" s="79" t="n"/>
+      <c r="I40" s="79" t="n"/>
+      <c r="J40" s="79" t="n"/>
+      <c r="K40" s="79" t="n"/>
+      <c r="L40" s="79" t="n"/>
+      <c r="M40" s="79" t="n"/>
+      <c r="N40" s="79" t="n"/>
+      <c r="O40" s="79" t="n"/>
+      <c r="P40" s="79" t="n"/>
+      <c r="Q40" s="80" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="52" t="n"/>
-      <c r="B41" s="52" t="n"/>
-      <c r="C41" s="52" t="n"/>
-      <c r="D41" s="52" t="n"/>
-      <c r="E41" s="52" t="n"/>
-      <c r="F41" s="52" t="n"/>
-      <c r="G41" s="52" t="n"/>
-      <c r="H41" s="52" t="n"/>
-      <c r="I41" s="52" t="n"/>
-      <c r="J41" s="52" t="n"/>
-      <c r="K41" s="52" t="n"/>
-      <c r="L41" s="52" t="n"/>
-      <c r="M41" s="52" t="n"/>
-      <c r="N41" s="52" t="n"/>
-      <c r="O41" s="52" t="n"/>
-      <c r="P41" s="52" t="n"/>
-      <c r="Q41" s="59">
-        <f>IF(OR(L45="",L45="در انتظار"),"",IF(Q45="",TODAY(),Q45))</f>
-        <v/>
-      </c>
+      <c r="A41" s="79" t="n"/>
+      <c r="B41" s="79" t="n"/>
+      <c r="C41" s="79" t="n"/>
+      <c r="D41" s="79" t="n"/>
+      <c r="E41" s="79" t="n"/>
+      <c r="F41" s="79" t="n"/>
+      <c r="G41" s="79" t="n"/>
+      <c r="H41" s="79" t="n"/>
+      <c r="I41" s="79" t="n"/>
+      <c r="J41" s="79" t="n"/>
+      <c r="K41" s="79" t="n"/>
+      <c r="L41" s="79" t="n"/>
+      <c r="M41" s="79" t="n"/>
+      <c r="N41" s="79" t="n"/>
+      <c r="O41" s="79" t="n"/>
+      <c r="P41" s="79" t="n"/>
+      <c r="Q41" s="80" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="52" t="n"/>
-      <c r="B42" s="52" t="n"/>
-      <c r="C42" s="52" t="n"/>
-      <c r="D42" s="52" t="n"/>
-      <c r="E42" s="52" t="n"/>
-      <c r="F42" s="52" t="n"/>
-      <c r="G42" s="52" t="n"/>
-      <c r="H42" s="52" t="n"/>
-      <c r="I42" s="52" t="n"/>
-      <c r="J42" s="52" t="n"/>
-      <c r="K42" s="52" t="n"/>
-      <c r="L42" s="52" t="n"/>
-      <c r="M42" s="52" t="n"/>
-      <c r="N42" s="52" t="n"/>
-      <c r="O42" s="52" t="n"/>
-      <c r="P42" s="52" t="n"/>
-      <c r="Q42" s="59">
-        <f>IF(OR(L46="",L46="در انتظار"),"",IF(Q46="",TODAY(),Q46))</f>
-        <v/>
-      </c>
+      <c r="A42" s="79" t="n"/>
+      <c r="B42" s="79" t="n"/>
+      <c r="C42" s="79" t="n"/>
+      <c r="D42" s="79" t="n"/>
+      <c r="E42" s="79" t="n"/>
+      <c r="F42" s="79" t="n"/>
+      <c r="G42" s="79" t="n"/>
+      <c r="H42" s="79" t="n"/>
+      <c r="I42" s="79" t="n"/>
+      <c r="J42" s="79" t="n"/>
+      <c r="K42" s="79" t="n"/>
+      <c r="L42" s="79" t="n"/>
+      <c r="M42" s="79" t="n"/>
+      <c r="N42" s="79" t="n"/>
+      <c r="O42" s="79" t="n"/>
+      <c r="P42" s="79" t="n"/>
+      <c r="Q42" s="80" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="52" t="n"/>
-      <c r="B43" s="52" t="n"/>
-      <c r="C43" s="52" t="n"/>
-      <c r="D43" s="52" t="n"/>
-      <c r="E43" s="52" t="n"/>
-      <c r="F43" s="52" t="n"/>
-      <c r="G43" s="52" t="n"/>
-      <c r="H43" s="52" t="n"/>
-      <c r="I43" s="52" t="n"/>
-      <c r="J43" s="52" t="n"/>
-      <c r="K43" s="52" t="n"/>
-      <c r="L43" s="52" t="n"/>
-      <c r="M43" s="52" t="n"/>
-      <c r="N43" s="52" t="n"/>
-      <c r="O43" s="52" t="n"/>
-      <c r="P43" s="52" t="n"/>
-      <c r="Q43" s="59">
-        <f>IF(OR(L47="",L47="در انتظار"),"",IF(Q47="",TODAY(),Q47))</f>
-        <v/>
-      </c>
+      <c r="A43" s="79" t="n"/>
+      <c r="B43" s="79" t="n"/>
+      <c r="C43" s="79" t="n"/>
+      <c r="D43" s="79" t="n"/>
+      <c r="E43" s="79" t="n"/>
+      <c r="F43" s="79" t="n"/>
+      <c r="G43" s="79" t="n"/>
+      <c r="H43" s="79" t="n"/>
+      <c r="I43" s="79" t="n"/>
+      <c r="J43" s="79" t="n"/>
+      <c r="K43" s="79" t="n"/>
+      <c r="L43" s="79" t="n"/>
+      <c r="M43" s="79" t="n"/>
+      <c r="N43" s="79" t="n"/>
+      <c r="O43" s="79" t="n"/>
+      <c r="P43" s="79" t="n"/>
+      <c r="Q43" s="80" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="52" t="n"/>
-      <c r="B44" s="52" t="n"/>
-      <c r="C44" s="52" t="n"/>
-      <c r="D44" s="52" t="n"/>
-      <c r="E44" s="52" t="n"/>
-      <c r="F44" s="52" t="n"/>
-      <c r="G44" s="52" t="n"/>
-      <c r="H44" s="52" t="n"/>
-      <c r="I44" s="52" t="n"/>
-      <c r="J44" s="52" t="n"/>
-      <c r="K44" s="52" t="n"/>
-      <c r="L44" s="52" t="n"/>
-      <c r="M44" s="52" t="n"/>
-      <c r="N44" s="52" t="n"/>
-      <c r="O44" s="52" t="n"/>
-      <c r="P44" s="52" t="n"/>
-      <c r="Q44" s="59">
-        <f>IF(OR(L48="",L48="در انتظار"),"",IF(Q48="",TODAY(),Q48))</f>
-        <v/>
-      </c>
+      <c r="A44" s="79" t="n"/>
+      <c r="B44" s="79" t="n"/>
+      <c r="C44" s="79" t="n"/>
+      <c r="D44" s="79" t="n"/>
+      <c r="E44" s="79" t="n"/>
+      <c r="F44" s="79" t="n"/>
+      <c r="G44" s="79" t="n"/>
+      <c r="H44" s="79" t="n"/>
+      <c r="I44" s="79" t="n"/>
+      <c r="J44" s="79" t="n"/>
+      <c r="K44" s="79" t="n"/>
+      <c r="L44" s="79" t="n"/>
+      <c r="M44" s="79" t="n"/>
+      <c r="N44" s="79" t="n"/>
+      <c r="O44" s="79" t="n"/>
+      <c r="P44" s="79" t="n"/>
+      <c r="Q44" s="80" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="52" t="n"/>
-      <c r="B45" s="52" t="n"/>
-      <c r="C45" s="52" t="n"/>
-      <c r="D45" s="52" t="n"/>
-      <c r="E45" s="52" t="n"/>
-      <c r="F45" s="52" t="n"/>
-      <c r="G45" s="52" t="n"/>
-      <c r="H45" s="52" t="n"/>
-      <c r="I45" s="52" t="n"/>
-      <c r="J45" s="52" t="n"/>
-      <c r="K45" s="52" t="n"/>
-      <c r="L45" s="52" t="n"/>
-      <c r="M45" s="52" t="n"/>
-      <c r="N45" s="52" t="n"/>
-      <c r="O45" s="52" t="n"/>
-      <c r="P45" s="52" t="n"/>
-      <c r="Q45" s="59">
-        <f>IF(OR(L49="",L49="در انتظار"),"",IF(Q49="",TODAY(),Q49))</f>
-        <v/>
-      </c>
+      <c r="A45" s="79" t="n"/>
+      <c r="B45" s="79" t="n"/>
+      <c r="C45" s="79" t="n"/>
+      <c r="D45" s="79" t="n"/>
+      <c r="E45" s="79" t="n"/>
+      <c r="F45" s="79" t="n"/>
+      <c r="G45" s="79" t="n"/>
+      <c r="H45" s="79" t="n"/>
+      <c r="I45" s="79" t="n"/>
+      <c r="J45" s="79" t="n"/>
+      <c r="K45" s="79" t="n"/>
+      <c r="L45" s="79" t="n"/>
+      <c r="M45" s="79" t="n"/>
+      <c r="N45" s="79" t="n"/>
+      <c r="O45" s="79" t="n"/>
+      <c r="P45" s="79" t="n"/>
+      <c r="Q45" s="80" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="52" t="n"/>
-      <c r="B46" s="52" t="n"/>
-      <c r="C46" s="52" t="n"/>
-      <c r="D46" s="52" t="n"/>
-      <c r="E46" s="52" t="n"/>
-      <c r="F46" s="52" t="n"/>
-      <c r="G46" s="52" t="n"/>
-      <c r="H46" s="52" t="n"/>
-      <c r="I46" s="52" t="n"/>
-      <c r="J46" s="52" t="n"/>
-      <c r="K46" s="52" t="n"/>
-      <c r="L46" s="52" t="n"/>
-      <c r="M46" s="52" t="n"/>
-      <c r="N46" s="52" t="n"/>
-      <c r="O46" s="52" t="n"/>
-      <c r="P46" s="52" t="n"/>
-      <c r="Q46" s="59">
-        <f>IF(OR(L50="",L50="در انتظار"),"",IF(Q50="",TODAY(),Q50))</f>
-        <v/>
-      </c>
+      <c r="A46" s="79" t="n"/>
+      <c r="B46" s="79" t="n"/>
+      <c r="C46" s="79" t="n"/>
+      <c r="D46" s="79" t="n"/>
+      <c r="E46" s="79" t="n"/>
+      <c r="F46" s="79" t="n"/>
+      <c r="G46" s="79" t="n"/>
+      <c r="H46" s="79" t="n"/>
+      <c r="I46" s="79" t="n"/>
+      <c r="J46" s="79" t="n"/>
+      <c r="K46" s="79" t="n"/>
+      <c r="L46" s="79" t="n"/>
+      <c r="M46" s="79" t="n"/>
+      <c r="N46" s="79" t="n"/>
+      <c r="O46" s="79" t="n"/>
+      <c r="P46" s="79" t="n"/>
+      <c r="Q46" s="80" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q47"/>
@@ -2170,10 +2016,10 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5:C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$B$9:$B$11</formula1>
     </dataValidation>
-    <dataValidation sqref="L5:L90" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" prompt="وضعیت تست را از فهرست انتخاب کنید" type="list">
+    <dataValidation sqref="L5:L6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>='فهرست‌ها'!$A$2:$A$7</formula1>
     </dataValidation>
   </dataValidations>
@@ -3060,10 +2906,10 @@
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Protection</t>
         </is>
       </c>
-      <c r="B1" s="69" t="n"/>
-      <c r="C1" s="69" t="n"/>
-      <c r="D1" s="69" t="n"/>
-      <c r="E1" s="70" t="n"/>
+      <c r="B1" s="39" t="n"/>
+      <c r="C1" s="39" t="n"/>
+      <c r="D1" s="39" t="n"/>
+      <c r="E1" s="40" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="52" t="n"/>
@@ -3224,18 +3070,6 @@
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Protection</t>
         </is>
       </c>
-      <c r="B1" s="52" t="n"/>
-      <c r="C1" s="52" t="n"/>
-      <c r="D1" s="52" t="n"/>
-      <c r="E1" s="52" t="n"/>
-      <c r="F1" s="52" t="n"/>
-      <c r="G1" s="52" t="n"/>
-      <c r="H1" s="52" t="n"/>
-      <c r="I1" s="52" t="n"/>
-      <c r="J1" s="52" t="n"/>
-      <c r="K1" s="52" t="n"/>
-      <c r="L1" s="52" t="n"/>
-      <c r="M1" s="52" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="49" t="inlineStr">
@@ -3243,18 +3077,18 @@
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
       </c>
-      <c r="B2" s="69" t="n"/>
-      <c r="C2" s="69" t="n"/>
-      <c r="D2" s="69" t="n"/>
-      <c r="E2" s="69" t="n"/>
-      <c r="F2" s="69" t="n"/>
-      <c r="G2" s="69" t="n"/>
-      <c r="H2" s="69" t="n"/>
-      <c r="I2" s="69" t="n"/>
-      <c r="J2" s="69" t="n"/>
-      <c r="K2" s="69" t="n"/>
-      <c r="L2" s="69" t="n"/>
-      <c r="M2" s="70" t="n"/>
+      <c r="B2" s="39" t="n"/>
+      <c r="C2" s="39" t="n"/>
+      <c r="D2" s="39" t="n"/>
+      <c r="E2" s="39" t="n"/>
+      <c r="F2" s="39" t="n"/>
+      <c r="G2" s="39" t="n"/>
+      <c r="H2" s="39" t="n"/>
+      <c r="I2" s="39" t="n"/>
+      <c r="J2" s="39" t="n"/>
+      <c r="K2" s="39" t="n"/>
+      <c r="L2" s="39" t="n"/>
+      <c r="M2" s="40" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="71" t="inlineStr">
@@ -3353,8 +3187,6 @@
           <t>تأیید نهایی اعتبارسنجی — ماژول Protection</t>
         </is>
       </c>
-      <c r="B1" s="52" t="n"/>
-      <c r="C1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="48" t="inlineStr">
@@ -3362,8 +3194,6 @@
           <t>این صفحه فقط پس از تکمیل تست‌ها و بسته‌شدن ایرادها پر می‌شود.</t>
         </is>
       </c>
-      <c r="B2" s="52" t="n"/>
-      <c r="C2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="48" t="inlineStr">
@@ -3371,8 +3201,6 @@
           <t>مشخصات تست</t>
         </is>
       </c>
-      <c r="B3" s="52" t="n"/>
-      <c r="C3" s="52" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="48" t="inlineStr">
@@ -3757,8 +3585,6 @@
           <t>ماشین حالت ماژول نگهبان اعتبار (Protection)</t>
         </is>
       </c>
-      <c r="B1" s="52" t="n"/>
-      <c r="C1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="52" t="n"/>
@@ -3865,22 +3691,6 @@
           <t>برنامهٔ تست آزمایشگاهی — ماژول Protection</t>
         </is>
       </c>
-      <c r="B1" s="52" t="n"/>
-      <c r="C1" s="52" t="n"/>
-      <c r="D1" s="52" t="n"/>
-      <c r="E1" s="52" t="n"/>
-      <c r="F1" s="52" t="n"/>
-      <c r="G1" s="52" t="n"/>
-      <c r="H1" s="52" t="n"/>
-      <c r="I1" s="52" t="n"/>
-      <c r="J1" s="52" t="n"/>
-      <c r="K1" s="52" t="n"/>
-      <c r="L1" s="52" t="n"/>
-      <c r="M1" s="52" t="n"/>
-      <c r="N1" s="52" t="n"/>
-      <c r="O1" s="52" t="n"/>
-      <c r="P1" s="52" t="n"/>
-      <c r="Q1" s="52" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="48" t="inlineStr">
@@ -3888,22 +3698,6 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
-      <c r="B2" s="52" t="n"/>
-      <c r="C2" s="52" t="n"/>
-      <c r="D2" s="52" t="n"/>
-      <c r="E2" s="52" t="n"/>
-      <c r="F2" s="52" t="n"/>
-      <c r="G2" s="52" t="n"/>
-      <c r="H2" s="52" t="n"/>
-      <c r="I2" s="52" t="n"/>
-      <c r="J2" s="52" t="n"/>
-      <c r="K2" s="52" t="n"/>
-      <c r="L2" s="52" t="n"/>
-      <c r="M2" s="52" t="n"/>
-      <c r="N2" s="52" t="n"/>
-      <c r="O2" s="52" t="n"/>
-      <c r="P2" s="52" t="n"/>
-      <c r="Q2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="48" t="inlineStr">
@@ -3911,22 +3705,6 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
-      <c r="B3" s="52" t="n"/>
-      <c r="C3" s="52" t="n"/>
-      <c r="D3" s="52" t="n"/>
-      <c r="E3" s="52" t="n"/>
-      <c r="F3" s="52" t="n"/>
-      <c r="G3" s="52" t="n"/>
-      <c r="H3" s="52" t="n"/>
-      <c r="I3" s="52" t="n"/>
-      <c r="J3" s="52" t="n"/>
-      <c r="K3" s="52" t="n"/>
-      <c r="L3" s="52" t="n"/>
-      <c r="M3" s="52" t="n"/>
-      <c r="N3" s="52" t="n"/>
-      <c r="O3" s="52" t="n"/>
-      <c r="P3" s="52" t="n"/>
-      <c r="Q3" s="52" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="49" t="inlineStr">

--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -942,6 +942,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="78" t="inlineStr">
         <is>

--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -897,7 +897,8 @@
     <row r="2">
       <c r="A2" s="48" t="inlineStr">
         <is>
-          <t>Protection | اسکلت حفاظت (MODULE_PROTECTION=0) — FAULT_ADC به‌صورت وضعیت لحظه‌ای</t>
+          <t>Protection | این ماژول فعلاً در برنامه خاموش است (MODULE_PROTECTION=0).
+فقط بیت خطای ADC (FAULT_ADC) را نگه می‌دارد و آن هم لحظه‌ای است.</t>
         </is>
       </c>
     </row>
@@ -914,21 +915,26 @@
     <row r="5">
       <c r="A5" s="48" t="inlineStr">
         <is>
-          <t>ماژول در build فعال نیست؛ تنها رفتار تعریف‌شده: Set بیت FAULT_ADC با snapshot نامعتبر و Clear آن با snapshot معتبر (لحظه‌ای، نه latch).</t>
+          <t>این ماژول در بیلد فعلی فعال نیست.
+تنها رفتار مشخصش این است:
+اگر دادهٔ اندازه‌گیری نامعتبر شود، بیت FAULT_ADC ست می‌شود.
+اگر داده معتبر شود، بیت خودش پاک می‌شود.
+یعنی قفل نمی‌ماند؛ لحظه‌ای است.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="48" t="inlineStr">
         <is>
-          <t>ایراد قدیمی «latch ابدی FAULT_ADC در بوت» در ممیزی ۲۰۲۶-۰۹-۲۲ اصلاح شد؛ Changeover دیگر در بوت در FAULT گیر نمی‌کند.</t>
+          <t>ایراد قدیمی این بود که بیت FAULT_ADC موقع روشن‌شدن برای همیشه قفل می‌ماند.
+در ممیزی ۲۰۲۶-۰۹-۲۲ درست شد. حالا Changeover موقع روشن‌شدن در وضعیت خطا گیر نمی‌کند.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="48" t="inlineStr">
         <is>
-          <t>فعال‌سازی آیندهٔ حفاظت کامل (اضافه‌جریان/باتری ضعیف) با MODULE_PROTECTION=1 و به دستور کاربر.</t>
+          <t>حفاظت کامل (اضافه‌جریان و باتری ضعیف) بعداً و فقط با دستور کاربر فعال می‌شود (MODULE_PROTECTION=1).</t>
         </is>
       </c>
     </row>
@@ -938,7 +944,8 @@
     <row r="9">
       <c r="A9" s="50" t="inlineStr">
         <is>
-          <t>یادداشت: تست‌های PR-002/PR-003 به بیلد تستی با MODULE_PROTECTION=1 نیاز دارند؛ در بیلد فعلی فقط PR-001 قابل اجراست.</t>
+          <t>یادداشت: تست‌های PR-002 و PR-003 به یک بیلد تستی نیاز دارند که در آن MODULE_PROTECTION=1 باشد.
+در بیلد فعلی فقط تست PR-001 اجرا می‌شود.</t>
         </is>
       </c>
     </row>
@@ -946,8 +953,12 @@
     <row r="11">
       <c r="A11" s="78" t="inlineStr">
         <is>
-          <t>اولویت تست‌های عملی: «بالا» یعنی رفتار اصلی‌ای که در کار عادی دستگاه می‌بینید (روشن‌شدن، شروع و پایان شارژ، چهره‌های اصلی چراغ‌ها، رفتن تغذیه روی برق ورودی، خطاهای اصلی)؛ اول همین‌ها را انجام دهید. «متوسط» رفتارهای فرعیِ کاربردی است و «پایین» ریزه‌کاری‌ها (مثل اثر نوسان چند درصدی روی ریتم چشمک یا لبه‌های دقیق درصد و زمان).
-ستون «چه چیزی باید ببینید تا بگویید درست است» می‌گوید دقیقاً چه چیزی را باید ببینید یا بشنوید تا آن تست را قبول کنید؛ اگر چیز دیگری دیدید، وضعیت را «رد» بزنید و در شرح ایراد بنویسید چه دیدید.</t>
+          <t>اولویت‌ها ساده‌اند:
+«بالا» یعنی اول همین‌ها را تست کن. این‌ها کارهای اصلی دستگاه‌اند: روشن‌شدن، شروع و پایان شارژ، چراغ‌های اصلی، رفتن تغذیه روی برق ورودی و خطاهای اصلی.
+«متوسط» یعنی کارهای فرعی ولی کاربردی.
+«پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
+در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
+اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1074,7 @@
       </c>
       <c r="I4" s="49" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="49" t="inlineStr">
@@ -1088,12 +1099,12 @@
       </c>
       <c r="N4" s="49" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="49" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="49" t="inlineStr">
@@ -1169,7 +1180,7 @@
       <c r="N5" s="54" t="n"/>
       <c r="O5" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="56" t="n"/>
@@ -1240,7 +1251,7 @@
       <c r="N6" s="54" t="n"/>
       <c r="O6" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="56" t="n"/>
@@ -2166,7 +2177,7 @@
       </c>
       <c r="I4" s="49" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="49" t="inlineStr">
@@ -2191,12 +2202,12 @@
       </c>
       <c r="N4" s="49" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="49" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="49" t="inlineStr">
@@ -2274,7 +2285,7 @@
       <c r="N5" s="62" t="n"/>
       <c r="O5" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="63" t="n"/>
@@ -2348,7 +2359,7 @@
       <c r="N6" s="54" t="n"/>
       <c r="O6" s="56" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="56" t="n"/>
@@ -3139,7 +3150,7 @@
       </c>
       <c r="J3" s="71" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="K3" s="71" t="inlineStr">
@@ -3258,12 +3269,12 @@
     <row r="8">
       <c r="A8" s="48" t="inlineStr">
         <is>
-          <t>commit firmware</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="B8" s="48" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="C8" s="52" t="n"/>
@@ -3750,7 +3761,7 @@
       </c>
       <c r="I4" s="49" t="inlineStr">
         <is>
-          <t>وضعیت حفظ / latch</t>
+          <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
       <c r="J4" s="49" t="inlineStr">
@@ -3775,12 +3786,12 @@
       </c>
       <c r="N4" s="49" t="inlineStr">
         <is>
-          <t>مدرک تست / scope</t>
+          <t>مدرک تست</t>
         </is>
       </c>
       <c r="O4" s="49" t="inlineStr">
         <is>
-          <t>commit</t>
+          <t>نسخهٔ برنامه</t>
         </is>
       </c>
       <c r="P4" s="49" t="inlineStr">
@@ -3818,9 +3829,10 @@
       <c r="E5" s="62" t="inlineStr">
         <is>
           <t>گام ۱: یک بیلد تستی بگیر که در آن MODULE_PROTECTION=1 باشد.
-گام ۲: ADC را موقتاً نامعتبر کن (مثلاً ورودی را در دورهٔ warm-up قطع کن تا snapshot نامعتبر شود).
-گام ۳: بیت FAULT_ADC باید لحظه‌ای ست شود (در پنل/ماسک ببین).
-گام ۴: ADC را معتبر کن و اولین snapshot معتبر را بده (5 ثانیه کافی است): بیت باید خودش پاک شود؛ بیت بعد از معتبر شدن صفر است.</t>
+گام ۲: ADC را موقتاً نامعتبر کن. مثلاً ورودی را در دورهٔ گرم‌شدن (warm-up) قطع کن تا snapshot نامعتبر شود.
+گام ۳: بیت FAULT_ADC باید همان لحظه ست شود. در پنل یا ماسک ببین.
+گام ۴: ADC را معتبر کن و اولین snapshot معتبر را بده. 5 ثانیه کافی است.
+گام ۵: بیت باید خودش پاک شود. پس بعد از معتبرشدن، بیت صفر است.</t>
         </is>
       </c>
       <c r="F5" s="63" t="inlineStr">
@@ -3858,7 +3870,7 @@
       <c r="N5" s="62" t="n"/>
       <c r="O5" s="63" t="inlineStr">
         <is>
-          <t>TESTER: fill</t>
+          <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="63" t="n"/>

--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -14,8 +14,8 @@
     <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="ماشین حالت" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="تست‌های آزمایشگاهی" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$47</definedName>
@@ -191,7 +191,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -231,6 +231,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -319,7 +329,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -515,6 +525,32 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -888,7 +924,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>برگه تست و اعتبارسنجی عملی ماژول Protection</t>
         </is>
@@ -903,7 +939,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="49" t="inlineStr">
+      <c r="A3" s="82" t="inlineStr">
         <is>
           <t>هدف فایل</t>
         </is>
@@ -1011,7 +1047,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Protection</t>
         </is>
@@ -1032,87 +1068,87 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="82" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="82" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="82" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="82" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="H4" s="82" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="49" t="inlineStr">
+      <c r="I4" s="82" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="49" t="inlineStr">
+      <c r="J4" s="82" t="inlineStr">
         <is>
           <t>چه چیزی باید ببینید تا بگویید درست است</t>
         </is>
       </c>
-      <c r="K4" s="49" t="inlineStr">
+      <c r="K4" s="82" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="49" t="inlineStr">
+      <c r="L4" s="82" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="49" t="inlineStr">
+      <c r="M4" s="82" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="49" t="inlineStr">
+      <c r="N4" s="82" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="49" t="inlineStr">
+      <c r="O4" s="82" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="49" t="inlineStr">
+      <c r="P4" s="82" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="49" t="inlineStr">
+      <c r="Q4" s="82" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -1124,48 +1160,48 @@
           <t>PR-001</t>
         </is>
       </c>
-      <c r="B5" s="54" t="inlineStr">
+      <c r="B5" s="62" t="inlineStr">
         <is>
           <t>ماژول خاموش</t>
         </is>
       </c>
-      <c r="C5" s="55" t="inlineStr">
+      <c r="C5" s="67" t="inlineStr">
         <is>
           <t>بالا</t>
         </is>
       </c>
-      <c r="D5" s="54" t="inlineStr">
+      <c r="D5" s="62" t="inlineStr">
         <is>
           <t>دستگاه در حال کار عادی با باتری و بار واقعی است</t>
         </is>
       </c>
-      <c r="E5" s="54" t="inlineStr">
+      <c r="E5" s="62" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را چند ساعت در کار عادی (شارژ و مصرف) زیر نظر بگیر.
 گام ۲: دنبال قطع حفاظتیِ بی‌دلیل بگرد.</t>
         </is>
       </c>
-      <c r="F5" s="56" t="inlineStr">
+      <c r="F5" s="63" t="inlineStr">
         <is>
           <t>کار عادی چندساعته</t>
         </is>
       </c>
-      <c r="G5" s="56" t="inlineStr">
+      <c r="G5" s="63" t="inlineStr">
         <is>
           <t>چند ساعت</t>
         </is>
       </c>
-      <c r="H5" s="54" t="inlineStr">
+      <c r="H5" s="62" t="inlineStr">
         <is>
           <t>هیچ قطع حفاظتیِ اضافه‌ای در کار عادی دیده نمی‌شود؛ محصول با همان حفاظت‌های ماژول‌های فعال کار می‌کند</t>
         </is>
       </c>
-      <c r="I5" s="54" t="inlineStr">
+      <c r="I5" s="62" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J5" s="54" t="inlineStr">
+      <c r="J5" s="62" t="inlineStr">
         <is>
           <t>باید ببینید: در کار عادی هیچ قطع حفاظتیِ اضافه‌ای نیست و دستگاه چند ساعت تمیز کار می‌کند. اگر قطع بی‌دلیل دیدید، قبول نیست.</t>
         </is>
@@ -1178,13 +1214,13 @@
       </c>
       <c r="M5" s="54" t="n"/>
       <c r="N5" s="54" t="n"/>
-      <c r="O5" s="56" t="inlineStr">
+      <c r="O5" s="63" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P5" s="56" t="n"/>
-      <c r="Q5" s="58">
+      <c r="Q5" s="65">
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
@@ -1195,48 +1231,48 @@
           <t>PR-003</t>
         </is>
       </c>
-      <c r="B6" s="54" t="inlineStr">
+      <c r="B6" s="83" t="inlineStr">
         <is>
           <t>بوت قبل از warm-up</t>
         </is>
       </c>
-      <c r="C6" s="55" t="inlineStr">
+      <c r="C6" s="84" t="inlineStr">
         <is>
           <t>متوسط</t>
         </is>
       </c>
-      <c r="D6" s="54" t="inlineStr">
+      <c r="D6" s="83" t="inlineStr">
         <is>
           <t>دستگاه کاملاً خاموش و سرد است؛ بار روی خروجی وصل است</t>
         </is>
       </c>
-      <c r="E6" s="54" t="inlineStr">
+      <c r="E6" s="83" t="inlineStr">
         <is>
           <t>گام ۱: دستگاه را روشن کن.
 گام ۲: در همان ثانیه‌های اول بار را نگاه کن.</t>
         </is>
       </c>
-      <c r="F6" s="56" t="inlineStr">
+      <c r="F6" s="85" t="inlineStr">
         <is>
           <t>روشن‌کردن سرد با بار</t>
         </is>
       </c>
-      <c r="G6" s="56" t="inlineStr">
+      <c r="G6" s="85" t="inlineStr">
         <is>
           <t>یک دقیقه</t>
         </is>
       </c>
-      <c r="H6" s="54" t="inlineStr">
+      <c r="H6" s="83" t="inlineStr">
         <is>
           <t>خروجی در لحظه‌های اول بی‌دلیل قطع نمی‌شود؛ دستگاه تمیز بالا می‌آید و بار عادی کار می‌کند</t>
         </is>
       </c>
-      <c r="I6" s="54" t="inlineStr">
+      <c r="I6" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="54" t="inlineStr">
+      <c r="J6" s="83" t="inlineStr">
         <is>
           <t>باید ببینید: دستگاه در لحظه‌های اول بی‌دلیل قطع نمی‌شود و تمیز بالا می‌آید و بار عادی کار می‌کند. اگر قطع‌ووصل اول کار دیدید، قبول نیست.</t>
         </is>
@@ -1249,13 +1285,13 @@
       </c>
       <c r="M6" s="54" t="n"/>
       <c r="N6" s="54" t="n"/>
-      <c r="O6" s="56" t="inlineStr">
+      <c r="O6" s="85" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="56" t="n"/>
-      <c r="Q6" s="58">
+      <c r="Q6" s="86">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
         <v/>
       </c>
@@ -2043,7 +2079,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00385723"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2070,7 +2106,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="60" t="inlineStr">
+      <c r="A1" s="87" t="inlineStr">
         <is>
           <t>تست‌های برنامه‌نویسی و هاست (جدا از ولیدیشن عملی برد)</t>
         </is>
@@ -2135,87 +2171,87 @@
       <c r="Q3" s="52" t="n"/>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="82" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="82" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="82" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="82" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="H4" s="82" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="49" t="inlineStr">
+      <c r="I4" s="82" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="49" t="inlineStr">
+      <c r="J4" s="82" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="49" t="inlineStr">
+      <c r="K4" s="82" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="49" t="inlineStr">
+      <c r="L4" s="82" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="49" t="inlineStr">
+      <c r="M4" s="82" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="49" t="inlineStr">
+      <c r="N4" s="82" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="49" t="inlineStr">
+      <c r="O4" s="82" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="49" t="inlineStr">
+      <c r="P4" s="82" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="49" t="inlineStr">
+      <c r="Q4" s="82" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -2301,22 +2337,22 @@
           <t>PR-005</t>
         </is>
       </c>
-      <c r="B6" s="54" t="inlineStr">
+      <c r="B6" s="83" t="inlineStr">
         <is>
           <t>فعال‌سازی آینده</t>
         </is>
       </c>
-      <c r="C6" s="56" t="inlineStr">
+      <c r="C6" s="85" t="inlineStr">
         <is>
           <t>پایین</t>
         </is>
       </c>
-      <c r="D6" s="54" t="inlineStr">
+      <c r="D6" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="66" t="inlineStr">
+      <c r="E6" s="88" t="inlineStr">
         <is>
           <t>گام ۱: کد ماژول را کامل مرور کن (protection.c و هدرش).
 گام ۲: شرایط فعال‌سازی حفاظت کامل (اضافه‌جریان، باتری ضعیف و...) و سیاست هر کدام را روی کاغذ بنویس.
@@ -2324,27 +2360,27 @@
 گام ۴: قبولی یعنی همین سند تصمیم موجود و تأیید شده باشد؛ این ردیف تست برد نیست.</t>
         </is>
       </c>
-      <c r="F6" s="56" t="inlineStr">
+      <c r="F6" s="85" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="56" t="inlineStr">
+      <c r="G6" s="85" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="54" t="inlineStr">
+      <c r="H6" s="83" t="inlineStr">
         <is>
           <t>شرایط فعال‌سازی و سیاست‌ها قبل از MODULE_PROTECTION=1 مستند و به تأیید کاربر برسد</t>
         </is>
       </c>
-      <c r="I6" s="54" t="inlineStr">
+      <c r="I6" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J6" s="54" t="inlineStr">
+      <c r="J6" s="83" t="inlineStr">
         <is>
           <t>سند تصمیم موجود</t>
         </is>
@@ -2357,13 +2393,13 @@
       </c>
       <c r="M6" s="54" t="n"/>
       <c r="N6" s="54" t="n"/>
-      <c r="O6" s="56" t="inlineStr">
+      <c r="O6" s="85" t="inlineStr">
         <is>
           <t>(بعد از تست پر شود)</t>
         </is>
       </c>
       <c r="P6" s="56" t="n"/>
-      <c r="Q6" s="58" t="inlineStr">
+      <c r="Q6" s="86" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -2902,7 +2938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2913,7 +2949,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="89" t="inlineStr">
         <is>
           <t>مرجع سریع سناریوها و ثابت‌های ماژول Protection</t>
         </is>
@@ -3038,6 +3074,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
@@ -3077,14 +3114,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>ثبت ایرادهای مشاهده‌شده — ماژول Protection</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="49" t="inlineStr">
+      <c r="A2" s="82" t="inlineStr">
         <is>
           <t>برای هر وضعیت «رد» یا تفاوت مهم، یک ردیف با شناسهٔ یکتا ثبت و پس از اصلاح دوباره تست شود.</t>
         </is>
@@ -3194,7 +3231,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="47" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>تأیید نهایی اعتبارسنجی — ماژول Protection</t>
         </is>
@@ -3429,7 +3466,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00808080"/>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3441,7 +3478,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="76" t="inlineStr">
+      <c r="A1" s="90" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
@@ -3497,7 +3534,7 @@
       <c r="B7" s="52" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="76" t="inlineStr">
+      <c r="A8" s="90" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
@@ -3533,7 +3570,7 @@
       <c r="B12" s="52" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="76" t="inlineStr">
+      <c r="A13" s="90" t="inlineStr">
         <is>
           <t>شدت</t>
         </is>
@@ -3580,98 +3617,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="007030A0"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>ماشین حالت ماژول نگهبان اعتبار (Protection)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="52" t="n"/>
-      <c r="B2" s="52" t="n"/>
-      <c r="C2" s="52" t="n"/>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>حالت‌ها و گذارهای همین ماژول</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Protection_State_Machine.xlsx</t>
-        </is>
-      </c>
-      <c r="C3" s="52" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>../../../Documentation/System_State_Machine.xlsx</t>
-        </is>
-      </c>
-      <c r="C4" s="52" t="n"/>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>راهنمای رنگ‌ها</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
-        </is>
-      </c>
-      <c r="C5" s="52" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>بازتولید</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>python3 tools/make_module_state_machines.py</t>
-        </is>
-      </c>
-      <c r="C6" s="52" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId3"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F4E79"/>
+    <tabColor rgb="00ED7D31"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3698,7 +3644,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="81" t="inlineStr">
         <is>
           <t>برنامهٔ تست آزمایشگاهی — ماژول Protection</t>
         </is>
@@ -3719,87 +3665,87 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="49" t="inlineStr">
+      <c r="A4" s="82" t="inlineStr">
         <is>
           <t>شناسه</t>
         </is>
       </c>
-      <c r="B4" s="49" t="inlineStr">
+      <c r="B4" s="82" t="inlineStr">
         <is>
           <t>دسته</t>
         </is>
       </c>
-      <c r="C4" s="49" t="inlineStr">
+      <c r="C4" s="82" t="inlineStr">
         <is>
           <t>اولویت</t>
         </is>
       </c>
-      <c r="D4" s="49" t="inlineStr">
+      <c r="D4" s="82" t="inlineStr">
         <is>
           <t>پیش‌شرط</t>
         </is>
       </c>
-      <c r="E4" s="49" t="inlineStr">
+      <c r="E4" s="82" t="inlineStr">
         <is>
           <t>روش اجرای دقیق</t>
         </is>
       </c>
-      <c r="F4" s="49" t="inlineStr">
+      <c r="F4" s="82" t="inlineStr">
         <is>
           <t>ورودی‌ها / شرایط</t>
         </is>
       </c>
-      <c r="G4" s="49" t="inlineStr">
+      <c r="G4" s="82" t="inlineStr">
         <is>
           <t>مدت مشاهده</t>
         </is>
       </c>
-      <c r="H4" s="49" t="inlineStr">
+      <c r="H4" s="82" t="inlineStr">
         <is>
           <t>رفتار مورد انتظار</t>
         </is>
       </c>
-      <c r="I4" s="49" t="inlineStr">
+      <c r="I4" s="82" t="inlineStr">
         <is>
           <t>می‌ماند یا پاک می‌شود</t>
         </is>
       </c>
-      <c r="J4" s="49" t="inlineStr">
+      <c r="J4" s="82" t="inlineStr">
         <is>
           <t>معیار قبولی</t>
         </is>
       </c>
-      <c r="K4" s="49" t="inlineStr">
+      <c r="K4" s="82" t="inlineStr">
         <is>
           <t>نتیجهٔ واقعی / اندازه‌گیری</t>
         </is>
       </c>
-      <c r="L4" s="49" t="inlineStr">
+      <c r="L4" s="82" t="inlineStr">
         <is>
           <t>وضعیت</t>
         </is>
       </c>
-      <c r="M4" s="49" t="inlineStr">
+      <c r="M4" s="82" t="inlineStr">
         <is>
           <t>شرح ایراد / تفاوت</t>
         </is>
       </c>
-      <c r="N4" s="49" t="inlineStr">
+      <c r="N4" s="82" t="inlineStr">
         <is>
           <t>مدرک تست</t>
         </is>
       </c>
-      <c r="O4" s="49" t="inlineStr">
+      <c r="O4" s="82" t="inlineStr">
         <is>
           <t>نسخهٔ برنامه</t>
         </is>
       </c>
-      <c r="P4" s="49" t="inlineStr">
+      <c r="P4" s="82" t="inlineStr">
         <is>
           <t>نام تست‌کننده</t>
         </is>
       </c>
-      <c r="Q4" s="49" t="inlineStr">
+      <c r="Q4" s="82" t="inlineStr">
         <is>
           <t>تاریخ</t>
         </is>
@@ -3893,4 +3839,87 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="78" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>ماشین حالت ماژول نگهبان اعتبار (Protection)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>حالت‌ها و گذارهای همین ماژول</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Protection_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>ماشین حالت کل برنامه (نمای سیستمی)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>../../../Documentation/System_State_Machine.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>راهنمای رنگ‌ها</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>سبز = عادی/سالم · زرد = هشدار یا انتظار · قرمز = خطا یا قفل · نارنجی = در حال کار · خاکستری = بی‌کار · آبی = اطلاعاتی</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>بازتولید</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>python3 tools/make_module_state_machines.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId2"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -32,7 +32,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -190,8 +190,19 @@
       <name val="Vazirmatn"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Vazirmatn"/>
+      <i val="1"/>
+      <color rgb="00404040"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -241,6 +252,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -329,7 +345,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -551,6 +567,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -917,7 +951,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -985,7 +1019,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="78" t="inlineStr">
         <is>
@@ -995,6 +1028,18 @@
 «پایین» یعنی ریزه‌کاری‌ها؛ مثل اثر نوسان کوچک روی ریتم چشمک.
 در ستون «چه چیزی باید ببینید تا بگویید درست است» نوشته‌ایم دقیقاً چه باید ببینی یا بشنوی.
 اگر چیز دیگری دیدی، وضعیت را «رد» بزن و در «شرح ایراد» بنویس چه دیدی.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="91" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه</t>
+        </is>
+      </c>
+      <c r="B13" s="92" t="inlineStr">
+        <is>
+          <t>در شیت «برنامه تست»، ستون آخر («پیش‌بینی زندهٔ برنامه») با فرمول اکسل حساب می‌کند که برنامهٔ روی برد با ورودی‌های فعلی چه کار می‌کند. ورودی‌ها خانه‌های زرد بالای همان شیت‌اند؛ عددشان را عوض کن، نتیجه را بخوان و با رفتار واقعی برد مقایسه کن. هر جا «—» است، آن تست پیش‌بینی فرمولی ندارد (مثل دیالوگ پنل یا تست‌های حافظه).</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q46"/>
+  <dimension ref="A1:U46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1044,12 +1089,20 @@
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="52" customWidth="1" min="18" max="18"/>
+    <col width="34" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="81" t="inlineStr">
         <is>
           <t>برنامهٔ تست عملی — ماژول Protection</t>
+        </is>
+      </c>
+      <c r="T1" s="93" t="inlineStr">
+        <is>
+          <t>ورودی‌های پیش‌بینی — خانه‌های زرد را عوض کن و ستون «پیش‌بینی زنده» را ببین</t>
         </is>
       </c>
     </row>
@@ -1059,6 +1112,14 @@
           <t>وضعیت فقط یکی از: در انتظار / قبول / رد / مسدود / نیاز به تکرار. تست Host جایگزین تست برد نیست.</t>
         </is>
       </c>
+      <c r="T2" s="94" t="inlineStr">
+        <is>
+          <t>داده معتبر است؟ (1/0)</t>
+        </is>
+      </c>
+      <c r="U2" s="95" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="48" t="inlineStr">
@@ -1066,6 +1127,14 @@
           <t>برای هر ردیف پیش‌شرط، ورودی، انتظار و معیار قبولی صریح است؛ نتیجهٔ واقعی فقط با اندازه‌گیری روی برد پر می‌شود.</t>
         </is>
       </c>
+      <c r="T3" s="94" t="inlineStr">
+        <is>
+          <t>ماژول در بیلد روشن است؟ (1/0)</t>
+        </is>
+      </c>
+      <c r="U3" s="95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="82" t="inlineStr">
@@ -1151,6 +1220,16 @@
       <c r="Q4" s="82" t="inlineStr">
         <is>
           <t>تاریخ</t>
+        </is>
+      </c>
+      <c r="R4" s="82" t="inlineStr">
+        <is>
+          <t>پیش‌بینی زندهٔ برنامه (فرمول)</t>
+        </is>
+      </c>
+      <c r="T4" s="96" t="inlineStr">
+        <is>
+          <t>پیش‌بینی برای حالت پایدار است؛ چشمک و زمان‌بندی را با چشم و کرنومتر چک کن و با برد مقایسه کن.</t>
         </is>
       </c>
     </row>
@@ -1224,6 +1303,10 @@
         <f>IF(OR(L5="",L5="در انتظار"),"",IF(Q5="",TODAY(),Q5))</f>
         <v/>
       </c>
+      <c r="R5" s="92">
+        <f>IF($U$3=0,"ماژول در بیلد خاموش است: هیچ بیتی ست نمی‌شود و دستگاه عادی کار می‌کند","بیلد تستی است: رفتار ماژول روشن را ببین")</f>
+        <v/>
+      </c>
     </row>
     <row r="6" ht="54" customHeight="1">
       <c r="A6" s="53" t="inlineStr">
@@ -1293,6 +1376,10 @@
       <c r="P6" s="56" t="n"/>
       <c r="Q6" s="86">
         <f>IF(OR(L6="",L6="در انتظار"),"",IF(Q6="",TODAY(),Q6))</f>
+        <v/>
+      </c>
+      <c r="R6" s="92">
+        <f>IF($U$2=1,"داده معتبر: بیت FAULT_ADC پاک است","داده نامعتبر: بیت FAULT_ADC همان لحظه ست می‌شود (قفل نمی‌ماند)")</f>
         <v/>
       </c>
     </row>
@@ -2058,10 +2145,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:Q47"/>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="T1:U1"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="T4:U4"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C5:C6" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2938,7 +3027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3074,7 +3163,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
@@ -3848,7 +3936,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3862,7 +3950,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
@@ -3911,7 +3998,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/Firmware/Modules/Protection/Protection_Validation.xlsx
+++ b/Firmware/Modules/Protection/Protection_Validation.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="تست‌های آزمایشگاهی" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="برنامه تست" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های برنامه‌نویسی" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مراجع سناریو" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ثبت ایراد" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تأیید نهایی" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="فهرست‌ها" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="تست‌های آزمایشگاهی" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ماشین حالت" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'برنامه تست'!$A$4:$Q$47</definedName>
